--- a/Revision_Previsiones_Q4_2026/Revision_Previsiones_Q4_2026_Garcia.xlsx
+++ b/Revision_Previsiones_Q4_2026/Revision_Previsiones_Q4_2026_Garcia.xlsx
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:U128"/>
+  <dimension ref="B2:V128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -749,19 +749,20 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="32" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="15" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="17" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="32" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
     <col width="17" customWidth="1" min="19" max="19"/>
-    <col width="15" customWidth="1" min="20" max="20"/>
-    <col width="34" customWidth="1" min="21" max="21"/>
+    <col width="17" customWidth="1" min="20" max="20"/>
+    <col width="15" customWidth="1" min="21" max="21"/>
+    <col width="34" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="2" ht="36" customHeight="1">
@@ -774,14 +775,14 @@
     <row r="3" ht="20" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>DELEGADO COMERCIAL: GARCÍA | Cierre Septiembre Oficial (01/10/2026) vs Previsiones a Final de Año | Generado: 01/10/2026 10:17</t>
+          <t>DELEGADO COMERCIAL: GARCÍA | Cierre Septiembre Oficial (01/10/2026) vs Previsiones a Final de Año | Generado: 01/10/2026 10:45</t>
         </is>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>📌 INSTRUCCIONES: 1) Revise el bloque de SEPTIEMBRE (Previsto vs Real) e indique en la col. K el motivo de la desviación (adelanto, atraso, extra). 2) En las columnas verdes (M, O, Q), revise y actualice las cantidades estimadas de Octubre, Noviembre y Diciembre si prevé cambios. 3) Comente en col. U cualquier nota de campaña.</t>
+          <t>📌 INSTRUCCIONES: 1) Revise el bloque de SEPTIEMBRE (Previsto, Real, Error Absoluto y Forecast Accuracy) e indique en col. L el motivo de la desviación (adelanto, atraso, extra). 2) En las columnas verdes (N, P, R), revise y actualice las cantidades estimadas de Octubre, Noviembre y Diciembre si prevé cambios. 3) Comente en col. V cualquier nota de campaña.</t>
         </is>
       </c>
     </row>
@@ -808,32 +809,33 @@
       <c r="I5" s="5" t="n"/>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>FORECAST ACCURACY SEP</t>
+          <t>FORECAST ACCURACY SEP (OFICIAL)</t>
         </is>
       </c>
       <c r="K5" s="5" t="n"/>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>PREVISIÓN INICIAL Q4 (U)</t>
         </is>
       </c>
-      <c r="M5" s="5" t="n"/>
       <c r="N5" s="5" t="n"/>
-      <c r="O5" s="6" t="inlineStr">
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="6" t="inlineStr">
         <is>
           <t>PREVISIÓN REVISADA Q4 (U)</t>
         </is>
       </c>
-      <c r="P5" s="5" t="n"/>
       <c r="Q5" s="5" t="n"/>
-      <c r="R5" s="8" t="inlineStr">
+      <c r="R5" s="5" t="n"/>
+      <c r="S5" s="8" t="inlineStr">
         <is>
           <t>VARIACIÓN NETA Q4 (U)</t>
         </is>
       </c>
-      <c r="S5" s="5" t="n"/>
       <c r="T5" s="5" t="n"/>
       <c r="U5" s="5" t="n"/>
+      <c r="V5" s="5" t="n"/>
     </row>
     <row r="6" ht="26" customHeight="1">
       <c r="B6" s="9">
@@ -849,34 +851,35 @@
       <c r="F6" s="5" t="n"/>
       <c r="G6" s="5" t="n"/>
       <c r="H6" s="11">
-        <f>I128</f>
+        <f>J128</f>
         <v/>
       </c>
       <c r="I6" s="5" t="n"/>
       <c r="J6" s="11">
-        <f>J128</f>
+        <f>K128</f>
         <v/>
       </c>
       <c r="K6" s="5" t="n"/>
-      <c r="L6" s="9">
-        <f>R128</f>
-        <v/>
-      </c>
-      <c r="M6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="9">
+        <f>S128</f>
+        <v/>
+      </c>
       <c r="N6" s="5" t="n"/>
-      <c r="O6" s="10">
-        <f>S128</f>
-        <v/>
-      </c>
-      <c r="P6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="10">
+        <f>T128</f>
+        <v/>
+      </c>
       <c r="Q6" s="5" t="n"/>
-      <c r="R6" s="12">
-        <f>T128</f>
-        <v/>
-      </c>
-      <c r="S6" s="5" t="n"/>
+      <c r="R6" s="5" t="n"/>
+      <c r="S6" s="12">
+        <f>U128</f>
+        <v/>
+      </c>
       <c r="T6" s="5" t="n"/>
       <c r="U6" s="5" t="n"/>
+      <c r="V6" s="5" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="B8" s="13" t="inlineStr">
@@ -886,15 +889,15 @@
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>CIERRE SEPTIEMBRE 2026 (CALIBRACIÓN Y ANÁLISIS)</t>
-        </is>
-      </c>
-      <c r="L8" s="15" t="inlineStr">
+          <t>CIERRE SEPTIEMBRE 2026 (CALIBRACIÓN Y ANÁLISIS DE EXACTITUD)</t>
+        </is>
+      </c>
+      <c r="M8" s="15" t="inlineStr">
         <is>
           <t>REVISIÓN PREVISIONES MES A MES (HASTA FINAL DE AÑO 2026)</t>
         </is>
       </c>
-      <c r="R8" s="16" t="inlineStr">
+      <c r="S8" s="16" t="inlineStr">
         <is>
           <t>IMPACTO Q4 Y JUSTIFICACIÓN</t>
         </is>
@@ -938,65 +941,70 @@
       </c>
       <c r="I9" s="18" t="inlineStr">
         <is>
+          <t>Error Abs. Sep (u)</t>
+        </is>
+      </c>
+      <c r="J9" s="18" t="inlineStr">
+        <is>
           <t>% Consec.</t>
         </is>
       </c>
-      <c r="J9" s="18" t="inlineStr">
+      <c r="K9" s="18" t="inlineStr">
         <is>
           <t>Forecast Accuracy</t>
         </is>
       </c>
-      <c r="K9" s="18" t="inlineStr">
+      <c r="L9" s="18" t="inlineStr">
         <is>
           <t>Comentario Sep (¿Adelanto/Atraso/Extra?)</t>
         </is>
       </c>
-      <c r="L9" s="19" t="inlineStr">
+      <c r="M9" s="19" t="inlineStr">
         <is>
           <t>Oct Anterior (u)</t>
         </is>
       </c>
-      <c r="M9" s="19" t="inlineStr">
+      <c r="N9" s="19" t="inlineStr">
         <is>
           <t>Oct Revisado (u)</t>
         </is>
       </c>
-      <c r="N9" s="19" t="inlineStr">
+      <c r="O9" s="19" t="inlineStr">
         <is>
           <t>Nov Anterior (u)</t>
         </is>
       </c>
-      <c r="O9" s="19" t="inlineStr">
+      <c r="P9" s="19" t="inlineStr">
         <is>
           <t>Nov Revisado (u)</t>
         </is>
       </c>
-      <c r="P9" s="19" t="inlineStr">
+      <c r="Q9" s="19" t="inlineStr">
         <is>
           <t>Dic Anterior (u)</t>
         </is>
       </c>
-      <c r="Q9" s="19" t="inlineStr">
+      <c r="R9" s="19" t="inlineStr">
         <is>
           <t>Dic Revisado (u)</t>
         </is>
       </c>
-      <c r="R9" s="17" t="inlineStr">
+      <c r="S9" s="17" t="inlineStr">
         <is>
           <t>Total Q4 Ant (u)</t>
         </is>
       </c>
-      <c r="S9" s="17" t="inlineStr">
+      <c r="T9" s="17" t="inlineStr">
         <is>
           <t>Total Q4 Rev (u)</t>
         </is>
       </c>
-      <c r="T9" s="17" t="inlineStr">
+      <c r="U9" s="17" t="inlineStr">
         <is>
           <t>Dif Q4 (u)</t>
         </is>
       </c>
-      <c r="U9" s="17" t="inlineStr">
+      <c r="V9" s="17" t="inlineStr">
         <is>
           <t>Comentarios / Justificación Q4</t>
         </is>
@@ -1033,46 +1041,50 @@
         <f>G10-F10</f>
         <v/>
       </c>
-      <c r="I10" s="26">
+      <c r="I10" s="23">
+        <f>ABS(G10-F10)</f>
+        <v/>
+      </c>
+      <c r="J10" s="26">
         <f>IF(F10&gt;0, G10/F10, IF(G10&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J10" s="27">
-        <f>IF(F10=0, IF(G10=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G10-F10)/F10))</f>
-        <v/>
-      </c>
-      <c r="K10" s="28" t="inlineStr"/>
-      <c r="L10" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="29" t="n">
+      <c r="K10" s="27">
+        <f>IF(F10&gt;0, 1.0 - (I10/F10), IF(G10=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L10" s="28" t="inlineStr"/>
+      <c r="M10" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="29" t="n">
         <v>200</v>
       </c>
-      <c r="Q10" s="30" t="n">
+      <c r="R10" s="30" t="n">
         <v>200</v>
       </c>
-      <c r="R10" s="23">
-        <f>L10+N10+P10</f>
-        <v/>
-      </c>
-      <c r="S10" s="24">
+      <c r="S10" s="23">
         <f>M10+O10+Q10</f>
         <v/>
       </c>
-      <c r="T10" s="25">
-        <f>S10-R10</f>
-        <v/>
-      </c>
-      <c r="U10" s="31" t="inlineStr"/>
+      <c r="T10" s="24">
+        <f>N10+P10+R10</f>
+        <v/>
+      </c>
+      <c r="U10" s="25">
+        <f>T10-S10</f>
+        <v/>
+      </c>
+      <c r="V10" s="31" t="inlineStr"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="B11" s="20" t="inlineStr">
@@ -1105,46 +1117,50 @@
         <f>G11-F11</f>
         <v/>
       </c>
-      <c r="I11" s="26">
+      <c r="I11" s="23">
+        <f>ABS(G11-F11)</f>
+        <v/>
+      </c>
+      <c r="J11" s="26">
         <f>IF(F11&gt;0, G11/F11, IF(G11&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J11" s="27">
-        <f>IF(F11=0, IF(G11=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G11-F11)/F11))</f>
-        <v/>
-      </c>
-      <c r="K11" s="28" t="inlineStr"/>
-      <c r="L11" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="29" t="n">
+      <c r="K11" s="27">
+        <f>IF(F11&gt;0, 1.0 - (I11/F11), IF(G11=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L11" s="28" t="inlineStr"/>
+      <c r="M11" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="29" t="n">
         <v>1280</v>
       </c>
-      <c r="O11" s="30" t="n">
+      <c r="P11" s="30" t="n">
         <v>1280</v>
       </c>
-      <c r="P11" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="23">
-        <f>L11+N11+P11</f>
-        <v/>
-      </c>
-      <c r="S11" s="24">
+      <c r="Q11" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="23">
         <f>M11+O11+Q11</f>
         <v/>
       </c>
-      <c r="T11" s="25">
-        <f>S11-R11</f>
-        <v/>
-      </c>
-      <c r="U11" s="31" t="inlineStr"/>
+      <c r="T11" s="24">
+        <f>N11+P11+R11</f>
+        <v/>
+      </c>
+      <c r="U11" s="25">
+        <f>T11-S11</f>
+        <v/>
+      </c>
+      <c r="V11" s="31" t="inlineStr"/>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="B12" s="20" t="inlineStr">
@@ -1177,46 +1193,50 @@
         <f>G12-F12</f>
         <v/>
       </c>
-      <c r="I12" s="26">
+      <c r="I12" s="23">
+        <f>ABS(G12-F12)</f>
+        <v/>
+      </c>
+      <c r="J12" s="26">
         <f>IF(F12&gt;0, G12/F12, IF(G12&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J12" s="27">
-        <f>IF(F12=0, IF(G12=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G12-F12)/F12))</f>
-        <v/>
-      </c>
-      <c r="K12" s="28" t="inlineStr"/>
-      <c r="L12" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="29" t="n">
+      <c r="K12" s="27">
+        <f>IF(F12&gt;0, 1.0 - (I12/F12), IF(G12=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L12" s="28" t="inlineStr"/>
+      <c r="M12" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="29" t="n">
         <v>2000</v>
       </c>
-      <c r="O12" s="30" t="n">
+      <c r="P12" s="30" t="n">
         <v>2000</v>
       </c>
-      <c r="P12" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="23">
-        <f>L12+N12+P12</f>
-        <v/>
-      </c>
-      <c r="S12" s="24">
+      <c r="Q12" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="23">
         <f>M12+O12+Q12</f>
         <v/>
       </c>
-      <c r="T12" s="25">
-        <f>S12-R12</f>
-        <v/>
-      </c>
-      <c r="U12" s="31" t="inlineStr"/>
+      <c r="T12" s="24">
+        <f>N12+P12+R12</f>
+        <v/>
+      </c>
+      <c r="U12" s="25">
+        <f>T12-S12</f>
+        <v/>
+      </c>
+      <c r="V12" s="31" t="inlineStr"/>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="B13" s="20" t="inlineStr">
@@ -1249,46 +1269,50 @@
         <f>G13-F13</f>
         <v/>
       </c>
-      <c r="I13" s="26">
+      <c r="I13" s="23">
+        <f>ABS(G13-F13)</f>
+        <v/>
+      </c>
+      <c r="J13" s="26">
         <f>IF(F13&gt;0, G13/F13, IF(G13&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J13" s="27">
-        <f>IF(F13=0, IF(G13=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G13-F13)/F13))</f>
-        <v/>
-      </c>
-      <c r="K13" s="28" t="inlineStr"/>
-      <c r="L13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="23">
-        <f>L13+N13+P13</f>
-        <v/>
-      </c>
-      <c r="S13" s="24">
+      <c r="K13" s="27">
+        <f>IF(F13&gt;0, 1.0 - (I13/F13), IF(G13=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L13" s="28" t="inlineStr"/>
+      <c r="M13" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="23">
         <f>M13+O13+Q13</f>
         <v/>
       </c>
-      <c r="T13" s="25">
-        <f>S13-R13</f>
-        <v/>
-      </c>
-      <c r="U13" s="31" t="inlineStr"/>
+      <c r="T13" s="24">
+        <f>N13+P13+R13</f>
+        <v/>
+      </c>
+      <c r="U13" s="25">
+        <f>T13-S13</f>
+        <v/>
+      </c>
+      <c r="V13" s="31" t="inlineStr"/>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="B14" s="20" t="inlineStr">
@@ -1321,50 +1345,54 @@
         <f>G14-F14</f>
         <v/>
       </c>
-      <c r="I14" s="26">
+      <c r="I14" s="23">
+        <f>ABS(G14-F14)</f>
+        <v/>
+      </c>
+      <c r="J14" s="26">
         <f>IF(F14&gt;0, G14/F14, IF(G14&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J14" s="27">
-        <f>IF(F14=0, IF(G14=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G14-F14)/F14))</f>
-        <v/>
-      </c>
-      <c r="K14" s="28" t="inlineStr">
+      <c r="K14" s="27">
+        <f>IF(F14&gt;0, 1.0 - (I14/F14), IF(G14=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L14" s="28" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
       </c>
-      <c r="L14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="23">
-        <f>L14+N14+P14</f>
-        <v/>
-      </c>
-      <c r="S14" s="24">
+      <c r="M14" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="23">
         <f>M14+O14+Q14</f>
         <v/>
       </c>
-      <c r="T14" s="25">
-        <f>S14-R14</f>
-        <v/>
-      </c>
-      <c r="U14" s="31" t="inlineStr"/>
+      <c r="T14" s="24">
+        <f>N14+P14+R14</f>
+        <v/>
+      </c>
+      <c r="U14" s="25">
+        <f>T14-S14</f>
+        <v/>
+      </c>
+      <c r="V14" s="31" t="inlineStr"/>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="B15" s="20" t="inlineStr">
@@ -1397,46 +1425,50 @@
         <f>G15-F15</f>
         <v/>
       </c>
-      <c r="I15" s="26">
+      <c r="I15" s="23">
+        <f>ABS(G15-F15)</f>
+        <v/>
+      </c>
+      <c r="J15" s="26">
         <f>IF(F15&gt;0, G15/F15, IF(G15&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J15" s="27">
-        <f>IF(F15=0, IF(G15=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G15-F15)/F15))</f>
-        <v/>
-      </c>
-      <c r="K15" s="28" t="inlineStr"/>
-      <c r="L15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="29" t="n">
+      <c r="K15" s="27">
+        <f>IF(F15&gt;0, 1.0 - (I15/F15), IF(G15=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L15" s="28" t="inlineStr"/>
+      <c r="M15" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="29" t="n">
         <v>600</v>
       </c>
-      <c r="O15" s="30" t="n">
+      <c r="P15" s="30" t="n">
         <v>600</v>
       </c>
-      <c r="P15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="23">
-        <f>L15+N15+P15</f>
-        <v/>
-      </c>
-      <c r="S15" s="24">
+      <c r="Q15" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="23">
         <f>M15+O15+Q15</f>
         <v/>
       </c>
-      <c r="T15" s="25">
-        <f>S15-R15</f>
-        <v/>
-      </c>
-      <c r="U15" s="31" t="inlineStr"/>
+      <c r="T15" s="24">
+        <f>N15+P15+R15</f>
+        <v/>
+      </c>
+      <c r="U15" s="25">
+        <f>T15-S15</f>
+        <v/>
+      </c>
+      <c r="V15" s="31" t="inlineStr"/>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="B16" s="20" t="inlineStr">
@@ -1469,46 +1501,50 @@
         <f>G16-F16</f>
         <v/>
       </c>
-      <c r="I16" s="26">
+      <c r="I16" s="23">
+        <f>ABS(G16-F16)</f>
+        <v/>
+      </c>
+      <c r="J16" s="26">
         <f>IF(F16&gt;0, G16/F16, IF(G16&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J16" s="27">
-        <f>IF(F16=0, IF(G16=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G16-F16)/F16))</f>
-        <v/>
-      </c>
-      <c r="K16" s="28" t="inlineStr"/>
-      <c r="L16" s="29" t="n">
+      <c r="K16" s="27">
+        <f>IF(F16&gt;0, 1.0 - (I16/F16), IF(G16=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L16" s="28" t="inlineStr"/>
+      <c r="M16" s="29" t="n">
         <v>1100</v>
       </c>
-      <c r="M16" s="30" t="n">
+      <c r="N16" s="30" t="n">
         <v>1100</v>
       </c>
-      <c r="N16" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="23">
-        <f>L16+N16+P16</f>
-        <v/>
-      </c>
-      <c r="S16" s="24">
+      <c r="O16" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="23">
         <f>M16+O16+Q16</f>
         <v/>
       </c>
-      <c r="T16" s="25">
-        <f>S16-R16</f>
-        <v/>
-      </c>
-      <c r="U16" s="31" t="inlineStr"/>
+      <c r="T16" s="24">
+        <f>N16+P16+R16</f>
+        <v/>
+      </c>
+      <c r="U16" s="25">
+        <f>T16-S16</f>
+        <v/>
+      </c>
+      <c r="V16" s="31" t="inlineStr"/>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="B17" s="20" t="inlineStr">
@@ -1541,46 +1577,50 @@
         <f>G17-F17</f>
         <v/>
       </c>
-      <c r="I17" s="26">
+      <c r="I17" s="23">
+        <f>ABS(G17-F17)</f>
+        <v/>
+      </c>
+      <c r="J17" s="26">
         <f>IF(F17&gt;0, G17/F17, IF(G17&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J17" s="27">
-        <f>IF(F17=0, IF(G17=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G17-F17)/F17))</f>
-        <v/>
-      </c>
-      <c r="K17" s="28" t="inlineStr"/>
-      <c r="L17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="29" t="n">
+      <c r="K17" s="27">
+        <f>IF(F17&gt;0, 1.0 - (I17/F17), IF(G17=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L17" s="28" t="inlineStr"/>
+      <c r="M17" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="29" t="n">
         <v>1280</v>
       </c>
-      <c r="O17" s="30" t="n">
+      <c r="P17" s="30" t="n">
         <v>1280</v>
       </c>
-      <c r="P17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" s="23">
-        <f>L17+N17+P17</f>
-        <v/>
-      </c>
-      <c r="S17" s="24">
+      <c r="Q17" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="23">
         <f>M17+O17+Q17</f>
         <v/>
       </c>
-      <c r="T17" s="25">
-        <f>S17-R17</f>
-        <v/>
-      </c>
-      <c r="U17" s="31" t="inlineStr"/>
+      <c r="T17" s="24">
+        <f>N17+P17+R17</f>
+        <v/>
+      </c>
+      <c r="U17" s="25">
+        <f>T17-S17</f>
+        <v/>
+      </c>
+      <c r="V17" s="31" t="inlineStr"/>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="B18" s="20" t="inlineStr">
@@ -1613,46 +1653,50 @@
         <f>G18-F18</f>
         <v/>
       </c>
-      <c r="I18" s="26">
+      <c r="I18" s="23">
+        <f>ABS(G18-F18)</f>
+        <v/>
+      </c>
+      <c r="J18" s="26">
         <f>IF(F18&gt;0, G18/F18, IF(G18&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J18" s="27">
-        <f>IF(F18=0, IF(G18=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G18-F18)/F18))</f>
-        <v/>
-      </c>
-      <c r="K18" s="28" t="inlineStr"/>
-      <c r="L18" s="29" t="n">
+      <c r="K18" s="27">
+        <f>IF(F18&gt;0, 1.0 - (I18/F18), IF(G18=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L18" s="28" t="inlineStr"/>
+      <c r="M18" s="29" t="n">
         <v>5000</v>
       </c>
-      <c r="M18" s="30" t="n">
+      <c r="N18" s="30" t="n">
         <v>5000</v>
       </c>
-      <c r="N18" s="29" t="n">
+      <c r="O18" s="29" t="n">
         <v>5000</v>
       </c>
-      <c r="O18" s="30" t="n">
+      <c r="P18" s="30" t="n">
         <v>5000</v>
       </c>
-      <c r="P18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" s="23">
-        <f>L18+N18+P18</f>
-        <v/>
-      </c>
-      <c r="S18" s="24">
+      <c r="Q18" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="23">
         <f>M18+O18+Q18</f>
         <v/>
       </c>
-      <c r="T18" s="25">
-        <f>S18-R18</f>
-        <v/>
-      </c>
-      <c r="U18" s="31" t="inlineStr"/>
+      <c r="T18" s="24">
+        <f>N18+P18+R18</f>
+        <v/>
+      </c>
+      <c r="U18" s="25">
+        <f>T18-S18</f>
+        <v/>
+      </c>
+      <c r="V18" s="31" t="inlineStr"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="B19" s="20" t="inlineStr">
@@ -1685,46 +1729,50 @@
         <f>G19-F19</f>
         <v/>
       </c>
-      <c r="I19" s="26">
+      <c r="I19" s="23">
+        <f>ABS(G19-F19)</f>
+        <v/>
+      </c>
+      <c r="J19" s="26">
         <f>IF(F19&gt;0, G19/F19, IF(G19&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J19" s="27">
-        <f>IF(F19=0, IF(G19=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G19-F19)/F19))</f>
-        <v/>
-      </c>
-      <c r="K19" s="28" t="inlineStr"/>
-      <c r="L19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="29" t="n">
+      <c r="K19" s="27">
+        <f>IF(F19&gt;0, 1.0 - (I19/F19), IF(G19=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L19" s="28" t="inlineStr"/>
+      <c r="M19" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="29" t="n">
         <v>750</v>
       </c>
-      <c r="Q19" s="30" t="n">
+      <c r="R19" s="30" t="n">
         <v>750</v>
       </c>
-      <c r="R19" s="23">
-        <f>L19+N19+P19</f>
-        <v/>
-      </c>
-      <c r="S19" s="24">
+      <c r="S19" s="23">
         <f>M19+O19+Q19</f>
         <v/>
       </c>
-      <c r="T19" s="25">
-        <f>S19-R19</f>
-        <v/>
-      </c>
-      <c r="U19" s="31" t="inlineStr"/>
+      <c r="T19" s="24">
+        <f>N19+P19+R19</f>
+        <v/>
+      </c>
+      <c r="U19" s="25">
+        <f>T19-S19</f>
+        <v/>
+      </c>
+      <c r="V19" s="31" t="inlineStr"/>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="B20" s="20" t="inlineStr">
@@ -1757,46 +1805,50 @@
         <f>G20-F20</f>
         <v/>
       </c>
-      <c r="I20" s="26">
+      <c r="I20" s="23">
+        <f>ABS(G20-F20)</f>
+        <v/>
+      </c>
+      <c r="J20" s="26">
         <f>IF(F20&gt;0, G20/F20, IF(G20&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J20" s="27">
-        <f>IF(F20=0, IF(G20=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G20-F20)/F20))</f>
-        <v/>
-      </c>
-      <c r="K20" s="28" t="inlineStr"/>
-      <c r="L20" s="29" t="n">
+      <c r="K20" s="27">
+        <f>IF(F20&gt;0, 1.0 - (I20/F20), IF(G20=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L20" s="28" t="inlineStr"/>
+      <c r="M20" s="29" t="n">
         <v>2200</v>
       </c>
-      <c r="M20" s="30" t="n">
+      <c r="N20" s="30" t="n">
         <v>2200</v>
       </c>
-      <c r="N20" s="29" t="n">
+      <c r="O20" s="29" t="n">
         <v>3300</v>
       </c>
-      <c r="O20" s="30" t="n">
+      <c r="P20" s="30" t="n">
         <v>3300</v>
       </c>
-      <c r="P20" s="29" t="n">
+      <c r="Q20" s="29" t="n">
         <v>1100</v>
       </c>
-      <c r="Q20" s="30" t="n">
+      <c r="R20" s="30" t="n">
         <v>1100</v>
       </c>
-      <c r="R20" s="23">
-        <f>L20+N20+P20</f>
-        <v/>
-      </c>
-      <c r="S20" s="24">
+      <c r="S20" s="23">
         <f>M20+O20+Q20</f>
         <v/>
       </c>
-      <c r="T20" s="25">
-        <f>S20-R20</f>
-        <v/>
-      </c>
-      <c r="U20" s="31" t="inlineStr"/>
+      <c r="T20" s="24">
+        <f>N20+P20+R20</f>
+        <v/>
+      </c>
+      <c r="U20" s="25">
+        <f>T20-S20</f>
+        <v/>
+      </c>
+      <c r="V20" s="31" t="inlineStr"/>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="B21" s="20" t="inlineStr">
@@ -1829,46 +1881,50 @@
         <f>G21-F21</f>
         <v/>
       </c>
-      <c r="I21" s="26">
+      <c r="I21" s="23">
+        <f>ABS(G21-F21)</f>
+        <v/>
+      </c>
+      <c r="J21" s="26">
         <f>IF(F21&gt;0, G21/F21, IF(G21&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J21" s="27">
-        <f>IF(F21=0, IF(G21=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G21-F21)/F21))</f>
-        <v/>
-      </c>
-      <c r="K21" s="28" t="inlineStr"/>
-      <c r="L21" s="29" t="n">
+      <c r="K21" s="27">
+        <f>IF(F21&gt;0, 1.0 - (I21/F21), IF(G21=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L21" s="28" t="inlineStr"/>
+      <c r="M21" s="29" t="n">
         <v>1280</v>
       </c>
-      <c r="M21" s="30" t="n">
+      <c r="N21" s="30" t="n">
         <v>1280</v>
       </c>
-      <c r="N21" s="29" t="n">
+      <c r="O21" s="29" t="n">
         <v>640</v>
       </c>
-      <c r="O21" s="30" t="n">
+      <c r="P21" s="30" t="n">
         <v>640</v>
       </c>
-      <c r="P21" s="29" t="n">
+      <c r="Q21" s="29" t="n">
         <v>640</v>
       </c>
-      <c r="Q21" s="30" t="n">
+      <c r="R21" s="30" t="n">
         <v>640</v>
       </c>
-      <c r="R21" s="23">
-        <f>L21+N21+P21</f>
-        <v/>
-      </c>
-      <c r="S21" s="24">
+      <c r="S21" s="23">
         <f>M21+O21+Q21</f>
         <v/>
       </c>
-      <c r="T21" s="25">
-        <f>S21-R21</f>
-        <v/>
-      </c>
-      <c r="U21" s="31" t="inlineStr"/>
+      <c r="T21" s="24">
+        <f>N21+P21+R21</f>
+        <v/>
+      </c>
+      <c r="U21" s="25">
+        <f>T21-S21</f>
+        <v/>
+      </c>
+      <c r="V21" s="31" t="inlineStr"/>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="B22" s="20" t="inlineStr">
@@ -1901,46 +1957,50 @@
         <f>G22-F22</f>
         <v/>
       </c>
-      <c r="I22" s="26">
+      <c r="I22" s="23">
+        <f>ABS(G22-F22)</f>
+        <v/>
+      </c>
+      <c r="J22" s="26">
         <f>IF(F22&gt;0, G22/F22, IF(G22&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J22" s="27">
-        <f>IF(F22=0, IF(G22=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G22-F22)/F22))</f>
-        <v/>
-      </c>
-      <c r="K22" s="28" t="inlineStr"/>
-      <c r="L22" s="29" t="n">
+      <c r="K22" s="27">
+        <f>IF(F22&gt;0, 1.0 - (I22/F22), IF(G22=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L22" s="28" t="inlineStr"/>
+      <c r="M22" s="29" t="n">
         <v>2000</v>
       </c>
-      <c r="M22" s="30" t="n">
+      <c r="N22" s="30" t="n">
         <v>2000</v>
       </c>
-      <c r="N22" s="29" t="n">
+      <c r="O22" s="29" t="n">
         <v>2000</v>
       </c>
-      <c r="O22" s="30" t="n">
+      <c r="P22" s="30" t="n">
         <v>2000</v>
       </c>
-      <c r="P22" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" s="23">
-        <f>L22+N22+P22</f>
-        <v/>
-      </c>
-      <c r="S22" s="24">
+      <c r="Q22" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="23">
         <f>M22+O22+Q22</f>
         <v/>
       </c>
-      <c r="T22" s="25">
-        <f>S22-R22</f>
-        <v/>
-      </c>
-      <c r="U22" s="31" t="inlineStr"/>
+      <c r="T22" s="24">
+        <f>N22+P22+R22</f>
+        <v/>
+      </c>
+      <c r="U22" s="25">
+        <f>T22-S22</f>
+        <v/>
+      </c>
+      <c r="V22" s="31" t="inlineStr"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="B23" s="20" t="inlineStr">
@@ -1973,46 +2033,50 @@
         <f>G23-F23</f>
         <v/>
       </c>
-      <c r="I23" s="26">
+      <c r="I23" s="23">
+        <f>ABS(G23-F23)</f>
+        <v/>
+      </c>
+      <c r="J23" s="26">
         <f>IF(F23&gt;0, G23/F23, IF(G23&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J23" s="27">
-        <f>IF(F23=0, IF(G23=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G23-F23)/F23))</f>
-        <v/>
-      </c>
-      <c r="K23" s="28" t="inlineStr"/>
-      <c r="L23" s="29" t="n">
+      <c r="K23" s="27">
+        <f>IF(F23&gt;0, 1.0 - (I23/F23), IF(G23=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L23" s="28" t="inlineStr"/>
+      <c r="M23" s="29" t="n">
         <v>600</v>
       </c>
-      <c r="M23" s="30" t="n">
+      <c r="N23" s="30" t="n">
         <v>600</v>
       </c>
-      <c r="N23" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" s="23">
-        <f>L23+N23+P23</f>
-        <v/>
-      </c>
-      <c r="S23" s="24">
+      <c r="O23" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="23">
         <f>M23+O23+Q23</f>
         <v/>
       </c>
-      <c r="T23" s="25">
-        <f>S23-R23</f>
-        <v/>
-      </c>
-      <c r="U23" s="31" t="inlineStr"/>
+      <c r="T23" s="24">
+        <f>N23+P23+R23</f>
+        <v/>
+      </c>
+      <c r="U23" s="25">
+        <f>T23-S23</f>
+        <v/>
+      </c>
+      <c r="V23" s="31" t="inlineStr"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="B24" s="20" t="inlineStr">
@@ -2045,46 +2109,50 @@
         <f>G24-F24</f>
         <v/>
       </c>
-      <c r="I24" s="26">
+      <c r="I24" s="23">
+        <f>ABS(G24-F24)</f>
+        <v/>
+      </c>
+      <c r="J24" s="26">
         <f>IF(F24&gt;0, G24/F24, IF(G24&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J24" s="27">
-        <f>IF(F24=0, IF(G24=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G24-F24)/F24))</f>
-        <v/>
-      </c>
-      <c r="K24" s="28" t="inlineStr"/>
-      <c r="L24" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="29" t="n">
+      <c r="K24" s="27">
+        <f>IF(F24&gt;0, 1.0 - (I24/F24), IF(G24=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L24" s="28" t="inlineStr"/>
+      <c r="M24" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="29" t="n">
         <v>200</v>
       </c>
-      <c r="O24" s="30" t="n">
+      <c r="P24" s="30" t="n">
         <v>200</v>
       </c>
-      <c r="P24" s="29" t="n">
+      <c r="Q24" s="29" t="n">
         <v>200</v>
       </c>
-      <c r="Q24" s="30" t="n">
+      <c r="R24" s="30" t="n">
         <v>200</v>
       </c>
-      <c r="R24" s="23">
-        <f>L24+N24+P24</f>
-        <v/>
-      </c>
-      <c r="S24" s="24">
+      <c r="S24" s="23">
         <f>M24+O24+Q24</f>
         <v/>
       </c>
-      <c r="T24" s="25">
-        <f>S24-R24</f>
-        <v/>
-      </c>
-      <c r="U24" s="31" t="inlineStr"/>
+      <c r="T24" s="24">
+        <f>N24+P24+R24</f>
+        <v/>
+      </c>
+      <c r="U24" s="25">
+        <f>T24-S24</f>
+        <v/>
+      </c>
+      <c r="V24" s="31" t="inlineStr"/>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="B25" s="20" t="inlineStr">
@@ -2117,46 +2185,50 @@
         <f>G25-F25</f>
         <v/>
       </c>
-      <c r="I25" s="26">
+      <c r="I25" s="23">
+        <f>ABS(G25-F25)</f>
+        <v/>
+      </c>
+      <c r="J25" s="26">
         <f>IF(F25&gt;0, G25/F25, IF(G25&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J25" s="27">
-        <f>IF(F25=0, IF(G25=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G25-F25)/F25))</f>
-        <v/>
-      </c>
-      <c r="K25" s="28" t="inlineStr"/>
-      <c r="L25" s="29" t="n">
+      <c r="K25" s="27">
+        <f>IF(F25&gt;0, 1.0 - (I25/F25), IF(G25=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L25" s="28" t="inlineStr"/>
+      <c r="M25" s="29" t="n">
         <v>640</v>
       </c>
-      <c r="M25" s="30" t="n">
+      <c r="N25" s="30" t="n">
         <v>640</v>
       </c>
-      <c r="N25" s="29" t="n">
+      <c r="O25" s="29" t="n">
         <v>640</v>
       </c>
-      <c r="O25" s="30" t="n">
+      <c r="P25" s="30" t="n">
         <v>640</v>
       </c>
-      <c r="P25" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" s="23">
-        <f>L25+N25+P25</f>
-        <v/>
-      </c>
-      <c r="S25" s="24">
+      <c r="Q25" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="23">
         <f>M25+O25+Q25</f>
         <v/>
       </c>
-      <c r="T25" s="25">
-        <f>S25-R25</f>
-        <v/>
-      </c>
-      <c r="U25" s="31" t="inlineStr"/>
+      <c r="T25" s="24">
+        <f>N25+P25+R25</f>
+        <v/>
+      </c>
+      <c r="U25" s="25">
+        <f>T25-S25</f>
+        <v/>
+      </c>
+      <c r="V25" s="31" t="inlineStr"/>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="B26" s="20" t="inlineStr">
@@ -2189,46 +2261,50 @@
         <f>G26-F26</f>
         <v/>
       </c>
-      <c r="I26" s="26">
+      <c r="I26" s="23">
+        <f>ABS(G26-F26)</f>
+        <v/>
+      </c>
+      <c r="J26" s="26">
         <f>IF(F26&gt;0, G26/F26, IF(G26&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J26" s="27">
-        <f>IF(F26=0, IF(G26=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G26-F26)/F26))</f>
-        <v/>
-      </c>
-      <c r="K26" s="28" t="inlineStr"/>
-      <c r="L26" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="23">
-        <f>L26+N26+P26</f>
-        <v/>
-      </c>
-      <c r="S26" s="24">
+      <c r="K26" s="27">
+        <f>IF(F26&gt;0, 1.0 - (I26/F26), IF(G26=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L26" s="28" t="inlineStr"/>
+      <c r="M26" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="23">
         <f>M26+O26+Q26</f>
         <v/>
       </c>
-      <c r="T26" s="25">
-        <f>S26-R26</f>
-        <v/>
-      </c>
-      <c r="U26" s="31" t="inlineStr"/>
+      <c r="T26" s="24">
+        <f>N26+P26+R26</f>
+        <v/>
+      </c>
+      <c r="U26" s="25">
+        <f>T26-S26</f>
+        <v/>
+      </c>
+      <c r="V26" s="31" t="inlineStr"/>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="B27" s="20" t="inlineStr">
@@ -2261,46 +2337,50 @@
         <f>G27-F27</f>
         <v/>
       </c>
-      <c r="I27" s="26">
+      <c r="I27" s="23">
+        <f>ABS(G27-F27)</f>
+        <v/>
+      </c>
+      <c r="J27" s="26">
         <f>IF(F27&gt;0, G27/F27, IF(G27&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J27" s="27">
-        <f>IF(F27=0, IF(G27=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G27-F27)/F27))</f>
-        <v/>
-      </c>
-      <c r="K27" s="28" t="inlineStr"/>
-      <c r="L27" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" s="23">
-        <f>L27+N27+P27</f>
-        <v/>
-      </c>
-      <c r="S27" s="24">
+      <c r="K27" s="27">
+        <f>IF(F27&gt;0, 1.0 - (I27/F27), IF(G27=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L27" s="28" t="inlineStr"/>
+      <c r="M27" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="23">
         <f>M27+O27+Q27</f>
         <v/>
       </c>
-      <c r="T27" s="25">
-        <f>S27-R27</f>
-        <v/>
-      </c>
-      <c r="U27" s="31" t="inlineStr"/>
+      <c r="T27" s="24">
+        <f>N27+P27+R27</f>
+        <v/>
+      </c>
+      <c r="U27" s="25">
+        <f>T27-S27</f>
+        <v/>
+      </c>
+      <c r="V27" s="31" t="inlineStr"/>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="B28" s="20" t="inlineStr">
@@ -2333,46 +2413,50 @@
         <f>G28-F28</f>
         <v/>
       </c>
-      <c r="I28" s="26">
+      <c r="I28" s="23">
+        <f>ABS(G28-F28)</f>
+        <v/>
+      </c>
+      <c r="J28" s="26">
         <f>IF(F28&gt;0, G28/F28, IF(G28&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J28" s="27">
-        <f>IF(F28=0, IF(G28=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G28-F28)/F28))</f>
-        <v/>
-      </c>
-      <c r="K28" s="28" t="inlineStr"/>
-      <c r="L28" s="29" t="n">
+      <c r="K28" s="27">
+        <f>IF(F28&gt;0, 1.0 - (I28/F28), IF(G28=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L28" s="28" t="inlineStr"/>
+      <c r="M28" s="29" t="n">
         <v>100</v>
       </c>
-      <c r="M28" s="30" t="n">
+      <c r="N28" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="N28" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" s="23">
-        <f>L28+N28+P28</f>
-        <v/>
-      </c>
-      <c r="S28" s="24">
+      <c r="O28" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="23">
         <f>M28+O28+Q28</f>
         <v/>
       </c>
-      <c r="T28" s="25">
-        <f>S28-R28</f>
-        <v/>
-      </c>
-      <c r="U28" s="31" t="inlineStr"/>
+      <c r="T28" s="24">
+        <f>N28+P28+R28</f>
+        <v/>
+      </c>
+      <c r="U28" s="25">
+        <f>T28-S28</f>
+        <v/>
+      </c>
+      <c r="V28" s="31" t="inlineStr"/>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="B29" s="20" t="inlineStr">
@@ -2405,46 +2489,50 @@
         <f>G29-F29</f>
         <v/>
       </c>
-      <c r="I29" s="26">
+      <c r="I29" s="23">
+        <f>ABS(G29-F29)</f>
+        <v/>
+      </c>
+      <c r="J29" s="26">
         <f>IF(F29&gt;0, G29/F29, IF(G29&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J29" s="27">
-        <f>IF(F29=0, IF(G29=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G29-F29)/F29))</f>
-        <v/>
-      </c>
-      <c r="K29" s="28" t="inlineStr"/>
-      <c r="L29" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="29" t="n">
+      <c r="K29" s="27">
+        <f>IF(F29&gt;0, 1.0 - (I29/F29), IF(G29=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L29" s="28" t="inlineStr"/>
+      <c r="M29" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="29" t="n">
         <v>200</v>
       </c>
-      <c r="O29" s="30" t="n">
+      <c r="P29" s="30" t="n">
         <v>200</v>
       </c>
-      <c r="P29" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" s="23">
-        <f>L29+N29+P29</f>
-        <v/>
-      </c>
-      <c r="S29" s="24">
+      <c r="Q29" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="23">
         <f>M29+O29+Q29</f>
         <v/>
       </c>
-      <c r="T29" s="25">
-        <f>S29-R29</f>
-        <v/>
-      </c>
-      <c r="U29" s="31" t="inlineStr"/>
+      <c r="T29" s="24">
+        <f>N29+P29+R29</f>
+        <v/>
+      </c>
+      <c r="U29" s="25">
+        <f>T29-S29</f>
+        <v/>
+      </c>
+      <c r="V29" s="31" t="inlineStr"/>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="B30" s="20" t="inlineStr">
@@ -2477,46 +2565,50 @@
         <f>G30-F30</f>
         <v/>
       </c>
-      <c r="I30" s="26">
+      <c r="I30" s="23">
+        <f>ABS(G30-F30)</f>
+        <v/>
+      </c>
+      <c r="J30" s="26">
         <f>IF(F30&gt;0, G30/F30, IF(G30&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J30" s="27">
-        <f>IF(F30=0, IF(G30=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G30-F30)/F30))</f>
-        <v/>
-      </c>
-      <c r="K30" s="28" t="inlineStr"/>
-      <c r="L30" s="29" t="n">
+      <c r="K30" s="27">
+        <f>IF(F30&gt;0, 1.0 - (I30/F30), IF(G30=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L30" s="28" t="inlineStr"/>
+      <c r="M30" s="29" t="n">
         <v>100</v>
       </c>
-      <c r="M30" s="30" t="n">
+      <c r="N30" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="N30" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="29" t="n">
+      <c r="O30" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="29" t="n">
         <v>100</v>
       </c>
-      <c r="Q30" s="30" t="n">
+      <c r="R30" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="R30" s="23">
-        <f>L30+N30+P30</f>
-        <v/>
-      </c>
-      <c r="S30" s="24">
+      <c r="S30" s="23">
         <f>M30+O30+Q30</f>
         <v/>
       </c>
-      <c r="T30" s="25">
-        <f>S30-R30</f>
-        <v/>
-      </c>
-      <c r="U30" s="31" t="inlineStr"/>
+      <c r="T30" s="24">
+        <f>N30+P30+R30</f>
+        <v/>
+      </c>
+      <c r="U30" s="25">
+        <f>T30-S30</f>
+        <v/>
+      </c>
+      <c r="V30" s="31" t="inlineStr"/>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="B31" s="20" t="inlineStr">
@@ -2549,46 +2641,50 @@
         <f>G31-F31</f>
         <v/>
       </c>
-      <c r="I31" s="26">
+      <c r="I31" s="23">
+        <f>ABS(G31-F31)</f>
+        <v/>
+      </c>
+      <c r="J31" s="26">
         <f>IF(F31&gt;0, G31/F31, IF(G31&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J31" s="27">
-        <f>IF(F31=0, IF(G31=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G31-F31)/F31))</f>
-        <v/>
-      </c>
-      <c r="K31" s="28" t="inlineStr"/>
-      <c r="L31" s="29" t="n">
+      <c r="K31" s="27">
+        <f>IF(F31&gt;0, 1.0 - (I31/F31), IF(G31=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L31" s="28" t="inlineStr"/>
+      <c r="M31" s="29" t="n">
         <v>300</v>
       </c>
-      <c r="M31" s="30" t="n">
+      <c r="N31" s="30" t="n">
         <v>300</v>
       </c>
-      <c r="N31" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" s="29" t="n">
+      <c r="O31" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="29" t="n">
         <v>300</v>
       </c>
-      <c r="Q31" s="30" t="n">
+      <c r="R31" s="30" t="n">
         <v>300</v>
       </c>
-      <c r="R31" s="23">
-        <f>L31+N31+P31</f>
-        <v/>
-      </c>
-      <c r="S31" s="24">
+      <c r="S31" s="23">
         <f>M31+O31+Q31</f>
         <v/>
       </c>
-      <c r="T31" s="25">
-        <f>S31-R31</f>
-        <v/>
-      </c>
-      <c r="U31" s="31" t="inlineStr"/>
+      <c r="T31" s="24">
+        <f>N31+P31+R31</f>
+        <v/>
+      </c>
+      <c r="U31" s="25">
+        <f>T31-S31</f>
+        <v/>
+      </c>
+      <c r="V31" s="31" t="inlineStr"/>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="B32" s="20" t="inlineStr">
@@ -2621,46 +2717,50 @@
         <f>G32-F32</f>
         <v/>
       </c>
-      <c r="I32" s="26">
+      <c r="I32" s="23">
+        <f>ABS(G32-F32)</f>
+        <v/>
+      </c>
+      <c r="J32" s="26">
         <f>IF(F32&gt;0, G32/F32, IF(G32&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J32" s="27">
-        <f>IF(F32=0, IF(G32=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G32-F32)/F32))</f>
-        <v/>
-      </c>
-      <c r="K32" s="28" t="inlineStr"/>
-      <c r="L32" s="29" t="n">
+      <c r="K32" s="27">
+        <f>IF(F32&gt;0, 1.0 - (I32/F32), IF(G32=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L32" s="28" t="inlineStr"/>
+      <c r="M32" s="29" t="n">
         <v>200</v>
       </c>
-      <c r="M32" s="30" t="n">
+      <c r="N32" s="30" t="n">
         <v>200</v>
       </c>
-      <c r="N32" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" s="29" t="n">
+      <c r="O32" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="29" t="n">
         <v>200</v>
       </c>
-      <c r="Q32" s="30" t="n">
+      <c r="R32" s="30" t="n">
         <v>200</v>
       </c>
-      <c r="R32" s="23">
-        <f>L32+N32+P32</f>
-        <v/>
-      </c>
-      <c r="S32" s="24">
+      <c r="S32" s="23">
         <f>M32+O32+Q32</f>
         <v/>
       </c>
-      <c r="T32" s="25">
-        <f>S32-R32</f>
-        <v/>
-      </c>
-      <c r="U32" s="31" t="inlineStr"/>
+      <c r="T32" s="24">
+        <f>N32+P32+R32</f>
+        <v/>
+      </c>
+      <c r="U32" s="25">
+        <f>T32-S32</f>
+        <v/>
+      </c>
+      <c r="V32" s="31" t="inlineStr"/>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="B33" s="20" t="inlineStr">
@@ -2693,46 +2793,50 @@
         <f>G33-F33</f>
         <v/>
       </c>
-      <c r="I33" s="26">
+      <c r="I33" s="23">
+        <f>ABS(G33-F33)</f>
+        <v/>
+      </c>
+      <c r="J33" s="26">
         <f>IF(F33&gt;0, G33/F33, IF(G33&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J33" s="27">
-        <f>IF(F33=0, IF(G33=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G33-F33)/F33))</f>
-        <v/>
-      </c>
-      <c r="K33" s="28" t="inlineStr"/>
-      <c r="L33" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" s="29" t="n">
+      <c r="K33" s="27">
+        <f>IF(F33&gt;0, 1.0 - (I33/F33), IF(G33=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L33" s="28" t="inlineStr"/>
+      <c r="M33" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="29" t="n">
         <v>200</v>
       </c>
-      <c r="Q33" s="30" t="n">
+      <c r="R33" s="30" t="n">
         <v>200</v>
       </c>
-      <c r="R33" s="23">
-        <f>L33+N33+P33</f>
-        <v/>
-      </c>
-      <c r="S33" s="24">
+      <c r="S33" s="23">
         <f>M33+O33+Q33</f>
         <v/>
       </c>
-      <c r="T33" s="25">
-        <f>S33-R33</f>
-        <v/>
-      </c>
-      <c r="U33" s="31" t="inlineStr"/>
+      <c r="T33" s="24">
+        <f>N33+P33+R33</f>
+        <v/>
+      </c>
+      <c r="U33" s="25">
+        <f>T33-S33</f>
+        <v/>
+      </c>
+      <c r="V33" s="31" t="inlineStr"/>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="B34" s="20" t="inlineStr">
@@ -2765,46 +2869,50 @@
         <f>G34-F34</f>
         <v/>
       </c>
-      <c r="I34" s="26">
+      <c r="I34" s="23">
+        <f>ABS(G34-F34)</f>
+        <v/>
+      </c>
+      <c r="J34" s="26">
         <f>IF(F34&gt;0, G34/F34, IF(G34&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J34" s="27">
-        <f>IF(F34=0, IF(G34=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G34-F34)/F34))</f>
-        <v/>
-      </c>
-      <c r="K34" s="28" t="inlineStr"/>
-      <c r="L34" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" s="29" t="n">
+      <c r="K34" s="27">
+        <f>IF(F34&gt;0, 1.0 - (I34/F34), IF(G34=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L34" s="28" t="inlineStr"/>
+      <c r="M34" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="29" t="n">
         <v>5000</v>
       </c>
-      <c r="Q34" s="30" t="n">
+      <c r="R34" s="30" t="n">
         <v>5000</v>
       </c>
-      <c r="R34" s="23">
-        <f>L34+N34+P34</f>
-        <v/>
-      </c>
-      <c r="S34" s="24">
+      <c r="S34" s="23">
         <f>M34+O34+Q34</f>
         <v/>
       </c>
-      <c r="T34" s="25">
-        <f>S34-R34</f>
-        <v/>
-      </c>
-      <c r="U34" s="31" t="inlineStr"/>
+      <c r="T34" s="24">
+        <f>N34+P34+R34</f>
+        <v/>
+      </c>
+      <c r="U34" s="25">
+        <f>T34-S34</f>
+        <v/>
+      </c>
+      <c r="V34" s="31" t="inlineStr"/>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="B35" s="20" t="inlineStr">
@@ -2837,46 +2945,50 @@
         <f>G35-F35</f>
         <v/>
       </c>
-      <c r="I35" s="26">
+      <c r="I35" s="23">
+        <f>ABS(G35-F35)</f>
+        <v/>
+      </c>
+      <c r="J35" s="26">
         <f>IF(F35&gt;0, G35/F35, IF(G35&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J35" s="27">
-        <f>IF(F35=0, IF(G35=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G35-F35)/F35))</f>
-        <v/>
-      </c>
-      <c r="K35" s="28" t="inlineStr"/>
-      <c r="L35" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" s="29" t="n">
+      <c r="K35" s="27">
+        <f>IF(F35&gt;0, 1.0 - (I35/F35), IF(G35=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L35" s="28" t="inlineStr"/>
+      <c r="M35" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="29" t="n">
         <v>5000</v>
       </c>
-      <c r="Q35" s="30" t="n">
+      <c r="R35" s="30" t="n">
         <v>5000</v>
       </c>
-      <c r="R35" s="23">
-        <f>L35+N35+P35</f>
-        <v/>
-      </c>
-      <c r="S35" s="24">
+      <c r="S35" s="23">
         <f>M35+O35+Q35</f>
         <v/>
       </c>
-      <c r="T35" s="25">
-        <f>S35-R35</f>
-        <v/>
-      </c>
-      <c r="U35" s="31" t="inlineStr"/>
+      <c r="T35" s="24">
+        <f>N35+P35+R35</f>
+        <v/>
+      </c>
+      <c r="U35" s="25">
+        <f>T35-S35</f>
+        <v/>
+      </c>
+      <c r="V35" s="31" t="inlineStr"/>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="B36" s="20" t="inlineStr">
@@ -2909,46 +3021,50 @@
         <f>G36-F36</f>
         <v/>
       </c>
-      <c r="I36" s="26">
+      <c r="I36" s="23">
+        <f>ABS(G36-F36)</f>
+        <v/>
+      </c>
+      <c r="J36" s="26">
         <f>IF(F36&gt;0, G36/F36, IF(G36&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J36" s="27">
-        <f>IF(F36=0, IF(G36=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G36-F36)/F36))</f>
-        <v/>
-      </c>
-      <c r="K36" s="28" t="inlineStr"/>
-      <c r="L36" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" s="29" t="n">
+      <c r="K36" s="27">
+        <f>IF(F36&gt;0, 1.0 - (I36/F36), IF(G36=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L36" s="28" t="inlineStr"/>
+      <c r="M36" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="29" t="n">
         <v>7700</v>
       </c>
-      <c r="Q36" s="30" t="n">
+      <c r="R36" s="30" t="n">
         <v>7700</v>
       </c>
-      <c r="R36" s="23">
-        <f>L36+N36+P36</f>
-        <v/>
-      </c>
-      <c r="S36" s="24">
+      <c r="S36" s="23">
         <f>M36+O36+Q36</f>
         <v/>
       </c>
-      <c r="T36" s="25">
-        <f>S36-R36</f>
-        <v/>
-      </c>
-      <c r="U36" s="31" t="inlineStr"/>
+      <c r="T36" s="24">
+        <f>N36+P36+R36</f>
+        <v/>
+      </c>
+      <c r="U36" s="25">
+        <f>T36-S36</f>
+        <v/>
+      </c>
+      <c r="V36" s="31" t="inlineStr"/>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="B37" s="20" t="inlineStr">
@@ -2981,46 +3097,50 @@
         <f>G37-F37</f>
         <v/>
       </c>
-      <c r="I37" s="26">
+      <c r="I37" s="23">
+        <f>ABS(G37-F37)</f>
+        <v/>
+      </c>
+      <c r="J37" s="26">
         <f>IF(F37&gt;0, G37/F37, IF(G37&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J37" s="27">
-        <f>IF(F37=0, IF(G37=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G37-F37)/F37))</f>
-        <v/>
-      </c>
-      <c r="K37" s="28" t="inlineStr"/>
-      <c r="L37" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" s="29" t="n">
+      <c r="K37" s="27">
+        <f>IF(F37&gt;0, 1.0 - (I37/F37), IF(G37=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L37" s="28" t="inlineStr"/>
+      <c r="M37" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="29" t="n">
         <v>10000</v>
       </c>
-      <c r="Q37" s="30" t="n">
+      <c r="R37" s="30" t="n">
         <v>10000</v>
       </c>
-      <c r="R37" s="23">
-        <f>L37+N37+P37</f>
-        <v/>
-      </c>
-      <c r="S37" s="24">
+      <c r="S37" s="23">
         <f>M37+O37+Q37</f>
         <v/>
       </c>
-      <c r="T37" s="25">
-        <f>S37-R37</f>
-        <v/>
-      </c>
-      <c r="U37" s="31" t="inlineStr"/>
+      <c r="T37" s="24">
+        <f>N37+P37+R37</f>
+        <v/>
+      </c>
+      <c r="U37" s="25">
+        <f>T37-S37</f>
+        <v/>
+      </c>
+      <c r="V37" s="31" t="inlineStr"/>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="B38" s="20" t="inlineStr">
@@ -3053,46 +3173,50 @@
         <f>G38-F38</f>
         <v/>
       </c>
-      <c r="I38" s="26">
+      <c r="I38" s="23">
+        <f>ABS(G38-F38)</f>
+        <v/>
+      </c>
+      <c r="J38" s="26">
         <f>IF(F38&gt;0, G38/F38, IF(G38&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J38" s="27">
-        <f>IF(F38=0, IF(G38=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G38-F38)/F38))</f>
-        <v/>
-      </c>
-      <c r="K38" s="28" t="inlineStr"/>
-      <c r="L38" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" s="29" t="n">
+      <c r="K38" s="27">
+        <f>IF(F38&gt;0, 1.0 - (I38/F38), IF(G38=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L38" s="28" t="inlineStr"/>
+      <c r="M38" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="29" t="n">
         <v>1000</v>
       </c>
-      <c r="Q38" s="30" t="n">
+      <c r="R38" s="30" t="n">
         <v>1000</v>
       </c>
-      <c r="R38" s="23">
-        <f>L38+N38+P38</f>
-        <v/>
-      </c>
-      <c r="S38" s="24">
+      <c r="S38" s="23">
         <f>M38+O38+Q38</f>
         <v/>
       </c>
-      <c r="T38" s="25">
-        <f>S38-R38</f>
-        <v/>
-      </c>
-      <c r="U38" s="31" t="inlineStr"/>
+      <c r="T38" s="24">
+        <f>N38+P38+R38</f>
+        <v/>
+      </c>
+      <c r="U38" s="25">
+        <f>T38-S38</f>
+        <v/>
+      </c>
+      <c r="V38" s="31" t="inlineStr"/>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="B39" s="20" t="inlineStr">
@@ -3125,46 +3249,50 @@
         <f>G39-F39</f>
         <v/>
       </c>
-      <c r="I39" s="26">
+      <c r="I39" s="23">
+        <f>ABS(G39-F39)</f>
+        <v/>
+      </c>
+      <c r="J39" s="26">
         <f>IF(F39&gt;0, G39/F39, IF(G39&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J39" s="27">
-        <f>IF(F39=0, IF(G39=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G39-F39)/F39))</f>
-        <v/>
-      </c>
-      <c r="K39" s="28" t="inlineStr"/>
-      <c r="L39" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" s="29" t="n">
+      <c r="K39" s="27">
+        <f>IF(F39&gt;0, 1.0 - (I39/F39), IF(G39=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L39" s="28" t="inlineStr"/>
+      <c r="M39" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="29" t="n">
         <v>5000</v>
       </c>
-      <c r="Q39" s="30" t="n">
+      <c r="R39" s="30" t="n">
         <v>5000</v>
       </c>
-      <c r="R39" s="23">
-        <f>L39+N39+P39</f>
-        <v/>
-      </c>
-      <c r="S39" s="24">
+      <c r="S39" s="23">
         <f>M39+O39+Q39</f>
         <v/>
       </c>
-      <c r="T39" s="25">
-        <f>S39-R39</f>
-        <v/>
-      </c>
-      <c r="U39" s="31" t="inlineStr"/>
+      <c r="T39" s="24">
+        <f>N39+P39+R39</f>
+        <v/>
+      </c>
+      <c r="U39" s="25">
+        <f>T39-S39</f>
+        <v/>
+      </c>
+      <c r="V39" s="31" t="inlineStr"/>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="B40" s="20" t="inlineStr">
@@ -3197,46 +3325,50 @@
         <f>G40-F40</f>
         <v/>
       </c>
-      <c r="I40" s="26">
+      <c r="I40" s="23">
+        <f>ABS(G40-F40)</f>
+        <v/>
+      </c>
+      <c r="J40" s="26">
         <f>IF(F40&gt;0, G40/F40, IF(G40&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J40" s="27">
-        <f>IF(F40=0, IF(G40=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G40-F40)/F40))</f>
-        <v/>
-      </c>
-      <c r="K40" s="28" t="inlineStr"/>
-      <c r="L40" s="29" t="n">
+      <c r="K40" s="27">
+        <f>IF(F40&gt;0, 1.0 - (I40/F40), IF(G40=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L40" s="28" t="inlineStr"/>
+      <c r="M40" s="29" t="n">
         <v>3000</v>
       </c>
-      <c r="M40" s="30" t="n">
+      <c r="N40" s="30" t="n">
         <v>3000</v>
       </c>
-      <c r="N40" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" s="23">
-        <f>L40+N40+P40</f>
-        <v/>
-      </c>
-      <c r="S40" s="24">
+      <c r="O40" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="23">
         <f>M40+O40+Q40</f>
         <v/>
       </c>
-      <c r="T40" s="25">
-        <f>S40-R40</f>
-        <v/>
-      </c>
-      <c r="U40" s="31" t="inlineStr"/>
+      <c r="T40" s="24">
+        <f>N40+P40+R40</f>
+        <v/>
+      </c>
+      <c r="U40" s="25">
+        <f>T40-S40</f>
+        <v/>
+      </c>
+      <c r="V40" s="31" t="inlineStr"/>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="B41" s="20" t="inlineStr">
@@ -3269,46 +3401,50 @@
         <f>G41-F41</f>
         <v/>
       </c>
-      <c r="I41" s="26">
+      <c r="I41" s="23">
+        <f>ABS(G41-F41)</f>
+        <v/>
+      </c>
+      <c r="J41" s="26">
         <f>IF(F41&gt;0, G41/F41, IF(G41&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J41" s="27">
-        <f>IF(F41=0, IF(G41=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G41-F41)/F41))</f>
-        <v/>
-      </c>
-      <c r="K41" s="28" t="inlineStr"/>
-      <c r="L41" s="29" t="n">
+      <c r="K41" s="27">
+        <f>IF(F41&gt;0, 1.0 - (I41/F41), IF(G41=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L41" s="28" t="inlineStr"/>
+      <c r="M41" s="29" t="n">
         <v>2000</v>
       </c>
-      <c r="M41" s="30" t="n">
+      <c r="N41" s="30" t="n">
         <v>2000</v>
       </c>
-      <c r="N41" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" s="23">
-        <f>L41+N41+P41</f>
-        <v/>
-      </c>
-      <c r="S41" s="24">
+      <c r="O41" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" s="23">
         <f>M41+O41+Q41</f>
         <v/>
       </c>
-      <c r="T41" s="25">
-        <f>S41-R41</f>
-        <v/>
-      </c>
-      <c r="U41" s="31" t="inlineStr"/>
+      <c r="T41" s="24">
+        <f>N41+P41+R41</f>
+        <v/>
+      </c>
+      <c r="U41" s="25">
+        <f>T41-S41</f>
+        <v/>
+      </c>
+      <c r="V41" s="31" t="inlineStr"/>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="B42" s="20" t="inlineStr">
@@ -3341,46 +3477,50 @@
         <f>G42-F42</f>
         <v/>
       </c>
-      <c r="I42" s="26">
+      <c r="I42" s="23">
+        <f>ABS(G42-F42)</f>
+        <v/>
+      </c>
+      <c r="J42" s="26">
         <f>IF(F42&gt;0, G42/F42, IF(G42&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J42" s="27">
-        <f>IF(F42=0, IF(G42=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G42-F42)/F42))</f>
-        <v/>
-      </c>
-      <c r="K42" s="28" t="inlineStr"/>
-      <c r="L42" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" s="29" t="n">
+      <c r="K42" s="27">
+        <f>IF(F42&gt;0, 1.0 - (I42/F42), IF(G42=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L42" s="28" t="inlineStr"/>
+      <c r="M42" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="29" t="n">
         <v>20000</v>
       </c>
-      <c r="O42" s="30" t="n">
+      <c r="P42" s="30" t="n">
         <v>20000</v>
       </c>
-      <c r="P42" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" s="23">
-        <f>L42+N42+P42</f>
-        <v/>
-      </c>
-      <c r="S42" s="24">
+      <c r="Q42" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" s="23">
         <f>M42+O42+Q42</f>
         <v/>
       </c>
-      <c r="T42" s="25">
-        <f>S42-R42</f>
-        <v/>
-      </c>
-      <c r="U42" s="31" t="inlineStr"/>
+      <c r="T42" s="24">
+        <f>N42+P42+R42</f>
+        <v/>
+      </c>
+      <c r="U42" s="25">
+        <f>T42-S42</f>
+        <v/>
+      </c>
+      <c r="V42" s="31" t="inlineStr"/>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="B43" s="20" t="inlineStr">
@@ -3413,46 +3553,50 @@
         <f>G43-F43</f>
         <v/>
       </c>
-      <c r="I43" s="26">
+      <c r="I43" s="23">
+        <f>ABS(G43-F43)</f>
+        <v/>
+      </c>
+      <c r="J43" s="26">
         <f>IF(F43&gt;0, G43/F43, IF(G43&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J43" s="27">
-        <f>IF(F43=0, IF(G43=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G43-F43)/F43))</f>
-        <v/>
-      </c>
-      <c r="K43" s="28" t="inlineStr"/>
-      <c r="L43" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" s="29" t="n">
+      <c r="K43" s="27">
+        <f>IF(F43&gt;0, 1.0 - (I43/F43), IF(G43=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L43" s="28" t="inlineStr"/>
+      <c r="M43" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="29" t="n">
         <v>3000</v>
       </c>
-      <c r="Q43" s="30" t="n">
+      <c r="R43" s="30" t="n">
         <v>3000</v>
       </c>
-      <c r="R43" s="23">
-        <f>L43+N43+P43</f>
-        <v/>
-      </c>
-      <c r="S43" s="24">
+      <c r="S43" s="23">
         <f>M43+O43+Q43</f>
         <v/>
       </c>
-      <c r="T43" s="25">
-        <f>S43-R43</f>
-        <v/>
-      </c>
-      <c r="U43" s="31" t="inlineStr"/>
+      <c r="T43" s="24">
+        <f>N43+P43+R43</f>
+        <v/>
+      </c>
+      <c r="U43" s="25">
+        <f>T43-S43</f>
+        <v/>
+      </c>
+      <c r="V43" s="31" t="inlineStr"/>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="B44" s="20" t="inlineStr">
@@ -3485,46 +3629,50 @@
         <f>G44-F44</f>
         <v/>
       </c>
-      <c r="I44" s="26">
+      <c r="I44" s="23">
+        <f>ABS(G44-F44)</f>
+        <v/>
+      </c>
+      <c r="J44" s="26">
         <f>IF(F44&gt;0, G44/F44, IF(G44&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J44" s="27">
-        <f>IF(F44=0, IF(G44=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G44-F44)/F44))</f>
-        <v/>
-      </c>
-      <c r="K44" s="28" t="inlineStr"/>
-      <c r="L44" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" s="29" t="n">
+      <c r="K44" s="27">
+        <f>IF(F44&gt;0, 1.0 - (I44/F44), IF(G44=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L44" s="28" t="inlineStr"/>
+      <c r="M44" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="29" t="n">
         <v>7920</v>
       </c>
-      <c r="O44" s="30" t="n">
+      <c r="P44" s="30" t="n">
         <v>7920</v>
       </c>
-      <c r="P44" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" s="23">
-        <f>L44+N44+P44</f>
-        <v/>
-      </c>
-      <c r="S44" s="24">
+      <c r="Q44" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" s="23">
         <f>M44+O44+Q44</f>
         <v/>
       </c>
-      <c r="T44" s="25">
-        <f>S44-R44</f>
-        <v/>
-      </c>
-      <c r="U44" s="31" t="inlineStr"/>
+      <c r="T44" s="24">
+        <f>N44+P44+R44</f>
+        <v/>
+      </c>
+      <c r="U44" s="25">
+        <f>T44-S44</f>
+        <v/>
+      </c>
+      <c r="V44" s="31" t="inlineStr"/>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="B45" s="20" t="inlineStr">
@@ -3557,46 +3705,50 @@
         <f>G45-F45</f>
         <v/>
       </c>
-      <c r="I45" s="26">
+      <c r="I45" s="23">
+        <f>ABS(G45-F45)</f>
+        <v/>
+      </c>
+      <c r="J45" s="26">
         <f>IF(F45&gt;0, G45/F45, IF(G45&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J45" s="27">
-        <f>IF(F45=0, IF(G45=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G45-F45)/F45))</f>
-        <v/>
-      </c>
-      <c r="K45" s="28" t="inlineStr"/>
-      <c r="L45" s="29" t="n">
+      <c r="K45" s="27">
+        <f>IF(F45&gt;0, 1.0 - (I45/F45), IF(G45=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L45" s="28" t="inlineStr"/>
+      <c r="M45" s="29" t="n">
         <v>5000</v>
       </c>
-      <c r="M45" s="30" t="n">
+      <c r="N45" s="30" t="n">
         <v>5000</v>
       </c>
-      <c r="N45" s="29" t="n">
+      <c r="O45" s="29" t="n">
         <v>10000</v>
       </c>
-      <c r="O45" s="30" t="n">
+      <c r="P45" s="30" t="n">
         <v>10000</v>
       </c>
-      <c r="P45" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" s="23">
-        <f>L45+N45+P45</f>
-        <v/>
-      </c>
-      <c r="S45" s="24">
+      <c r="Q45" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" s="23">
         <f>M45+O45+Q45</f>
         <v/>
       </c>
-      <c r="T45" s="25">
-        <f>S45-R45</f>
-        <v/>
-      </c>
-      <c r="U45" s="31" t="inlineStr"/>
+      <c r="T45" s="24">
+        <f>N45+P45+R45</f>
+        <v/>
+      </c>
+      <c r="U45" s="25">
+        <f>T45-S45</f>
+        <v/>
+      </c>
+      <c r="V45" s="31" t="inlineStr"/>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="B46" s="20" t="inlineStr">
@@ -3629,46 +3781,50 @@
         <f>G46-F46</f>
         <v/>
       </c>
-      <c r="I46" s="26">
+      <c r="I46" s="23">
+        <f>ABS(G46-F46)</f>
+        <v/>
+      </c>
+      <c r="J46" s="26">
         <f>IF(F46&gt;0, G46/F46, IF(G46&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J46" s="27">
-        <f>IF(F46=0, IF(G46=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G46-F46)/F46))</f>
-        <v/>
-      </c>
-      <c r="K46" s="28" t="inlineStr"/>
-      <c r="L46" s="29" t="n">
+      <c r="K46" s="27">
+        <f>IF(F46&gt;0, 1.0 - (I46/F46), IF(G46=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L46" s="28" t="inlineStr"/>
+      <c r="M46" s="29" t="n">
         <v>20000</v>
       </c>
-      <c r="M46" s="30" t="n">
+      <c r="N46" s="30" t="n">
         <v>20000</v>
       </c>
-      <c r="N46" s="29" t="n">
+      <c r="O46" s="29" t="n">
         <v>30000</v>
       </c>
-      <c r="O46" s="30" t="n">
+      <c r="P46" s="30" t="n">
         <v>30000</v>
       </c>
-      <c r="P46" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" s="23">
-        <f>L46+N46+P46</f>
-        <v/>
-      </c>
-      <c r="S46" s="24">
+      <c r="Q46" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" s="23">
         <f>M46+O46+Q46</f>
         <v/>
       </c>
-      <c r="T46" s="25">
-        <f>S46-R46</f>
-        <v/>
-      </c>
-      <c r="U46" s="31" t="inlineStr"/>
+      <c r="T46" s="24">
+        <f>N46+P46+R46</f>
+        <v/>
+      </c>
+      <c r="U46" s="25">
+        <f>T46-S46</f>
+        <v/>
+      </c>
+      <c r="V46" s="31" t="inlineStr"/>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="B47" s="20" t="inlineStr">
@@ -3701,46 +3857,50 @@
         <f>G47-F47</f>
         <v/>
       </c>
-      <c r="I47" s="26">
+      <c r="I47" s="23">
+        <f>ABS(G47-F47)</f>
+        <v/>
+      </c>
+      <c r="J47" s="26">
         <f>IF(F47&gt;0, G47/F47, IF(G47&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J47" s="27">
-        <f>IF(F47=0, IF(G47=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G47-F47)/F47))</f>
-        <v/>
-      </c>
-      <c r="K47" s="28" t="inlineStr"/>
-      <c r="L47" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" s="29" t="n">
+      <c r="K47" s="27">
+        <f>IF(F47&gt;0, 1.0 - (I47/F47), IF(G47=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L47" s="28" t="inlineStr"/>
+      <c r="M47" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="29" t="n">
         <v>10000</v>
       </c>
-      <c r="O47" s="30" t="n">
+      <c r="P47" s="30" t="n">
         <v>10000</v>
       </c>
-      <c r="P47" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" s="23">
-        <f>L47+N47+P47</f>
-        <v/>
-      </c>
-      <c r="S47" s="24">
+      <c r="Q47" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" s="23">
         <f>M47+O47+Q47</f>
         <v/>
       </c>
-      <c r="T47" s="25">
-        <f>S47-R47</f>
-        <v/>
-      </c>
-      <c r="U47" s="31" t="inlineStr"/>
+      <c r="T47" s="24">
+        <f>N47+P47+R47</f>
+        <v/>
+      </c>
+      <c r="U47" s="25">
+        <f>T47-S47</f>
+        <v/>
+      </c>
+      <c r="V47" s="31" t="inlineStr"/>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="B48" s="20" t="inlineStr">
@@ -3773,50 +3933,54 @@
         <f>G48-F48</f>
         <v/>
       </c>
-      <c r="I48" s="26">
+      <c r="I48" s="23">
+        <f>ABS(G48-F48)</f>
+        <v/>
+      </c>
+      <c r="J48" s="26">
         <f>IF(F48&gt;0, G48/F48, IF(G48&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J48" s="27">
-        <f>IF(F48=0, IF(G48=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G48-F48)/F48))</f>
-        <v/>
-      </c>
-      <c r="K48" s="28" t="inlineStr">
+      <c r="K48" s="27">
+        <f>IF(F48&gt;0, 1.0 - (I48/F48), IF(G48=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L48" s="28" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
       </c>
-      <c r="L48" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" s="23">
-        <f>L48+N48+P48</f>
-        <v/>
-      </c>
-      <c r="S48" s="24">
+      <c r="M48" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" s="23">
         <f>M48+O48+Q48</f>
         <v/>
       </c>
-      <c r="T48" s="25">
-        <f>S48-R48</f>
-        <v/>
-      </c>
-      <c r="U48" s="31" t="inlineStr"/>
+      <c r="T48" s="24">
+        <f>N48+P48+R48</f>
+        <v/>
+      </c>
+      <c r="U48" s="25">
+        <f>T48-S48</f>
+        <v/>
+      </c>
+      <c r="V48" s="31" t="inlineStr"/>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="B49" s="20" t="inlineStr">
@@ -3849,50 +4013,54 @@
         <f>G49-F49</f>
         <v/>
       </c>
-      <c r="I49" s="26">
+      <c r="I49" s="23">
+        <f>ABS(G49-F49)</f>
+        <v/>
+      </c>
+      <c r="J49" s="26">
         <f>IF(F49&gt;0, G49/F49, IF(G49&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J49" s="27">
-        <f>IF(F49=0, IF(G49=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G49-F49)/F49))</f>
-        <v/>
-      </c>
-      <c r="K49" s="28" t="inlineStr">
+      <c r="K49" s="27">
+        <f>IF(F49&gt;0, 1.0 - (I49/F49), IF(G49=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L49" s="28" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
       </c>
-      <c r="L49" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" s="23">
-        <f>L49+N49+P49</f>
-        <v/>
-      </c>
-      <c r="S49" s="24">
+      <c r="M49" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" s="23">
         <f>M49+O49+Q49</f>
         <v/>
       </c>
-      <c r="T49" s="25">
-        <f>S49-R49</f>
-        <v/>
-      </c>
-      <c r="U49" s="31" t="inlineStr"/>
+      <c r="T49" s="24">
+        <f>N49+P49+R49</f>
+        <v/>
+      </c>
+      <c r="U49" s="25">
+        <f>T49-S49</f>
+        <v/>
+      </c>
+      <c r="V49" s="31" t="inlineStr"/>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="B50" s="20" t="inlineStr">
@@ -3925,50 +4093,54 @@
         <f>G50-F50</f>
         <v/>
       </c>
-      <c r="I50" s="26">
+      <c r="I50" s="23">
+        <f>ABS(G50-F50)</f>
+        <v/>
+      </c>
+      <c r="J50" s="26">
         <f>IF(F50&gt;0, G50/F50, IF(G50&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J50" s="27">
-        <f>IF(F50=0, IF(G50=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G50-F50)/F50))</f>
-        <v/>
-      </c>
-      <c r="K50" s="28" t="inlineStr">
+      <c r="K50" s="27">
+        <f>IF(F50&gt;0, 1.0 - (I50/F50), IF(G50=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L50" s="28" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
       </c>
-      <c r="L50" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" s="23">
-        <f>L50+N50+P50</f>
-        <v/>
-      </c>
-      <c r="S50" s="24">
+      <c r="M50" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" s="23">
         <f>M50+O50+Q50</f>
         <v/>
       </c>
-      <c r="T50" s="25">
-        <f>S50-R50</f>
-        <v/>
-      </c>
-      <c r="U50" s="31" t="inlineStr"/>
+      <c r="T50" s="24">
+        <f>N50+P50+R50</f>
+        <v/>
+      </c>
+      <c r="U50" s="25">
+        <f>T50-S50</f>
+        <v/>
+      </c>
+      <c r="V50" s="31" t="inlineStr"/>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="B51" s="20" t="inlineStr">
@@ -4001,50 +4173,54 @@
         <f>G51-F51</f>
         <v/>
       </c>
-      <c r="I51" s="26">
+      <c r="I51" s="23">
+        <f>ABS(G51-F51)</f>
+        <v/>
+      </c>
+      <c r="J51" s="26">
         <f>IF(F51&gt;0, G51/F51, IF(G51&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J51" s="27">
-        <f>IF(F51=0, IF(G51=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G51-F51)/F51))</f>
-        <v/>
-      </c>
-      <c r="K51" s="28" t="inlineStr">
+      <c r="K51" s="27">
+        <f>IF(F51&gt;0, 1.0 - (I51/F51), IF(G51=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L51" s="28" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
       </c>
-      <c r="L51" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" s="23">
-        <f>L51+N51+P51</f>
-        <v/>
-      </c>
-      <c r="S51" s="24">
+      <c r="M51" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" s="23">
         <f>M51+O51+Q51</f>
         <v/>
       </c>
-      <c r="T51" s="25">
-        <f>S51-R51</f>
-        <v/>
-      </c>
-      <c r="U51" s="31" t="inlineStr"/>
+      <c r="T51" s="24">
+        <f>N51+P51+R51</f>
+        <v/>
+      </c>
+      <c r="U51" s="25">
+        <f>T51-S51</f>
+        <v/>
+      </c>
+      <c r="V51" s="31" t="inlineStr"/>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="B52" s="20" t="inlineStr">
@@ -4077,50 +4253,54 @@
         <f>G52-F52</f>
         <v/>
       </c>
-      <c r="I52" s="26">
+      <c r="I52" s="23">
+        <f>ABS(G52-F52)</f>
+        <v/>
+      </c>
+      <c r="J52" s="26">
         <f>IF(F52&gt;0, G52/F52, IF(G52&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J52" s="27">
-        <f>IF(F52=0, IF(G52=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G52-F52)/F52))</f>
-        <v/>
-      </c>
-      <c r="K52" s="28" t="inlineStr">
+      <c r="K52" s="27">
+        <f>IF(F52&gt;0, 1.0 - (I52/F52), IF(G52=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L52" s="28" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
       </c>
-      <c r="L52" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" s="23">
-        <f>L52+N52+P52</f>
-        <v/>
-      </c>
-      <c r="S52" s="24">
+      <c r="M52" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" s="23">
         <f>M52+O52+Q52</f>
         <v/>
       </c>
-      <c r="T52" s="25">
-        <f>S52-R52</f>
-        <v/>
-      </c>
-      <c r="U52" s="31" t="inlineStr"/>
+      <c r="T52" s="24">
+        <f>N52+P52+R52</f>
+        <v/>
+      </c>
+      <c r="U52" s="25">
+        <f>T52-S52</f>
+        <v/>
+      </c>
+      <c r="V52" s="31" t="inlineStr"/>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="B53" s="20" t="inlineStr">
@@ -4153,46 +4333,50 @@
         <f>G53-F53</f>
         <v/>
       </c>
-      <c r="I53" s="26">
+      <c r="I53" s="23">
+        <f>ABS(G53-F53)</f>
+        <v/>
+      </c>
+      <c r="J53" s="26">
         <f>IF(F53&gt;0, G53/F53, IF(G53&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J53" s="27">
-        <f>IF(F53=0, IF(G53=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G53-F53)/F53))</f>
-        <v/>
-      </c>
-      <c r="K53" s="28" t="inlineStr"/>
-      <c r="L53" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" s="29" t="n">
+      <c r="K53" s="27">
+        <f>IF(F53&gt;0, 1.0 - (I53/F53), IF(G53=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L53" s="28" t="inlineStr"/>
+      <c r="M53" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="29" t="n">
         <v>640</v>
       </c>
-      <c r="Q53" s="30" t="n">
+      <c r="R53" s="30" t="n">
         <v>640</v>
       </c>
-      <c r="R53" s="23">
-        <f>L53+N53+P53</f>
-        <v/>
-      </c>
-      <c r="S53" s="24">
+      <c r="S53" s="23">
         <f>M53+O53+Q53</f>
         <v/>
       </c>
-      <c r="T53" s="25">
-        <f>S53-R53</f>
-        <v/>
-      </c>
-      <c r="U53" s="31" t="inlineStr"/>
+      <c r="T53" s="24">
+        <f>N53+P53+R53</f>
+        <v/>
+      </c>
+      <c r="U53" s="25">
+        <f>T53-S53</f>
+        <v/>
+      </c>
+      <c r="V53" s="31" t="inlineStr"/>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="B54" s="20" t="inlineStr">
@@ -4225,50 +4409,54 @@
         <f>G54-F54</f>
         <v/>
       </c>
-      <c r="I54" s="26">
+      <c r="I54" s="23">
+        <f>ABS(G54-F54)</f>
+        <v/>
+      </c>
+      <c r="J54" s="26">
         <f>IF(F54&gt;0, G54/F54, IF(G54&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J54" s="27">
-        <f>IF(F54=0, IF(G54=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G54-F54)/F54))</f>
-        <v/>
-      </c>
-      <c r="K54" s="28" t="inlineStr">
+      <c r="K54" s="27">
+        <f>IF(F54&gt;0, 1.0 - (I54/F54), IF(G54=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L54" s="28" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
       </c>
-      <c r="L54" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" s="23">
-        <f>L54+N54+P54</f>
-        <v/>
-      </c>
-      <c r="S54" s="24">
+      <c r="M54" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" s="23">
         <f>M54+O54+Q54</f>
         <v/>
       </c>
-      <c r="T54" s="25">
-        <f>S54-R54</f>
-        <v/>
-      </c>
-      <c r="U54" s="31" t="inlineStr"/>
+      <c r="T54" s="24">
+        <f>N54+P54+R54</f>
+        <v/>
+      </c>
+      <c r="U54" s="25">
+        <f>T54-S54</f>
+        <v/>
+      </c>
+      <c r="V54" s="31" t="inlineStr"/>
     </row>
     <row r="55" ht="20" customHeight="1">
       <c r="B55" s="20" t="inlineStr">
@@ -4301,46 +4489,50 @@
         <f>G55-F55</f>
         <v/>
       </c>
-      <c r="I55" s="26">
+      <c r="I55" s="23">
+        <f>ABS(G55-F55)</f>
+        <v/>
+      </c>
+      <c r="J55" s="26">
         <f>IF(F55&gt;0, G55/F55, IF(G55&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J55" s="27">
-        <f>IF(F55=0, IF(G55=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G55-F55)/F55))</f>
-        <v/>
-      </c>
-      <c r="K55" s="28" t="inlineStr"/>
-      <c r="L55" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" s="29" t="n">
+      <c r="K55" s="27">
+        <f>IF(F55&gt;0, 1.0 - (I55/F55), IF(G55=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L55" s="28" t="inlineStr"/>
+      <c r="M55" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="29" t="n">
         <v>8000</v>
       </c>
-      <c r="Q55" s="30" t="n">
+      <c r="R55" s="30" t="n">
         <v>8000</v>
       </c>
-      <c r="R55" s="23">
-        <f>L55+N55+P55</f>
-        <v/>
-      </c>
-      <c r="S55" s="24">
+      <c r="S55" s="23">
         <f>M55+O55+Q55</f>
         <v/>
       </c>
-      <c r="T55" s="25">
-        <f>S55-R55</f>
-        <v/>
-      </c>
-      <c r="U55" s="31" t="inlineStr"/>
+      <c r="T55" s="24">
+        <f>N55+P55+R55</f>
+        <v/>
+      </c>
+      <c r="U55" s="25">
+        <f>T55-S55</f>
+        <v/>
+      </c>
+      <c r="V55" s="31" t="inlineStr"/>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="B56" s="20" t="inlineStr">
@@ -4373,46 +4565,50 @@
         <f>G56-F56</f>
         <v/>
       </c>
-      <c r="I56" s="26">
+      <c r="I56" s="23">
+        <f>ABS(G56-F56)</f>
+        <v/>
+      </c>
+      <c r="J56" s="26">
         <f>IF(F56&gt;0, G56/F56, IF(G56&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J56" s="27">
-        <f>IF(F56=0, IF(G56=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G56-F56)/F56))</f>
-        <v/>
-      </c>
-      <c r="K56" s="28" t="inlineStr"/>
-      <c r="L56" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" s="29" t="n">
+      <c r="K56" s="27">
+        <f>IF(F56&gt;0, 1.0 - (I56/F56), IF(G56=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L56" s="28" t="inlineStr"/>
+      <c r="M56" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="29" t="n">
         <v>4000</v>
       </c>
-      <c r="Q56" s="30" t="n">
+      <c r="R56" s="30" t="n">
         <v>4000</v>
       </c>
-      <c r="R56" s="23">
-        <f>L56+N56+P56</f>
-        <v/>
-      </c>
-      <c r="S56" s="24">
+      <c r="S56" s="23">
         <f>M56+O56+Q56</f>
         <v/>
       </c>
-      <c r="T56" s="25">
-        <f>S56-R56</f>
-        <v/>
-      </c>
-      <c r="U56" s="31" t="inlineStr"/>
+      <c r="T56" s="24">
+        <f>N56+P56+R56</f>
+        <v/>
+      </c>
+      <c r="U56" s="25">
+        <f>T56-S56</f>
+        <v/>
+      </c>
+      <c r="V56" s="31" t="inlineStr"/>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="B57" s="20" t="inlineStr">
@@ -4445,46 +4641,50 @@
         <f>G57-F57</f>
         <v/>
       </c>
-      <c r="I57" s="26">
+      <c r="I57" s="23">
+        <f>ABS(G57-F57)</f>
+        <v/>
+      </c>
+      <c r="J57" s="26">
         <f>IF(F57&gt;0, G57/F57, IF(G57&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J57" s="27">
-        <f>IF(F57=0, IF(G57=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G57-F57)/F57))</f>
-        <v/>
-      </c>
-      <c r="K57" s="28" t="inlineStr"/>
-      <c r="L57" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" s="29" t="n">
+      <c r="K57" s="27">
+        <f>IF(F57&gt;0, 1.0 - (I57/F57), IF(G57=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L57" s="28" t="inlineStr"/>
+      <c r="M57" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="29" t="n">
         <v>10000</v>
       </c>
-      <c r="Q57" s="30" t="n">
+      <c r="R57" s="30" t="n">
         <v>10000</v>
       </c>
-      <c r="R57" s="23">
-        <f>L57+N57+P57</f>
-        <v/>
-      </c>
-      <c r="S57" s="24">
+      <c r="S57" s="23">
         <f>M57+O57+Q57</f>
         <v/>
       </c>
-      <c r="T57" s="25">
-        <f>S57-R57</f>
-        <v/>
-      </c>
-      <c r="U57" s="31" t="inlineStr"/>
+      <c r="T57" s="24">
+        <f>N57+P57+R57</f>
+        <v/>
+      </c>
+      <c r="U57" s="25">
+        <f>T57-S57</f>
+        <v/>
+      </c>
+      <c r="V57" s="31" t="inlineStr"/>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="B58" s="20" t="inlineStr">
@@ -4517,46 +4717,50 @@
         <f>G58-F58</f>
         <v/>
       </c>
-      <c r="I58" s="26">
+      <c r="I58" s="23">
+        <f>ABS(G58-F58)</f>
+        <v/>
+      </c>
+      <c r="J58" s="26">
         <f>IF(F58&gt;0, G58/F58, IF(G58&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J58" s="27">
-        <f>IF(F58=0, IF(G58=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G58-F58)/F58))</f>
-        <v/>
-      </c>
-      <c r="K58" s="28" t="inlineStr"/>
-      <c r="L58" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" s="29" t="n">
+      <c r="K58" s="27">
+        <f>IF(F58&gt;0, 1.0 - (I58/F58), IF(G58=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L58" s="28" t="inlineStr"/>
+      <c r="M58" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="29" t="n">
         <v>10000</v>
       </c>
-      <c r="Q58" s="30" t="n">
+      <c r="R58" s="30" t="n">
         <v>10000</v>
       </c>
-      <c r="R58" s="23">
-        <f>L58+N58+P58</f>
-        <v/>
-      </c>
-      <c r="S58" s="24">
+      <c r="S58" s="23">
         <f>M58+O58+Q58</f>
         <v/>
       </c>
-      <c r="T58" s="25">
-        <f>S58-R58</f>
-        <v/>
-      </c>
-      <c r="U58" s="31" t="inlineStr"/>
+      <c r="T58" s="24">
+        <f>N58+P58+R58</f>
+        <v/>
+      </c>
+      <c r="U58" s="25">
+        <f>T58-S58</f>
+        <v/>
+      </c>
+      <c r="V58" s="31" t="inlineStr"/>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="B59" s="20" t="inlineStr">
@@ -4589,46 +4793,50 @@
         <f>G59-F59</f>
         <v/>
       </c>
-      <c r="I59" s="26">
+      <c r="I59" s="23">
+        <f>ABS(G59-F59)</f>
+        <v/>
+      </c>
+      <c r="J59" s="26">
         <f>IF(F59&gt;0, G59/F59, IF(G59&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J59" s="27">
-        <f>IF(F59=0, IF(G59=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G59-F59)/F59))</f>
-        <v/>
-      </c>
-      <c r="K59" s="28" t="inlineStr"/>
-      <c r="L59" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" s="29" t="n">
+      <c r="K59" s="27">
+        <f>IF(F59&gt;0, 1.0 - (I59/F59), IF(G59=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L59" s="28" t="inlineStr"/>
+      <c r="M59" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="29" t="n">
         <v>2000</v>
       </c>
-      <c r="Q59" s="30" t="n">
+      <c r="R59" s="30" t="n">
         <v>2000</v>
       </c>
-      <c r="R59" s="23">
-        <f>L59+N59+P59</f>
-        <v/>
-      </c>
-      <c r="S59" s="24">
+      <c r="S59" s="23">
         <f>M59+O59+Q59</f>
         <v/>
       </c>
-      <c r="T59" s="25">
-        <f>S59-R59</f>
-        <v/>
-      </c>
-      <c r="U59" s="31" t="inlineStr"/>
+      <c r="T59" s="24">
+        <f>N59+P59+R59</f>
+        <v/>
+      </c>
+      <c r="U59" s="25">
+        <f>T59-S59</f>
+        <v/>
+      </c>
+      <c r="V59" s="31" t="inlineStr"/>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="B60" s="20" t="inlineStr">
@@ -4661,46 +4869,50 @@
         <f>G60-F60</f>
         <v/>
       </c>
-      <c r="I60" s="26">
+      <c r="I60" s="23">
+        <f>ABS(G60-F60)</f>
+        <v/>
+      </c>
+      <c r="J60" s="26">
         <f>IF(F60&gt;0, G60/F60, IF(G60&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J60" s="27">
-        <f>IF(F60=0, IF(G60=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G60-F60)/F60))</f>
-        <v/>
-      </c>
-      <c r="K60" s="28" t="inlineStr"/>
-      <c r="L60" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" s="29" t="n">
+      <c r="K60" s="27">
+        <f>IF(F60&gt;0, 1.0 - (I60/F60), IF(G60=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L60" s="28" t="inlineStr"/>
+      <c r="M60" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="29" t="n">
         <v>1280</v>
       </c>
-      <c r="Q60" s="30" t="n">
+      <c r="R60" s="30" t="n">
         <v>1280</v>
       </c>
-      <c r="R60" s="23">
-        <f>L60+N60+P60</f>
-        <v/>
-      </c>
-      <c r="S60" s="24">
+      <c r="S60" s="23">
         <f>M60+O60+Q60</f>
         <v/>
       </c>
-      <c r="T60" s="25">
-        <f>S60-R60</f>
-        <v/>
-      </c>
-      <c r="U60" s="31" t="inlineStr"/>
+      <c r="T60" s="24">
+        <f>N60+P60+R60</f>
+        <v/>
+      </c>
+      <c r="U60" s="25">
+        <f>T60-S60</f>
+        <v/>
+      </c>
+      <c r="V60" s="31" t="inlineStr"/>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="B61" s="20" t="inlineStr">
@@ -4733,46 +4945,50 @@
         <f>G61-F61</f>
         <v/>
       </c>
-      <c r="I61" s="26">
+      <c r="I61" s="23">
+        <f>ABS(G61-F61)</f>
+        <v/>
+      </c>
+      <c r="J61" s="26">
         <f>IF(F61&gt;0, G61/F61, IF(G61&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J61" s="27">
-        <f>IF(F61=0, IF(G61=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G61-F61)/F61))</f>
-        <v/>
-      </c>
-      <c r="K61" s="28" t="inlineStr"/>
-      <c r="L61" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" s="29" t="n">
+      <c r="K61" s="27">
+        <f>IF(F61&gt;0, 1.0 - (I61/F61), IF(G61=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L61" s="28" t="inlineStr"/>
+      <c r="M61" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="29" t="n">
         <v>25</v>
       </c>
-      <c r="Q61" s="30" t="n">
+      <c r="R61" s="30" t="n">
         <v>25</v>
       </c>
-      <c r="R61" s="23">
-        <f>L61+N61+P61</f>
-        <v/>
-      </c>
-      <c r="S61" s="24">
+      <c r="S61" s="23">
         <f>M61+O61+Q61</f>
         <v/>
       </c>
-      <c r="T61" s="25">
-        <f>S61-R61</f>
-        <v/>
-      </c>
-      <c r="U61" s="31" t="inlineStr"/>
+      <c r="T61" s="24">
+        <f>N61+P61+R61</f>
+        <v/>
+      </c>
+      <c r="U61" s="25">
+        <f>T61-S61</f>
+        <v/>
+      </c>
+      <c r="V61" s="31" t="inlineStr"/>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="B62" s="20" t="inlineStr">
@@ -4805,46 +5021,50 @@
         <f>G62-F62</f>
         <v/>
       </c>
-      <c r="I62" s="26">
+      <c r="I62" s="23">
+        <f>ABS(G62-F62)</f>
+        <v/>
+      </c>
+      <c r="J62" s="26">
         <f>IF(F62&gt;0, G62/F62, IF(G62&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J62" s="27">
-        <f>IF(F62=0, IF(G62=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G62-F62)/F62))</f>
-        <v/>
-      </c>
-      <c r="K62" s="28" t="inlineStr"/>
-      <c r="L62" s="29" t="n">
+      <c r="K62" s="27">
+        <f>IF(F62&gt;0, 1.0 - (I62/F62), IF(G62=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L62" s="28" t="inlineStr"/>
+      <c r="M62" s="29" t="n">
         <v>1920</v>
       </c>
-      <c r="M62" s="30" t="n">
+      <c r="N62" s="30" t="n">
         <v>1920</v>
       </c>
-      <c r="N62" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" s="23">
-        <f>L62+N62+P62</f>
-        <v/>
-      </c>
-      <c r="S62" s="24">
+      <c r="O62" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" s="23">
         <f>M62+O62+Q62</f>
         <v/>
       </c>
-      <c r="T62" s="25">
-        <f>S62-R62</f>
-        <v/>
-      </c>
-      <c r="U62" s="31" t="inlineStr"/>
+      <c r="T62" s="24">
+        <f>N62+P62+R62</f>
+        <v/>
+      </c>
+      <c r="U62" s="25">
+        <f>T62-S62</f>
+        <v/>
+      </c>
+      <c r="V62" s="31" t="inlineStr"/>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="B63" s="20" t="inlineStr">
@@ -4877,46 +5097,50 @@
         <f>G63-F63</f>
         <v/>
       </c>
-      <c r="I63" s="26">
+      <c r="I63" s="23">
+        <f>ABS(G63-F63)</f>
+        <v/>
+      </c>
+      <c r="J63" s="26">
         <f>IF(F63&gt;0, G63/F63, IF(G63&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J63" s="27">
-        <f>IF(F63=0, IF(G63=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G63-F63)/F63))</f>
-        <v/>
-      </c>
-      <c r="K63" s="28" t="inlineStr"/>
-      <c r="L63" s="29" t="n">
+      <c r="K63" s="27">
+        <f>IF(F63&gt;0, 1.0 - (I63/F63), IF(G63=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L63" s="28" t="inlineStr"/>
+      <c r="M63" s="29" t="n">
         <v>75</v>
       </c>
-      <c r="M63" s="30" t="n">
+      <c r="N63" s="30" t="n">
         <v>75</v>
       </c>
-      <c r="N63" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" s="23">
-        <f>L63+N63+P63</f>
-        <v/>
-      </c>
-      <c r="S63" s="24">
+      <c r="O63" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" s="23">
         <f>M63+O63+Q63</f>
         <v/>
       </c>
-      <c r="T63" s="25">
-        <f>S63-R63</f>
-        <v/>
-      </c>
-      <c r="U63" s="31" t="inlineStr"/>
+      <c r="T63" s="24">
+        <f>N63+P63+R63</f>
+        <v/>
+      </c>
+      <c r="U63" s="25">
+        <f>T63-S63</f>
+        <v/>
+      </c>
+      <c r="V63" s="31" t="inlineStr"/>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="B64" s="20" t="inlineStr">
@@ -4949,46 +5173,50 @@
         <f>G64-F64</f>
         <v/>
       </c>
-      <c r="I64" s="26">
+      <c r="I64" s="23">
+        <f>ABS(G64-F64)</f>
+        <v/>
+      </c>
+      <c r="J64" s="26">
         <f>IF(F64&gt;0, G64/F64, IF(G64&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J64" s="27">
-        <f>IF(F64=0, IF(G64=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G64-F64)/F64))</f>
-        <v/>
-      </c>
-      <c r="K64" s="28" t="inlineStr"/>
-      <c r="L64" s="29" t="n">
+      <c r="K64" s="27">
+        <f>IF(F64&gt;0, 1.0 - (I64/F64), IF(G64=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L64" s="28" t="inlineStr"/>
+      <c r="M64" s="29" t="n">
         <v>80</v>
       </c>
-      <c r="M64" s="30" t="n">
+      <c r="N64" s="30" t="n">
         <v>80</v>
       </c>
-      <c r="N64" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" s="29" t="n">
+      <c r="O64" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="29" t="n">
         <v>240</v>
       </c>
-      <c r="Q64" s="30" t="n">
+      <c r="R64" s="30" t="n">
         <v>240</v>
       </c>
-      <c r="R64" s="23">
-        <f>L64+N64+P64</f>
-        <v/>
-      </c>
-      <c r="S64" s="24">
+      <c r="S64" s="23">
         <f>M64+O64+Q64</f>
         <v/>
       </c>
-      <c r="T64" s="25">
-        <f>S64-R64</f>
-        <v/>
-      </c>
-      <c r="U64" s="31" t="inlineStr"/>
+      <c r="T64" s="24">
+        <f>N64+P64+R64</f>
+        <v/>
+      </c>
+      <c r="U64" s="25">
+        <f>T64-S64</f>
+        <v/>
+      </c>
+      <c r="V64" s="31" t="inlineStr"/>
     </row>
     <row r="65" ht="20" customHeight="1">
       <c r="B65" s="20" t="inlineStr">
@@ -5021,46 +5249,50 @@
         <f>G65-F65</f>
         <v/>
       </c>
-      <c r="I65" s="26">
+      <c r="I65" s="23">
+        <f>ABS(G65-F65)</f>
+        <v/>
+      </c>
+      <c r="J65" s="26">
         <f>IF(F65&gt;0, G65/F65, IF(G65&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J65" s="27">
-        <f>IF(F65=0, IF(G65=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G65-F65)/F65))</f>
-        <v/>
-      </c>
-      <c r="K65" s="28" t="inlineStr"/>
-      <c r="L65" s="29" t="n">
+      <c r="K65" s="27">
+        <f>IF(F65&gt;0, 1.0 - (I65/F65), IF(G65=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L65" s="28" t="inlineStr"/>
+      <c r="M65" s="29" t="n">
         <v>800</v>
       </c>
-      <c r="M65" s="30" t="n">
+      <c r="N65" s="30" t="n">
         <v>800</v>
       </c>
-      <c r="N65" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" s="23">
-        <f>L65+N65+P65</f>
-        <v/>
-      </c>
-      <c r="S65" s="24">
+      <c r="O65" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" s="23">
         <f>M65+O65+Q65</f>
         <v/>
       </c>
-      <c r="T65" s="25">
-        <f>S65-R65</f>
-        <v/>
-      </c>
-      <c r="U65" s="31" t="inlineStr"/>
+      <c r="T65" s="24">
+        <f>N65+P65+R65</f>
+        <v/>
+      </c>
+      <c r="U65" s="25">
+        <f>T65-S65</f>
+        <v/>
+      </c>
+      <c r="V65" s="31" t="inlineStr"/>
     </row>
     <row r="66" ht="20" customHeight="1">
       <c r="B66" s="20" t="inlineStr">
@@ -5093,50 +5325,54 @@
         <f>G66-F66</f>
         <v/>
       </c>
-      <c r="I66" s="26">
+      <c r="I66" s="23">
+        <f>ABS(G66-F66)</f>
+        <v/>
+      </c>
+      <c r="J66" s="26">
         <f>IF(F66&gt;0, G66/F66, IF(G66&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J66" s="27">
-        <f>IF(F66=0, IF(G66=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G66-F66)/F66))</f>
-        <v/>
-      </c>
-      <c r="K66" s="28" t="inlineStr">
+      <c r="K66" s="27">
+        <f>IF(F66&gt;0, 1.0 - (I66/F66), IF(G66=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L66" s="28" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
       </c>
-      <c r="L66" s="29" t="n">
+      <c r="M66" s="29" t="n">
         <v>1056</v>
       </c>
-      <c r="M66" s="30" t="n">
+      <c r="N66" s="30" t="n">
         <v>1056</v>
       </c>
-      <c r="N66" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R66" s="23">
-        <f>L66+N66+P66</f>
-        <v/>
-      </c>
-      <c r="S66" s="24">
+      <c r="O66" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" s="23">
         <f>M66+O66+Q66</f>
         <v/>
       </c>
-      <c r="T66" s="25">
-        <f>S66-R66</f>
-        <v/>
-      </c>
-      <c r="U66" s="31" t="inlineStr"/>
+      <c r="T66" s="24">
+        <f>N66+P66+R66</f>
+        <v/>
+      </c>
+      <c r="U66" s="25">
+        <f>T66-S66</f>
+        <v/>
+      </c>
+      <c r="V66" s="31" t="inlineStr"/>
     </row>
     <row r="67" ht="20" customHeight="1">
       <c r="B67" s="20" t="inlineStr">
@@ -5169,50 +5405,54 @@
         <f>G67-F67</f>
         <v/>
       </c>
-      <c r="I67" s="26">
+      <c r="I67" s="23">
+        <f>ABS(G67-F67)</f>
+        <v/>
+      </c>
+      <c r="J67" s="26">
         <f>IF(F67&gt;0, G67/F67, IF(G67&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J67" s="27">
-        <f>IF(F67=0, IF(G67=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G67-F67)/F67))</f>
-        <v/>
-      </c>
-      <c r="K67" s="28" t="inlineStr">
+      <c r="K67" s="27">
+        <f>IF(F67&gt;0, 1.0 - (I67/F67), IF(G67=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L67" s="28" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
       </c>
-      <c r="L67" s="29" t="n">
+      <c r="M67" s="29" t="n">
         <v>528</v>
       </c>
-      <c r="M67" s="30" t="n">
+      <c r="N67" s="30" t="n">
         <v>528</v>
       </c>
-      <c r="N67" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O67" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q67" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R67" s="23">
-        <f>L67+N67+P67</f>
-        <v/>
-      </c>
-      <c r="S67" s="24">
+      <c r="O67" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" s="23">
         <f>M67+O67+Q67</f>
         <v/>
       </c>
-      <c r="T67" s="25">
-        <f>S67-R67</f>
-        <v/>
-      </c>
-      <c r="U67" s="31" t="inlineStr"/>
+      <c r="T67" s="24">
+        <f>N67+P67+R67</f>
+        <v/>
+      </c>
+      <c r="U67" s="25">
+        <f>T67-S67</f>
+        <v/>
+      </c>
+      <c r="V67" s="31" t="inlineStr"/>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="B68" s="20" t="inlineStr">
@@ -5245,46 +5485,50 @@
         <f>G68-F68</f>
         <v/>
       </c>
-      <c r="I68" s="26">
+      <c r="I68" s="23">
+        <f>ABS(G68-F68)</f>
+        <v/>
+      </c>
+      <c r="J68" s="26">
         <f>IF(F68&gt;0, G68/F68, IF(G68&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J68" s="27">
-        <f>IF(F68=0, IF(G68=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G68-F68)/F68))</f>
-        <v/>
-      </c>
-      <c r="K68" s="28" t="inlineStr"/>
-      <c r="L68" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N68" s="29" t="n">
+      <c r="K68" s="27">
+        <f>IF(F68&gt;0, 1.0 - (I68/F68), IF(G68=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L68" s="28" t="inlineStr"/>
+      <c r="M68" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="29" t="n">
         <v>640</v>
       </c>
-      <c r="O68" s="30" t="n">
+      <c r="P68" s="30" t="n">
         <v>640</v>
       </c>
-      <c r="P68" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q68" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R68" s="23">
-        <f>L68+N68+P68</f>
-        <v/>
-      </c>
-      <c r="S68" s="24">
+      <c r="Q68" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" s="23">
         <f>M68+O68+Q68</f>
         <v/>
       </c>
-      <c r="T68" s="25">
-        <f>S68-R68</f>
-        <v/>
-      </c>
-      <c r="U68" s="31" t="inlineStr"/>
+      <c r="T68" s="24">
+        <f>N68+P68+R68</f>
+        <v/>
+      </c>
+      <c r="U68" s="25">
+        <f>T68-S68</f>
+        <v/>
+      </c>
+      <c r="V68" s="31" t="inlineStr"/>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="B69" s="20" t="inlineStr">
@@ -5317,46 +5561,50 @@
         <f>G69-F69</f>
         <v/>
       </c>
-      <c r="I69" s="26">
+      <c r="I69" s="23">
+        <f>ABS(G69-F69)</f>
+        <v/>
+      </c>
+      <c r="J69" s="26">
         <f>IF(F69&gt;0, G69/F69, IF(G69&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J69" s="27">
-        <f>IF(F69=0, IF(G69=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G69-F69)/F69))</f>
-        <v/>
-      </c>
-      <c r="K69" s="28" t="inlineStr"/>
-      <c r="L69" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" s="29" t="n">
+      <c r="K69" s="27">
+        <f>IF(F69&gt;0, 1.0 - (I69/F69), IF(G69=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L69" s="28" t="inlineStr"/>
+      <c r="M69" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" s="29" t="n">
         <v>1000</v>
       </c>
-      <c r="O69" s="30" t="n">
+      <c r="P69" s="30" t="n">
         <v>1000</v>
       </c>
-      <c r="P69" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q69" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R69" s="23">
-        <f>L69+N69+P69</f>
-        <v/>
-      </c>
-      <c r="S69" s="24">
+      <c r="Q69" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" s="23">
         <f>M69+O69+Q69</f>
         <v/>
       </c>
-      <c r="T69" s="25">
-        <f>S69-R69</f>
-        <v/>
-      </c>
-      <c r="U69" s="31" t="inlineStr"/>
+      <c r="T69" s="24">
+        <f>N69+P69+R69</f>
+        <v/>
+      </c>
+      <c r="U69" s="25">
+        <f>T69-S69</f>
+        <v/>
+      </c>
+      <c r="V69" s="31" t="inlineStr"/>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="B70" s="20" t="inlineStr">
@@ -5389,46 +5637,50 @@
         <f>G70-F70</f>
         <v/>
       </c>
-      <c r="I70" s="26">
+      <c r="I70" s="23">
+        <f>ABS(G70-F70)</f>
+        <v/>
+      </c>
+      <c r="J70" s="26">
         <f>IF(F70&gt;0, G70/F70, IF(G70&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J70" s="27">
-        <f>IF(F70=0, IF(G70=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G70-F70)/F70))</f>
-        <v/>
-      </c>
-      <c r="K70" s="28" t="inlineStr"/>
-      <c r="L70" s="29" t="n">
+      <c r="K70" s="27">
+        <f>IF(F70&gt;0, 1.0 - (I70/F70), IF(G70=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L70" s="28" t="inlineStr"/>
+      <c r="M70" s="29" t="n">
         <v>396</v>
       </c>
-      <c r="M70" s="30" t="n">
+      <c r="N70" s="30" t="n">
         <v>396</v>
       </c>
-      <c r="N70" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q70" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R70" s="23">
-        <f>L70+N70+P70</f>
-        <v/>
-      </c>
-      <c r="S70" s="24">
+      <c r="O70" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" s="23">
         <f>M70+O70+Q70</f>
         <v/>
       </c>
-      <c r="T70" s="25">
-        <f>S70-R70</f>
-        <v/>
-      </c>
-      <c r="U70" s="31" t="inlineStr"/>
+      <c r="T70" s="24">
+        <f>N70+P70+R70</f>
+        <v/>
+      </c>
+      <c r="U70" s="25">
+        <f>T70-S70</f>
+        <v/>
+      </c>
+      <c r="V70" s="31" t="inlineStr"/>
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="B71" s="20" t="inlineStr">
@@ -5461,50 +5713,54 @@
         <f>G71-F71</f>
         <v/>
       </c>
-      <c r="I71" s="26">
+      <c r="I71" s="23">
+        <f>ABS(G71-F71)</f>
+        <v/>
+      </c>
+      <c r="J71" s="26">
         <f>IF(F71&gt;0, G71/F71, IF(G71&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J71" s="27">
-        <f>IF(F71=0, IF(G71=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G71-F71)/F71))</f>
-        <v/>
-      </c>
-      <c r="K71" s="28" t="inlineStr">
+      <c r="K71" s="27">
+        <f>IF(F71&gt;0, 1.0 - (I71/F71), IF(G71=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L71" s="28" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
       </c>
-      <c r="L71" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q71" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R71" s="23">
-        <f>L71+N71+P71</f>
-        <v/>
-      </c>
-      <c r="S71" s="24">
+      <c r="M71" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" s="23">
         <f>M71+O71+Q71</f>
         <v/>
       </c>
-      <c r="T71" s="25">
-        <f>S71-R71</f>
-        <v/>
-      </c>
-      <c r="U71" s="31" t="inlineStr"/>
+      <c r="T71" s="24">
+        <f>N71+P71+R71</f>
+        <v/>
+      </c>
+      <c r="U71" s="25">
+        <f>T71-S71</f>
+        <v/>
+      </c>
+      <c r="V71" s="31" t="inlineStr"/>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="B72" s="20" t="inlineStr">
@@ -5537,46 +5793,50 @@
         <f>G72-F72</f>
         <v/>
       </c>
-      <c r="I72" s="26">
+      <c r="I72" s="23">
+        <f>ABS(G72-F72)</f>
+        <v/>
+      </c>
+      <c r="J72" s="26">
         <f>IF(F72&gt;0, G72/F72, IF(G72&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J72" s="27">
-        <f>IF(F72=0, IF(G72=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G72-F72)/F72))</f>
-        <v/>
-      </c>
-      <c r="K72" s="28" t="inlineStr"/>
-      <c r="L72" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N72" s="29" t="n">
+      <c r="K72" s="27">
+        <f>IF(F72&gt;0, 1.0 - (I72/F72), IF(G72=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L72" s="28" t="inlineStr"/>
+      <c r="M72" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="29" t="n">
         <v>1100</v>
       </c>
-      <c r="O72" s="30" t="n">
+      <c r="P72" s="30" t="n">
         <v>1100</v>
       </c>
-      <c r="P72" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R72" s="23">
-        <f>L72+N72+P72</f>
-        <v/>
-      </c>
-      <c r="S72" s="24">
+      <c r="Q72" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" s="23">
         <f>M72+O72+Q72</f>
         <v/>
       </c>
-      <c r="T72" s="25">
-        <f>S72-R72</f>
-        <v/>
-      </c>
-      <c r="U72" s="31" t="inlineStr"/>
+      <c r="T72" s="24">
+        <f>N72+P72+R72</f>
+        <v/>
+      </c>
+      <c r="U72" s="25">
+        <f>T72-S72</f>
+        <v/>
+      </c>
+      <c r="V72" s="31" t="inlineStr"/>
     </row>
     <row r="73" ht="20" customHeight="1">
       <c r="B73" s="20" t="inlineStr">
@@ -5609,46 +5869,50 @@
         <f>G73-F73</f>
         <v/>
       </c>
-      <c r="I73" s="26">
+      <c r="I73" s="23">
+        <f>ABS(G73-F73)</f>
+        <v/>
+      </c>
+      <c r="J73" s="26">
         <f>IF(F73&gt;0, G73/F73, IF(G73&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J73" s="27">
-        <f>IF(F73=0, IF(G73=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G73-F73)/F73))</f>
-        <v/>
-      </c>
-      <c r="K73" s="28" t="inlineStr"/>
-      <c r="L73" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" s="29" t="n">
+      <c r="K73" s="27">
+        <f>IF(F73&gt;0, 1.0 - (I73/F73), IF(G73=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L73" s="28" t="inlineStr"/>
+      <c r="M73" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" s="29" t="n">
         <v>300</v>
       </c>
-      <c r="O73" s="30" t="n">
+      <c r="P73" s="30" t="n">
         <v>300</v>
       </c>
-      <c r="P73" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q73" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R73" s="23">
-        <f>L73+N73+P73</f>
-        <v/>
-      </c>
-      <c r="S73" s="24">
+      <c r="Q73" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" s="23">
         <f>M73+O73+Q73</f>
         <v/>
       </c>
-      <c r="T73" s="25">
-        <f>S73-R73</f>
-        <v/>
-      </c>
-      <c r="U73" s="31" t="inlineStr"/>
+      <c r="T73" s="24">
+        <f>N73+P73+R73</f>
+        <v/>
+      </c>
+      <c r="U73" s="25">
+        <f>T73-S73</f>
+        <v/>
+      </c>
+      <c r="V73" s="31" t="inlineStr"/>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="B74" s="20" t="inlineStr">
@@ -5681,46 +5945,50 @@
         <f>G74-F74</f>
         <v/>
       </c>
-      <c r="I74" s="26">
+      <c r="I74" s="23">
+        <f>ABS(G74-F74)</f>
+        <v/>
+      </c>
+      <c r="J74" s="26">
         <f>IF(F74&gt;0, G74/F74, IF(G74&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J74" s="27">
-        <f>IF(F74=0, IF(G74=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G74-F74)/F74))</f>
-        <v/>
-      </c>
-      <c r="K74" s="28" t="inlineStr"/>
-      <c r="L74" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N74" s="29" t="n">
+      <c r="K74" s="27">
+        <f>IF(F74&gt;0, 1.0 - (I74/F74), IF(G74=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L74" s="28" t="inlineStr"/>
+      <c r="M74" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" s="29" t="n">
         <v>400</v>
       </c>
-      <c r="O74" s="30" t="n">
+      <c r="P74" s="30" t="n">
         <v>400</v>
       </c>
-      <c r="P74" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q74" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R74" s="23">
-        <f>L74+N74+P74</f>
-        <v/>
-      </c>
-      <c r="S74" s="24">
+      <c r="Q74" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" s="23">
         <f>M74+O74+Q74</f>
         <v/>
       </c>
-      <c r="T74" s="25">
-        <f>S74-R74</f>
-        <v/>
-      </c>
-      <c r="U74" s="31" t="inlineStr"/>
+      <c r="T74" s="24">
+        <f>N74+P74+R74</f>
+        <v/>
+      </c>
+      <c r="U74" s="25">
+        <f>T74-S74</f>
+        <v/>
+      </c>
+      <c r="V74" s="31" t="inlineStr"/>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="B75" s="20" t="inlineStr">
@@ -5753,46 +6021,50 @@
         <f>G75-F75</f>
         <v/>
       </c>
-      <c r="I75" s="26">
+      <c r="I75" s="23">
+        <f>ABS(G75-F75)</f>
+        <v/>
+      </c>
+      <c r="J75" s="26">
         <f>IF(F75&gt;0, G75/F75, IF(G75&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J75" s="27">
-        <f>IF(F75=0, IF(G75=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G75-F75)/F75))</f>
-        <v/>
-      </c>
-      <c r="K75" s="28" t="inlineStr"/>
-      <c r="L75" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N75" s="29" t="n">
+      <c r="K75" s="27">
+        <f>IF(F75&gt;0, 1.0 - (I75/F75), IF(G75=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L75" s="28" t="inlineStr"/>
+      <c r="M75" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" s="29" t="n">
         <v>660</v>
       </c>
-      <c r="O75" s="30" t="n">
+      <c r="P75" s="30" t="n">
         <v>660</v>
       </c>
-      <c r="P75" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q75" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R75" s="23">
-        <f>L75+N75+P75</f>
-        <v/>
-      </c>
-      <c r="S75" s="24">
+      <c r="Q75" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" s="23">
         <f>M75+O75+Q75</f>
         <v/>
       </c>
-      <c r="T75" s="25">
-        <f>S75-R75</f>
-        <v/>
-      </c>
-      <c r="U75" s="31" t="inlineStr"/>
+      <c r="T75" s="24">
+        <f>N75+P75+R75</f>
+        <v/>
+      </c>
+      <c r="U75" s="25">
+        <f>T75-S75</f>
+        <v/>
+      </c>
+      <c r="V75" s="31" t="inlineStr"/>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="B76" s="20" t="inlineStr">
@@ -5825,46 +6097,50 @@
         <f>G76-F76</f>
         <v/>
       </c>
-      <c r="I76" s="26">
+      <c r="I76" s="23">
+        <f>ABS(G76-F76)</f>
+        <v/>
+      </c>
+      <c r="J76" s="26">
         <f>IF(F76&gt;0, G76/F76, IF(G76&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J76" s="27">
-        <f>IF(F76=0, IF(G76=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G76-F76)/F76))</f>
-        <v/>
-      </c>
-      <c r="K76" s="28" t="inlineStr"/>
-      <c r="L76" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" s="29" t="n">
+      <c r="K76" s="27">
+        <f>IF(F76&gt;0, 1.0 - (I76/F76), IF(G76=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L76" s="28" t="inlineStr"/>
+      <c r="M76" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" s="29" t="n">
         <v>640</v>
       </c>
-      <c r="O76" s="30" t="n">
+      <c r="P76" s="30" t="n">
         <v>640</v>
       </c>
-      <c r="P76" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R76" s="23">
-        <f>L76+N76+P76</f>
-        <v/>
-      </c>
-      <c r="S76" s="24">
+      <c r="Q76" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" s="23">
         <f>M76+O76+Q76</f>
         <v/>
       </c>
-      <c r="T76" s="25">
-        <f>S76-R76</f>
-        <v/>
-      </c>
-      <c r="U76" s="31" t="inlineStr"/>
+      <c r="T76" s="24">
+        <f>N76+P76+R76</f>
+        <v/>
+      </c>
+      <c r="U76" s="25">
+        <f>T76-S76</f>
+        <v/>
+      </c>
+      <c r="V76" s="31" t="inlineStr"/>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="B77" s="20" t="inlineStr">
@@ -5897,46 +6173,50 @@
         <f>G77-F77</f>
         <v/>
       </c>
-      <c r="I77" s="26">
+      <c r="I77" s="23">
+        <f>ABS(G77-F77)</f>
+        <v/>
+      </c>
+      <c r="J77" s="26">
         <f>IF(F77&gt;0, G77/F77, IF(G77&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J77" s="27">
-        <f>IF(F77=0, IF(G77=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G77-F77)/F77))</f>
-        <v/>
-      </c>
-      <c r="K77" s="28" t="inlineStr"/>
-      <c r="L77" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N77" s="29" t="n">
+      <c r="K77" s="27">
+        <f>IF(F77&gt;0, 1.0 - (I77/F77), IF(G77=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L77" s="28" t="inlineStr"/>
+      <c r="M77" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" s="29" t="n">
         <v>1000</v>
       </c>
-      <c r="O77" s="30" t="n">
+      <c r="P77" s="30" t="n">
         <v>1000</v>
       </c>
-      <c r="P77" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q77" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R77" s="23">
-        <f>L77+N77+P77</f>
-        <v/>
-      </c>
-      <c r="S77" s="24">
+      <c r="Q77" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" s="23">
         <f>M77+O77+Q77</f>
         <v/>
       </c>
-      <c r="T77" s="25">
-        <f>S77-R77</f>
-        <v/>
-      </c>
-      <c r="U77" s="31" t="inlineStr"/>
+      <c r="T77" s="24">
+        <f>N77+P77+R77</f>
+        <v/>
+      </c>
+      <c r="U77" s="25">
+        <f>T77-S77</f>
+        <v/>
+      </c>
+      <c r="V77" s="31" t="inlineStr"/>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="B78" s="20" t="inlineStr">
@@ -5969,50 +6249,54 @@
         <f>G78-F78</f>
         <v/>
       </c>
-      <c r="I78" s="26">
+      <c r="I78" s="23">
+        <f>ABS(G78-F78)</f>
+        <v/>
+      </c>
+      <c r="J78" s="26">
         <f>IF(F78&gt;0, G78/F78, IF(G78&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J78" s="27">
-        <f>IF(F78=0, IF(G78=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G78-F78)/F78))</f>
-        <v/>
-      </c>
-      <c r="K78" s="28" t="inlineStr">
+      <c r="K78" s="27">
+        <f>IF(F78&gt;0, 1.0 - (I78/F78), IF(G78=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L78" s="28" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
       </c>
-      <c r="L78" s="29" t="n">
+      <c r="M78" s="29" t="n">
         <v>792</v>
       </c>
-      <c r="M78" s="30" t="n">
+      <c r="N78" s="30" t="n">
         <v>792</v>
       </c>
-      <c r="N78" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R78" s="23">
-        <f>L78+N78+P78</f>
-        <v/>
-      </c>
-      <c r="S78" s="24">
+      <c r="O78" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" s="23">
         <f>M78+O78+Q78</f>
         <v/>
       </c>
-      <c r="T78" s="25">
-        <f>S78-R78</f>
-        <v/>
-      </c>
-      <c r="U78" s="31" t="inlineStr"/>
+      <c r="T78" s="24">
+        <f>N78+P78+R78</f>
+        <v/>
+      </c>
+      <c r="U78" s="25">
+        <f>T78-S78</f>
+        <v/>
+      </c>
+      <c r="V78" s="31" t="inlineStr"/>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="B79" s="20" t="inlineStr">
@@ -6045,50 +6329,54 @@
         <f>G79-F79</f>
         <v/>
       </c>
-      <c r="I79" s="26">
+      <c r="I79" s="23">
+        <f>ABS(G79-F79)</f>
+        <v/>
+      </c>
+      <c r="J79" s="26">
         <f>IF(F79&gt;0, G79/F79, IF(G79&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J79" s="27">
-        <f>IF(F79=0, IF(G79=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G79-F79)/F79))</f>
-        <v/>
-      </c>
-      <c r="K79" s="28" t="inlineStr">
+      <c r="K79" s="27">
+        <f>IF(F79&gt;0, 1.0 - (I79/F79), IF(G79=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L79" s="28" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
       </c>
-      <c r="L79" s="29" t="n">
+      <c r="M79" s="29" t="n">
         <v>600</v>
       </c>
-      <c r="M79" s="30" t="n">
+      <c r="N79" s="30" t="n">
         <v>600</v>
       </c>
-      <c r="N79" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q79" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R79" s="23">
-        <f>L79+N79+P79</f>
-        <v/>
-      </c>
-      <c r="S79" s="24">
+      <c r="O79" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" s="23">
         <f>M79+O79+Q79</f>
         <v/>
       </c>
-      <c r="T79" s="25">
-        <f>S79-R79</f>
-        <v/>
-      </c>
-      <c r="U79" s="31" t="inlineStr"/>
+      <c r="T79" s="24">
+        <f>N79+P79+R79</f>
+        <v/>
+      </c>
+      <c r="U79" s="25">
+        <f>T79-S79</f>
+        <v/>
+      </c>
+      <c r="V79" s="31" t="inlineStr"/>
     </row>
     <row r="80" ht="20" customHeight="1">
       <c r="B80" s="20" t="inlineStr">
@@ -6121,50 +6409,54 @@
         <f>G80-F80</f>
         <v/>
       </c>
-      <c r="I80" s="26">
+      <c r="I80" s="23">
+        <f>ABS(G80-F80)</f>
+        <v/>
+      </c>
+      <c r="J80" s="26">
         <f>IF(F80&gt;0, G80/F80, IF(G80&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J80" s="27">
-        <f>IF(F80=0, IF(G80=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G80-F80)/F80))</f>
-        <v/>
-      </c>
-      <c r="K80" s="28" t="inlineStr">
+      <c r="K80" s="27">
+        <f>IF(F80&gt;0, 1.0 - (I80/F80), IF(G80=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L80" s="28" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
       </c>
-      <c r="L80" s="29" t="n">
+      <c r="M80" s="29" t="n">
         <v>640</v>
       </c>
-      <c r="M80" s="30" t="n">
+      <c r="N80" s="30" t="n">
         <v>640</v>
       </c>
-      <c r="N80" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q80" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R80" s="23">
-        <f>L80+N80+P80</f>
-        <v/>
-      </c>
-      <c r="S80" s="24">
+      <c r="O80" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" s="23">
         <f>M80+O80+Q80</f>
         <v/>
       </c>
-      <c r="T80" s="25">
-        <f>S80-R80</f>
-        <v/>
-      </c>
-      <c r="U80" s="31" t="inlineStr"/>
+      <c r="T80" s="24">
+        <f>N80+P80+R80</f>
+        <v/>
+      </c>
+      <c r="U80" s="25">
+        <f>T80-S80</f>
+        <v/>
+      </c>
+      <c r="V80" s="31" t="inlineStr"/>
     </row>
     <row r="81" ht="20" customHeight="1">
       <c r="B81" s="20" t="inlineStr">
@@ -6197,46 +6489,50 @@
         <f>G81-F81</f>
         <v/>
       </c>
-      <c r="I81" s="26">
+      <c r="I81" s="23">
+        <f>ABS(G81-F81)</f>
+        <v/>
+      </c>
+      <c r="J81" s="26">
         <f>IF(F81&gt;0, G81/F81, IF(G81&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J81" s="27">
-        <f>IF(F81=0, IF(G81=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G81-F81)/F81))</f>
-        <v/>
-      </c>
-      <c r="K81" s="28" t="inlineStr"/>
-      <c r="L81" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" s="29" t="n">
+      <c r="K81" s="27">
+        <f>IF(F81&gt;0, 1.0 - (I81/F81), IF(G81=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L81" s="28" t="inlineStr"/>
+      <c r="M81" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" s="29" t="n">
         <v>660</v>
       </c>
-      <c r="O81" s="30" t="n">
+      <c r="P81" s="30" t="n">
         <v>660</v>
       </c>
-      <c r="P81" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q81" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R81" s="23">
-        <f>L81+N81+P81</f>
-        <v/>
-      </c>
-      <c r="S81" s="24">
+      <c r="Q81" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" s="23">
         <f>M81+O81+Q81</f>
         <v/>
       </c>
-      <c r="T81" s="25">
-        <f>S81-R81</f>
-        <v/>
-      </c>
-      <c r="U81" s="31" t="inlineStr"/>
+      <c r="T81" s="24">
+        <f>N81+P81+R81</f>
+        <v/>
+      </c>
+      <c r="U81" s="25">
+        <f>T81-S81</f>
+        <v/>
+      </c>
+      <c r="V81" s="31" t="inlineStr"/>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="B82" s="20" t="inlineStr">
@@ -6269,46 +6565,50 @@
         <f>G82-F82</f>
         <v/>
       </c>
-      <c r="I82" s="26">
+      <c r="I82" s="23">
+        <f>ABS(G82-F82)</f>
+        <v/>
+      </c>
+      <c r="J82" s="26">
         <f>IF(F82&gt;0, G82/F82, IF(G82&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J82" s="27">
-        <f>IF(F82=0, IF(G82=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G82-F82)/F82))</f>
-        <v/>
-      </c>
-      <c r="K82" s="28" t="inlineStr"/>
-      <c r="L82" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" s="29" t="n">
+      <c r="K82" s="27">
+        <f>IF(F82&gt;0, 1.0 - (I82/F82), IF(G82=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L82" s="28" t="inlineStr"/>
+      <c r="M82" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="29" t="n">
         <v>320</v>
       </c>
-      <c r="O82" s="30" t="n">
+      <c r="P82" s="30" t="n">
         <v>320</v>
       </c>
-      <c r="P82" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q82" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R82" s="23">
-        <f>L82+N82+P82</f>
-        <v/>
-      </c>
-      <c r="S82" s="24">
+      <c r="Q82" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" s="23">
         <f>M82+O82+Q82</f>
         <v/>
       </c>
-      <c r="T82" s="25">
-        <f>S82-R82</f>
-        <v/>
-      </c>
-      <c r="U82" s="31" t="inlineStr"/>
+      <c r="T82" s="24">
+        <f>N82+P82+R82</f>
+        <v/>
+      </c>
+      <c r="U82" s="25">
+        <f>T82-S82</f>
+        <v/>
+      </c>
+      <c r="V82" s="31" t="inlineStr"/>
     </row>
     <row r="83" ht="20" customHeight="1">
       <c r="B83" s="20" t="inlineStr">
@@ -6341,50 +6641,54 @@
         <f>G83-F83</f>
         <v/>
       </c>
-      <c r="I83" s="26">
+      <c r="I83" s="23">
+        <f>ABS(G83-F83)</f>
+        <v/>
+      </c>
+      <c r="J83" s="26">
         <f>IF(F83&gt;0, G83/F83, IF(G83&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J83" s="27">
-        <f>IF(F83=0, IF(G83=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G83-F83)/F83))</f>
-        <v/>
-      </c>
-      <c r="K83" s="28" t="inlineStr">
+      <c r="K83" s="27">
+        <f>IF(F83&gt;0, 1.0 - (I83/F83), IF(G83=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L83" s="28" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
       </c>
-      <c r="L83" s="29" t="n">
+      <c r="M83" s="29" t="n">
         <v>792</v>
       </c>
-      <c r="M83" s="30" t="n">
+      <c r="N83" s="30" t="n">
         <v>792</v>
       </c>
-      <c r="N83" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O83" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P83" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q83" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R83" s="23">
-        <f>L83+N83+P83</f>
-        <v/>
-      </c>
-      <c r="S83" s="24">
+      <c r="O83" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" s="23">
         <f>M83+O83+Q83</f>
         <v/>
       </c>
-      <c r="T83" s="25">
-        <f>S83-R83</f>
-        <v/>
-      </c>
-      <c r="U83" s="31" t="inlineStr"/>
+      <c r="T83" s="24">
+        <f>N83+P83+R83</f>
+        <v/>
+      </c>
+      <c r="U83" s="25">
+        <f>T83-S83</f>
+        <v/>
+      </c>
+      <c r="V83" s="31" t="inlineStr"/>
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="B84" s="20" t="inlineStr">
@@ -6417,46 +6721,50 @@
         <f>G84-F84</f>
         <v/>
       </c>
-      <c r="I84" s="26">
+      <c r="I84" s="23">
+        <f>ABS(G84-F84)</f>
+        <v/>
+      </c>
+      <c r="J84" s="26">
         <f>IF(F84&gt;0, G84/F84, IF(G84&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J84" s="27">
-        <f>IF(F84=0, IF(G84=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G84-F84)/F84))</f>
-        <v/>
-      </c>
-      <c r="K84" s="28" t="inlineStr"/>
-      <c r="L84" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N84" s="29" t="n">
+      <c r="K84" s="27">
+        <f>IF(F84&gt;0, 1.0 - (I84/F84), IF(G84=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L84" s="28" t="inlineStr"/>
+      <c r="M84" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" s="29" t="n">
         <v>300</v>
       </c>
-      <c r="O84" s="30" t="n">
+      <c r="P84" s="30" t="n">
         <v>300</v>
       </c>
-      <c r="P84" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q84" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R84" s="23">
-        <f>L84+N84+P84</f>
-        <v/>
-      </c>
-      <c r="S84" s="24">
+      <c r="Q84" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" s="23">
         <f>M84+O84+Q84</f>
         <v/>
       </c>
-      <c r="T84" s="25">
-        <f>S84-R84</f>
-        <v/>
-      </c>
-      <c r="U84" s="31" t="inlineStr"/>
+      <c r="T84" s="24">
+        <f>N84+P84+R84</f>
+        <v/>
+      </c>
+      <c r="U84" s="25">
+        <f>T84-S84</f>
+        <v/>
+      </c>
+      <c r="V84" s="31" t="inlineStr"/>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="B85" s="20" t="inlineStr">
@@ -6489,46 +6797,50 @@
         <f>G85-F85</f>
         <v/>
       </c>
-      <c r="I85" s="26">
+      <c r="I85" s="23">
+        <f>ABS(G85-F85)</f>
+        <v/>
+      </c>
+      <c r="J85" s="26">
         <f>IF(F85&gt;0, G85/F85, IF(G85&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J85" s="27">
-        <f>IF(F85=0, IF(G85=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G85-F85)/F85))</f>
-        <v/>
-      </c>
-      <c r="K85" s="28" t="inlineStr"/>
-      <c r="L85" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N85" s="29" t="n">
+      <c r="K85" s="27">
+        <f>IF(F85&gt;0, 1.0 - (I85/F85), IF(G85=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L85" s="28" t="inlineStr"/>
+      <c r="M85" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" s="29" t="n">
         <v>660</v>
       </c>
-      <c r="O85" s="30" t="n">
+      <c r="P85" s="30" t="n">
         <v>660</v>
       </c>
-      <c r="P85" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q85" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R85" s="23">
-        <f>L85+N85+P85</f>
-        <v/>
-      </c>
-      <c r="S85" s="24">
+      <c r="Q85" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" s="23">
         <f>M85+O85+Q85</f>
         <v/>
       </c>
-      <c r="T85" s="25">
-        <f>S85-R85</f>
-        <v/>
-      </c>
-      <c r="U85" s="31" t="inlineStr"/>
+      <c r="T85" s="24">
+        <f>N85+P85+R85</f>
+        <v/>
+      </c>
+      <c r="U85" s="25">
+        <f>T85-S85</f>
+        <v/>
+      </c>
+      <c r="V85" s="31" t="inlineStr"/>
     </row>
     <row r="86" ht="20" customHeight="1">
       <c r="B86" s="20" t="inlineStr">
@@ -6561,46 +6873,50 @@
         <f>G86-F86</f>
         <v/>
       </c>
-      <c r="I86" s="26">
+      <c r="I86" s="23">
+        <f>ABS(G86-F86)</f>
+        <v/>
+      </c>
+      <c r="J86" s="26">
         <f>IF(F86&gt;0, G86/F86, IF(G86&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J86" s="27">
-        <f>IF(F86=0, IF(G86=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G86-F86)/F86))</f>
-        <v/>
-      </c>
-      <c r="K86" s="28" t="inlineStr"/>
-      <c r="L86" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N86" s="29" t="n">
+      <c r="K86" s="27">
+        <f>IF(F86&gt;0, 1.0 - (I86/F86), IF(G86=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L86" s="28" t="inlineStr"/>
+      <c r="M86" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" s="29" t="n">
         <v>400</v>
       </c>
-      <c r="O86" s="30" t="n">
+      <c r="P86" s="30" t="n">
         <v>400</v>
       </c>
-      <c r="P86" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q86" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R86" s="23">
-        <f>L86+N86+P86</f>
-        <v/>
-      </c>
-      <c r="S86" s="24">
+      <c r="Q86" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" s="23">
         <f>M86+O86+Q86</f>
         <v/>
       </c>
-      <c r="T86" s="25">
-        <f>S86-R86</f>
-        <v/>
-      </c>
-      <c r="U86" s="31" t="inlineStr"/>
+      <c r="T86" s="24">
+        <f>N86+P86+R86</f>
+        <v/>
+      </c>
+      <c r="U86" s="25">
+        <f>T86-S86</f>
+        <v/>
+      </c>
+      <c r="V86" s="31" t="inlineStr"/>
     </row>
     <row r="87" ht="20" customHeight="1">
       <c r="B87" s="20" t="inlineStr">
@@ -6633,50 +6949,54 @@
         <f>G87-F87</f>
         <v/>
       </c>
-      <c r="I87" s="26">
+      <c r="I87" s="23">
+        <f>ABS(G87-F87)</f>
+        <v/>
+      </c>
+      <c r="J87" s="26">
         <f>IF(F87&gt;0, G87/F87, IF(G87&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J87" s="27">
-        <f>IF(F87=0, IF(G87=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G87-F87)/F87))</f>
-        <v/>
-      </c>
-      <c r="K87" s="28" t="inlineStr">
+      <c r="K87" s="27">
+        <f>IF(F87&gt;0, 1.0 - (I87/F87), IF(G87=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L87" s="28" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
       </c>
-      <c r="L87" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N87" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O87" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q87" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R87" s="23">
-        <f>L87+N87+P87</f>
-        <v/>
-      </c>
-      <c r="S87" s="24">
+      <c r="M87" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" s="23">
         <f>M87+O87+Q87</f>
         <v/>
       </c>
-      <c r="T87" s="25">
-        <f>S87-R87</f>
-        <v/>
-      </c>
-      <c r="U87" s="31" t="inlineStr"/>
+      <c r="T87" s="24">
+        <f>N87+P87+R87</f>
+        <v/>
+      </c>
+      <c r="U87" s="25">
+        <f>T87-S87</f>
+        <v/>
+      </c>
+      <c r="V87" s="31" t="inlineStr"/>
     </row>
     <row r="88" ht="20" customHeight="1">
       <c r="B88" s="20" t="inlineStr">
@@ -6709,46 +7029,50 @@
         <f>G88-F88</f>
         <v/>
       </c>
-      <c r="I88" s="26">
+      <c r="I88" s="23">
+        <f>ABS(G88-F88)</f>
+        <v/>
+      </c>
+      <c r="J88" s="26">
         <f>IF(F88&gt;0, G88/F88, IF(G88&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J88" s="27">
-        <f>IF(F88=0, IF(G88=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G88-F88)/F88))</f>
-        <v/>
-      </c>
-      <c r="K88" s="28" t="inlineStr"/>
-      <c r="L88" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" s="29" t="n">
+      <c r="K88" s="27">
+        <f>IF(F88&gt;0, 1.0 - (I88/F88), IF(G88=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L88" s="28" t="inlineStr"/>
+      <c r="M88" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="29" t="n">
         <v>300</v>
       </c>
-      <c r="O88" s="30" t="n">
+      <c r="P88" s="30" t="n">
         <v>300</v>
       </c>
-      <c r="P88" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q88" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R88" s="23">
-        <f>L88+N88+P88</f>
-        <v/>
-      </c>
-      <c r="S88" s="24">
+      <c r="Q88" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" s="23">
         <f>M88+O88+Q88</f>
         <v/>
       </c>
-      <c r="T88" s="25">
-        <f>S88-R88</f>
-        <v/>
-      </c>
-      <c r="U88" s="31" t="inlineStr"/>
+      <c r="T88" s="24">
+        <f>N88+P88+R88</f>
+        <v/>
+      </c>
+      <c r="U88" s="25">
+        <f>T88-S88</f>
+        <v/>
+      </c>
+      <c r="V88" s="31" t="inlineStr"/>
     </row>
     <row r="89" ht="20" customHeight="1">
       <c r="B89" s="20" t="inlineStr">
@@ -6781,46 +7105,50 @@
         <f>G89-F89</f>
         <v/>
       </c>
-      <c r="I89" s="26">
+      <c r="I89" s="23">
+        <f>ABS(G89-F89)</f>
+        <v/>
+      </c>
+      <c r="J89" s="26">
         <f>IF(F89&gt;0, G89/F89, IF(G89&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J89" s="27">
-        <f>IF(F89=0, IF(G89=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G89-F89)/F89))</f>
-        <v/>
-      </c>
-      <c r="K89" s="28" t="inlineStr"/>
-      <c r="L89" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N89" s="29" t="n">
+      <c r="K89" s="27">
+        <f>IF(F89&gt;0, 1.0 - (I89/F89), IF(G89=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L89" s="28" t="inlineStr"/>
+      <c r="M89" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" s="29" t="n">
         <v>640</v>
       </c>
-      <c r="O89" s="30" t="n">
+      <c r="P89" s="30" t="n">
         <v>640</v>
       </c>
-      <c r="P89" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q89" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R89" s="23">
-        <f>L89+N89+P89</f>
-        <v/>
-      </c>
-      <c r="S89" s="24">
+      <c r="Q89" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" s="23">
         <f>M89+O89+Q89</f>
         <v/>
       </c>
-      <c r="T89" s="25">
-        <f>S89-R89</f>
-        <v/>
-      </c>
-      <c r="U89" s="31" t="inlineStr"/>
+      <c r="T89" s="24">
+        <f>N89+P89+R89</f>
+        <v/>
+      </c>
+      <c r="U89" s="25">
+        <f>T89-S89</f>
+        <v/>
+      </c>
+      <c r="V89" s="31" t="inlineStr"/>
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="B90" s="20" t="inlineStr">
@@ -6853,46 +7181,50 @@
         <f>G90-F90</f>
         <v/>
       </c>
-      <c r="I90" s="26">
+      <c r="I90" s="23">
+        <f>ABS(G90-F90)</f>
+        <v/>
+      </c>
+      <c r="J90" s="26">
         <f>IF(F90&gt;0, G90/F90, IF(G90&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J90" s="27">
-        <f>IF(F90=0, IF(G90=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G90-F90)/F90))</f>
-        <v/>
-      </c>
-      <c r="K90" s="28" t="inlineStr"/>
-      <c r="L90" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" s="29" t="n">
+      <c r="K90" s="27">
+        <f>IF(F90&gt;0, 1.0 - (I90/F90), IF(G90=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L90" s="28" t="inlineStr"/>
+      <c r="M90" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="29" t="n">
         <v>660</v>
       </c>
-      <c r="O90" s="30" t="n">
+      <c r="P90" s="30" t="n">
         <v>660</v>
       </c>
-      <c r="P90" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R90" s="23">
-        <f>L90+N90+P90</f>
-        <v/>
-      </c>
-      <c r="S90" s="24">
+      <c r="Q90" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" s="23">
         <f>M90+O90+Q90</f>
         <v/>
       </c>
-      <c r="T90" s="25">
-        <f>S90-R90</f>
-        <v/>
-      </c>
-      <c r="U90" s="31" t="inlineStr"/>
+      <c r="T90" s="24">
+        <f>N90+P90+R90</f>
+        <v/>
+      </c>
+      <c r="U90" s="25">
+        <f>T90-S90</f>
+        <v/>
+      </c>
+      <c r="V90" s="31" t="inlineStr"/>
     </row>
     <row r="91" ht="20" customHeight="1">
       <c r="B91" s="20" t="inlineStr">
@@ -6925,46 +7257,50 @@
         <f>G91-F91</f>
         <v/>
       </c>
-      <c r="I91" s="26">
+      <c r="I91" s="23">
+        <f>ABS(G91-F91)</f>
+        <v/>
+      </c>
+      <c r="J91" s="26">
         <f>IF(F91&gt;0, G91/F91, IF(G91&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J91" s="27">
-        <f>IF(F91=0, IF(G91=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G91-F91)/F91))</f>
-        <v/>
-      </c>
-      <c r="K91" s="28" t="inlineStr"/>
-      <c r="L91" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" s="29" t="n">
+      <c r="K91" s="27">
+        <f>IF(F91&gt;0, 1.0 - (I91/F91), IF(G91=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L91" s="28" t="inlineStr"/>
+      <c r="M91" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" s="29" t="n">
         <v>600</v>
       </c>
-      <c r="O91" s="30" t="n">
+      <c r="P91" s="30" t="n">
         <v>600</v>
       </c>
-      <c r="P91" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R91" s="23">
-        <f>L91+N91+P91</f>
-        <v/>
-      </c>
-      <c r="S91" s="24">
+      <c r="Q91" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" s="23">
         <f>M91+O91+Q91</f>
         <v/>
       </c>
-      <c r="T91" s="25">
-        <f>S91-R91</f>
-        <v/>
-      </c>
-      <c r="U91" s="31" t="inlineStr"/>
+      <c r="T91" s="24">
+        <f>N91+P91+R91</f>
+        <v/>
+      </c>
+      <c r="U91" s="25">
+        <f>T91-S91</f>
+        <v/>
+      </c>
+      <c r="V91" s="31" t="inlineStr"/>
     </row>
     <row r="92" ht="20" customHeight="1">
       <c r="B92" s="20" t="inlineStr">
@@ -6997,46 +7333,50 @@
         <f>G92-F92</f>
         <v/>
       </c>
-      <c r="I92" s="26">
+      <c r="I92" s="23">
+        <f>ABS(G92-F92)</f>
+        <v/>
+      </c>
+      <c r="J92" s="26">
         <f>IF(F92&gt;0, G92/F92, IF(G92&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J92" s="27">
-        <f>IF(F92=0, IF(G92=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G92-F92)/F92))</f>
-        <v/>
-      </c>
-      <c r="K92" s="28" t="inlineStr"/>
-      <c r="L92" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M92" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N92" s="29" t="n">
+      <c r="K92" s="27">
+        <f>IF(F92&gt;0, 1.0 - (I92/F92), IF(G92=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L92" s="28" t="inlineStr"/>
+      <c r="M92" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" s="29" t="n">
         <v>600</v>
       </c>
-      <c r="O92" s="30" t="n">
+      <c r="P92" s="30" t="n">
         <v>600</v>
       </c>
-      <c r="P92" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q92" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R92" s="23">
-        <f>L92+N92+P92</f>
-        <v/>
-      </c>
-      <c r="S92" s="24">
+      <c r="Q92" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" s="23">
         <f>M92+O92+Q92</f>
         <v/>
       </c>
-      <c r="T92" s="25">
-        <f>S92-R92</f>
-        <v/>
-      </c>
-      <c r="U92" s="31" t="inlineStr"/>
+      <c r="T92" s="24">
+        <f>N92+P92+R92</f>
+        <v/>
+      </c>
+      <c r="U92" s="25">
+        <f>T92-S92</f>
+        <v/>
+      </c>
+      <c r="V92" s="31" t="inlineStr"/>
     </row>
     <row r="93" ht="20" customHeight="1">
       <c r="B93" s="20" t="inlineStr">
@@ -7069,50 +7409,54 @@
         <f>G93-F93</f>
         <v/>
       </c>
-      <c r="I93" s="26">
+      <c r="I93" s="23">
+        <f>ABS(G93-F93)</f>
+        <v/>
+      </c>
+      <c r="J93" s="26">
         <f>IF(F93&gt;0, G93/F93, IF(G93&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J93" s="27">
-        <f>IF(F93=0, IF(G93=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G93-F93)/F93))</f>
-        <v/>
-      </c>
-      <c r="K93" s="28" t="inlineStr">
+      <c r="K93" s="27">
+        <f>IF(F93&gt;0, 1.0 - (I93/F93), IF(G93=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L93" s="28" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
       </c>
-      <c r="L93" s="29" t="n">
+      <c r="M93" s="29" t="n">
         <v>792</v>
       </c>
-      <c r="M93" s="30" t="n">
+      <c r="N93" s="30" t="n">
         <v>792</v>
       </c>
-      <c r="N93" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O93" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P93" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q93" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R93" s="23">
-        <f>L93+N93+P93</f>
-        <v/>
-      </c>
-      <c r="S93" s="24">
+      <c r="O93" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" s="23">
         <f>M93+O93+Q93</f>
         <v/>
       </c>
-      <c r="T93" s="25">
-        <f>S93-R93</f>
-        <v/>
-      </c>
-      <c r="U93" s="31" t="inlineStr"/>
+      <c r="T93" s="24">
+        <f>N93+P93+R93</f>
+        <v/>
+      </c>
+      <c r="U93" s="25">
+        <f>T93-S93</f>
+        <v/>
+      </c>
+      <c r="V93" s="31" t="inlineStr"/>
     </row>
     <row r="94" ht="20" customHeight="1">
       <c r="B94" s="20" t="inlineStr">
@@ -7145,50 +7489,54 @@
         <f>G94-F94</f>
         <v/>
       </c>
-      <c r="I94" s="26">
+      <c r="I94" s="23">
+        <f>ABS(G94-F94)</f>
+        <v/>
+      </c>
+      <c r="J94" s="26">
         <f>IF(F94&gt;0, G94/F94, IF(G94&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J94" s="27">
-        <f>IF(F94=0, IF(G94=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G94-F94)/F94))</f>
-        <v/>
-      </c>
-      <c r="K94" s="28" t="inlineStr">
+      <c r="K94" s="27">
+        <f>IF(F94&gt;0, 1.0 - (I94/F94), IF(G94=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L94" s="28" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
       </c>
-      <c r="L94" s="29" t="n">
+      <c r="M94" s="29" t="n">
         <v>640</v>
       </c>
-      <c r="M94" s="30" t="n">
+      <c r="N94" s="30" t="n">
         <v>640</v>
       </c>
-      <c r="N94" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O94" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P94" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R94" s="23">
-        <f>L94+N94+P94</f>
-        <v/>
-      </c>
-      <c r="S94" s="24">
+      <c r="O94" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" s="23">
         <f>M94+O94+Q94</f>
         <v/>
       </c>
-      <c r="T94" s="25">
-        <f>S94-R94</f>
-        <v/>
-      </c>
-      <c r="U94" s="31" t="inlineStr"/>
+      <c r="T94" s="24">
+        <f>N94+P94+R94</f>
+        <v/>
+      </c>
+      <c r="U94" s="25">
+        <f>T94-S94</f>
+        <v/>
+      </c>
+      <c r="V94" s="31" t="inlineStr"/>
     </row>
     <row r="95" ht="20" customHeight="1">
       <c r="B95" s="20" t="inlineStr">
@@ -7221,50 +7569,54 @@
         <f>G95-F95</f>
         <v/>
       </c>
-      <c r="I95" s="26">
+      <c r="I95" s="23">
+        <f>ABS(G95-F95)</f>
+        <v/>
+      </c>
+      <c r="J95" s="26">
         <f>IF(F95&gt;0, G95/F95, IF(G95&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J95" s="27">
-        <f>IF(F95=0, IF(G95=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G95-F95)/F95))</f>
-        <v/>
-      </c>
-      <c r="K95" s="28" t="inlineStr">
+      <c r="K95" s="27">
+        <f>IF(F95&gt;0, 1.0 - (I95/F95), IF(G95=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L95" s="28" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
       </c>
-      <c r="L95" s="29" t="n">
+      <c r="M95" s="29" t="n">
         <v>1056</v>
       </c>
-      <c r="M95" s="30" t="n">
+      <c r="N95" s="30" t="n">
         <v>1056</v>
       </c>
-      <c r="N95" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O95" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P95" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q95" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R95" s="23">
-        <f>L95+N95+P95</f>
-        <v/>
-      </c>
-      <c r="S95" s="24">
+      <c r="O95" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" s="23">
         <f>M95+O95+Q95</f>
         <v/>
       </c>
-      <c r="T95" s="25">
-        <f>S95-R95</f>
-        <v/>
-      </c>
-      <c r="U95" s="31" t="inlineStr"/>
+      <c r="T95" s="24">
+        <f>N95+P95+R95</f>
+        <v/>
+      </c>
+      <c r="U95" s="25">
+        <f>T95-S95</f>
+        <v/>
+      </c>
+      <c r="V95" s="31" t="inlineStr"/>
     </row>
     <row r="96" ht="20" customHeight="1">
       <c r="B96" s="20" t="inlineStr">
@@ -7297,46 +7649,50 @@
         <f>G96-F96</f>
         <v/>
       </c>
-      <c r="I96" s="26">
+      <c r="I96" s="23">
+        <f>ABS(G96-F96)</f>
+        <v/>
+      </c>
+      <c r="J96" s="26">
         <f>IF(F96&gt;0, G96/F96, IF(G96&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J96" s="27">
-        <f>IF(F96=0, IF(G96=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G96-F96)/F96))</f>
-        <v/>
-      </c>
-      <c r="K96" s="28" t="inlineStr"/>
-      <c r="L96" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M96" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N96" s="29" t="n">
+      <c r="K96" s="27">
+        <f>IF(F96&gt;0, 1.0 - (I96/F96), IF(G96=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L96" s="28" t="inlineStr"/>
+      <c r="M96" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" s="29" t="n">
         <v>600</v>
       </c>
-      <c r="O96" s="30" t="n">
+      <c r="P96" s="30" t="n">
         <v>600</v>
       </c>
-      <c r="P96" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R96" s="23">
-        <f>L96+N96+P96</f>
-        <v/>
-      </c>
-      <c r="S96" s="24">
+      <c r="Q96" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" s="23">
         <f>M96+O96+Q96</f>
         <v/>
       </c>
-      <c r="T96" s="25">
-        <f>S96-R96</f>
-        <v/>
-      </c>
-      <c r="U96" s="31" t="inlineStr"/>
+      <c r="T96" s="24">
+        <f>N96+P96+R96</f>
+        <v/>
+      </c>
+      <c r="U96" s="25">
+        <f>T96-S96</f>
+        <v/>
+      </c>
+      <c r="V96" s="31" t="inlineStr"/>
     </row>
     <row r="97" ht="20" customHeight="1">
       <c r="B97" s="20" t="inlineStr">
@@ -7369,46 +7725,50 @@
         <f>G97-F97</f>
         <v/>
       </c>
-      <c r="I97" s="26">
+      <c r="I97" s="23">
+        <f>ABS(G97-F97)</f>
+        <v/>
+      </c>
+      <c r="J97" s="26">
         <f>IF(F97&gt;0, G97/F97, IF(G97&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J97" s="27">
-        <f>IF(F97=0, IF(G97=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G97-F97)/F97))</f>
-        <v/>
-      </c>
-      <c r="K97" s="28" t="inlineStr"/>
-      <c r="L97" s="29" t="n">
+      <c r="K97" s="27">
+        <f>IF(F97&gt;0, 1.0 - (I97/F97), IF(G97=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L97" s="28" t="inlineStr"/>
+      <c r="M97" s="29" t="n">
         <v>200</v>
       </c>
-      <c r="M97" s="30" t="n">
+      <c r="N97" s="30" t="n">
         <v>200</v>
       </c>
-      <c r="N97" s="29" t="n">
+      <c r="O97" s="29" t="n">
         <v>200</v>
       </c>
-      <c r="O97" s="30" t="n">
+      <c r="P97" s="30" t="n">
         <v>200</v>
       </c>
-      <c r="P97" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q97" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R97" s="23">
-        <f>L97+N97+P97</f>
-        <v/>
-      </c>
-      <c r="S97" s="24">
+      <c r="Q97" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" s="23">
         <f>M97+O97+Q97</f>
         <v/>
       </c>
-      <c r="T97" s="25">
-        <f>S97-R97</f>
-        <v/>
-      </c>
-      <c r="U97" s="31" t="inlineStr"/>
+      <c r="T97" s="24">
+        <f>N97+P97+R97</f>
+        <v/>
+      </c>
+      <c r="U97" s="25">
+        <f>T97-S97</f>
+        <v/>
+      </c>
+      <c r="V97" s="31" t="inlineStr"/>
     </row>
     <row r="98" ht="20" customHeight="1">
       <c r="B98" s="20" t="inlineStr">
@@ -7441,50 +7801,54 @@
         <f>G98-F98</f>
         <v/>
       </c>
-      <c r="I98" s="26">
+      <c r="I98" s="23">
+        <f>ABS(G98-F98)</f>
+        <v/>
+      </c>
+      <c r="J98" s="26">
         <f>IF(F98&gt;0, G98/F98, IF(G98&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J98" s="27">
-        <f>IF(F98=0, IF(G98=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G98-F98)/F98))</f>
-        <v/>
-      </c>
-      <c r="K98" s="28" t="inlineStr">
+      <c r="K98" s="27">
+        <f>IF(F98&gt;0, 1.0 - (I98/F98), IF(G98=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L98" s="28" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
       </c>
-      <c r="L98" s="29" t="n">
+      <c r="M98" s="29" t="n">
         <v>640</v>
       </c>
-      <c r="M98" s="30" t="n">
+      <c r="N98" s="30" t="n">
         <v>640</v>
       </c>
-      <c r="N98" s="29" t="n">
+      <c r="O98" s="29" t="n">
         <v>640</v>
       </c>
-      <c r="O98" s="30" t="n">
+      <c r="P98" s="30" t="n">
         <v>640</v>
       </c>
-      <c r="P98" s="29" t="n">
+      <c r="Q98" s="29" t="n">
         <v>640</v>
       </c>
-      <c r="Q98" s="30" t="n">
+      <c r="R98" s="30" t="n">
         <v>640</v>
       </c>
-      <c r="R98" s="23">
-        <f>L98+N98+P98</f>
-        <v/>
-      </c>
-      <c r="S98" s="24">
+      <c r="S98" s="23">
         <f>M98+O98+Q98</f>
         <v/>
       </c>
-      <c r="T98" s="25">
-        <f>S98-R98</f>
-        <v/>
-      </c>
-      <c r="U98" s="31" t="inlineStr"/>
+      <c r="T98" s="24">
+        <f>N98+P98+R98</f>
+        <v/>
+      </c>
+      <c r="U98" s="25">
+        <f>T98-S98</f>
+        <v/>
+      </c>
+      <c r="V98" s="31" t="inlineStr"/>
     </row>
     <row r="99" ht="20" customHeight="1">
       <c r="B99" s="20" t="inlineStr">
@@ -7517,46 +7881,50 @@
         <f>G99-F99</f>
         <v/>
       </c>
-      <c r="I99" s="26">
+      <c r="I99" s="23">
+        <f>ABS(G99-F99)</f>
+        <v/>
+      </c>
+      <c r="J99" s="26">
         <f>IF(F99&gt;0, G99/F99, IF(G99&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J99" s="27">
-        <f>IF(F99=0, IF(G99=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G99-F99)/F99))</f>
-        <v/>
-      </c>
-      <c r="K99" s="28" t="inlineStr"/>
-      <c r="L99" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" s="29" t="n">
+      <c r="K99" s="27">
+        <f>IF(F99&gt;0, 1.0 - (I99/F99), IF(G99=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L99" s="28" t="inlineStr"/>
+      <c r="M99" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="29" t="n">
         <v>50</v>
       </c>
-      <c r="O99" s="30" t="n">
+      <c r="P99" s="30" t="n">
         <v>50</v>
       </c>
-      <c r="P99" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q99" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R99" s="23">
-        <f>L99+N99+P99</f>
-        <v/>
-      </c>
-      <c r="S99" s="24">
+      <c r="Q99" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" s="23">
         <f>M99+O99+Q99</f>
         <v/>
       </c>
-      <c r="T99" s="25">
-        <f>S99-R99</f>
-        <v/>
-      </c>
-      <c r="U99" s="31" t="inlineStr"/>
+      <c r="T99" s="24">
+        <f>N99+P99+R99</f>
+        <v/>
+      </c>
+      <c r="U99" s="25">
+        <f>T99-S99</f>
+        <v/>
+      </c>
+      <c r="V99" s="31" t="inlineStr"/>
     </row>
     <row r="100" ht="20" customHeight="1">
       <c r="B100" s="20" t="inlineStr">
@@ -7589,46 +7957,50 @@
         <f>G100-F100</f>
         <v/>
       </c>
-      <c r="I100" s="26">
+      <c r="I100" s="23">
+        <f>ABS(G100-F100)</f>
+        <v/>
+      </c>
+      <c r="J100" s="26">
         <f>IF(F100&gt;0, G100/F100, IF(G100&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J100" s="27">
-        <f>IF(F100=0, IF(G100=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G100-F100)/F100))</f>
-        <v/>
-      </c>
-      <c r="K100" s="28" t="inlineStr"/>
-      <c r="L100" s="29" t="n">
+      <c r="K100" s="27">
+        <f>IF(F100&gt;0, 1.0 - (I100/F100), IF(G100=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L100" s="28" t="inlineStr"/>
+      <c r="M100" s="29" t="n">
         <v>100</v>
       </c>
-      <c r="M100" s="30" t="n">
+      <c r="N100" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="N100" s="29" t="n">
+      <c r="O100" s="29" t="n">
         <v>100</v>
       </c>
-      <c r="O100" s="30" t="n">
+      <c r="P100" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="P100" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R100" s="23">
-        <f>L100+N100+P100</f>
-        <v/>
-      </c>
-      <c r="S100" s="24">
+      <c r="Q100" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" s="23">
         <f>M100+O100+Q100</f>
         <v/>
       </c>
-      <c r="T100" s="25">
-        <f>S100-R100</f>
-        <v/>
-      </c>
-      <c r="U100" s="31" t="inlineStr"/>
+      <c r="T100" s="24">
+        <f>N100+P100+R100</f>
+        <v/>
+      </c>
+      <c r="U100" s="25">
+        <f>T100-S100</f>
+        <v/>
+      </c>
+      <c r="V100" s="31" t="inlineStr"/>
     </row>
     <row r="101" ht="20" customHeight="1">
       <c r="B101" s="20" t="inlineStr">
@@ -7661,46 +8033,50 @@
         <f>G101-F101</f>
         <v/>
       </c>
-      <c r="I101" s="26">
+      <c r="I101" s="23">
+        <f>ABS(G101-F101)</f>
+        <v/>
+      </c>
+      <c r="J101" s="26">
         <f>IF(F101&gt;0, G101/F101, IF(G101&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J101" s="27">
-        <f>IF(F101=0, IF(G101=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G101-F101)/F101))</f>
-        <v/>
-      </c>
-      <c r="K101" s="28" t="inlineStr"/>
-      <c r="L101" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N101" s="29" t="n">
+      <c r="K101" s="27">
+        <f>IF(F101&gt;0, 1.0 - (I101/F101), IF(G101=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L101" s="28" t="inlineStr"/>
+      <c r="M101" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" s="29" t="n">
         <v>12</v>
       </c>
-      <c r="O101" s="30" t="n">
+      <c r="P101" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="P101" s="29" t="n">
+      <c r="Q101" s="29" t="n">
         <v>12</v>
       </c>
-      <c r="Q101" s="30" t="n">
+      <c r="R101" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="R101" s="23">
-        <f>L101+N101+P101</f>
-        <v/>
-      </c>
-      <c r="S101" s="24">
+      <c r="S101" s="23">
         <f>M101+O101+Q101</f>
         <v/>
       </c>
-      <c r="T101" s="25">
-        <f>S101-R101</f>
-        <v/>
-      </c>
-      <c r="U101" s="31" t="inlineStr"/>
+      <c r="T101" s="24">
+        <f>N101+P101+R101</f>
+        <v/>
+      </c>
+      <c r="U101" s="25">
+        <f>T101-S101</f>
+        <v/>
+      </c>
+      <c r="V101" s="31" t="inlineStr"/>
     </row>
     <row r="102" ht="20" customHeight="1">
       <c r="B102" s="20" t="inlineStr">
@@ -7733,46 +8109,50 @@
         <f>G102-F102</f>
         <v/>
       </c>
-      <c r="I102" s="26">
+      <c r="I102" s="23">
+        <f>ABS(G102-F102)</f>
+        <v/>
+      </c>
+      <c r="J102" s="26">
         <f>IF(F102&gt;0, G102/F102, IF(G102&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J102" s="27">
-        <f>IF(F102=0, IF(G102=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G102-F102)/F102))</f>
-        <v/>
-      </c>
-      <c r="K102" s="28" t="inlineStr"/>
-      <c r="L102" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M102" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N102" s="29" t="n">
+      <c r="K102" s="27">
+        <f>IF(F102&gt;0, 1.0 - (I102/F102), IF(G102=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L102" s="28" t="inlineStr"/>
+      <c r="M102" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" s="29" t="n">
         <v>20</v>
       </c>
-      <c r="O102" s="30" t="n">
+      <c r="P102" s="30" t="n">
         <v>20</v>
       </c>
-      <c r="P102" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R102" s="23">
-        <f>L102+N102+P102</f>
-        <v/>
-      </c>
-      <c r="S102" s="24">
+      <c r="Q102" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" s="23">
         <f>M102+O102+Q102</f>
         <v/>
       </c>
-      <c r="T102" s="25">
-        <f>S102-R102</f>
-        <v/>
-      </c>
-      <c r="U102" s="31" t="inlineStr"/>
+      <c r="T102" s="24">
+        <f>N102+P102+R102</f>
+        <v/>
+      </c>
+      <c r="U102" s="25">
+        <f>T102-S102</f>
+        <v/>
+      </c>
+      <c r="V102" s="31" t="inlineStr"/>
     </row>
     <row r="103" ht="20" customHeight="1">
       <c r="B103" s="20" t="inlineStr">
@@ -7805,46 +8185,50 @@
         <f>G103-F103</f>
         <v/>
       </c>
-      <c r="I103" s="26">
+      <c r="I103" s="23">
+        <f>ABS(G103-F103)</f>
+        <v/>
+      </c>
+      <c r="J103" s="26">
         <f>IF(F103&gt;0, G103/F103, IF(G103&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J103" s="27">
-        <f>IF(F103=0, IF(G103=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G103-F103)/F103))</f>
-        <v/>
-      </c>
-      <c r="K103" s="28" t="inlineStr"/>
-      <c r="L103" s="29" t="n">
+      <c r="K103" s="27">
+        <f>IF(F103&gt;0, 1.0 - (I103/F103), IF(G103=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L103" s="28" t="inlineStr"/>
+      <c r="M103" s="29" t="n">
         <v>300</v>
       </c>
-      <c r="M103" s="30" t="n">
+      <c r="N103" s="30" t="n">
         <v>300</v>
       </c>
-      <c r="N103" s="29" t="n">
+      <c r="O103" s="29" t="n">
         <v>300</v>
       </c>
-      <c r="O103" s="30" t="n">
+      <c r="P103" s="30" t="n">
         <v>300</v>
       </c>
-      <c r="P103" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q103" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R103" s="23">
-        <f>L103+N103+P103</f>
-        <v/>
-      </c>
-      <c r="S103" s="24">
+      <c r="Q103" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" s="23">
         <f>M103+O103+Q103</f>
         <v/>
       </c>
-      <c r="T103" s="25">
-        <f>S103-R103</f>
-        <v/>
-      </c>
-      <c r="U103" s="31" t="inlineStr"/>
+      <c r="T103" s="24">
+        <f>N103+P103+R103</f>
+        <v/>
+      </c>
+      <c r="U103" s="25">
+        <f>T103-S103</f>
+        <v/>
+      </c>
+      <c r="V103" s="31" t="inlineStr"/>
     </row>
     <row r="104" ht="20" customHeight="1">
       <c r="B104" s="20" t="inlineStr">
@@ -7877,46 +8261,50 @@
         <f>G104-F104</f>
         <v/>
       </c>
-      <c r="I104" s="26">
+      <c r="I104" s="23">
+        <f>ABS(G104-F104)</f>
+        <v/>
+      </c>
+      <c r="J104" s="26">
         <f>IF(F104&gt;0, G104/F104, IF(G104&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J104" s="27">
-        <f>IF(F104=0, IF(G104=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G104-F104)/F104))</f>
-        <v/>
-      </c>
-      <c r="K104" s="28" t="inlineStr"/>
-      <c r="L104" s="29" t="n">
+      <c r="K104" s="27">
+        <f>IF(F104&gt;0, 1.0 - (I104/F104), IF(G104=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L104" s="28" t="inlineStr"/>
+      <c r="M104" s="29" t="n">
         <v>600</v>
       </c>
-      <c r="M104" s="30" t="n">
+      <c r="N104" s="30" t="n">
         <v>600</v>
       </c>
-      <c r="N104" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O104" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P104" s="29" t="n">
+      <c r="O104" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q104" s="29" t="n">
         <v>600</v>
       </c>
-      <c r="Q104" s="30" t="n">
+      <c r="R104" s="30" t="n">
         <v>600</v>
       </c>
-      <c r="R104" s="23">
-        <f>L104+N104+P104</f>
-        <v/>
-      </c>
-      <c r="S104" s="24">
+      <c r="S104" s="23">
         <f>M104+O104+Q104</f>
         <v/>
       </c>
-      <c r="T104" s="25">
-        <f>S104-R104</f>
-        <v/>
-      </c>
-      <c r="U104" s="31" t="inlineStr"/>
+      <c r="T104" s="24">
+        <f>N104+P104+R104</f>
+        <v/>
+      </c>
+      <c r="U104" s="25">
+        <f>T104-S104</f>
+        <v/>
+      </c>
+      <c r="V104" s="31" t="inlineStr"/>
     </row>
     <row r="105" ht="20" customHeight="1">
       <c r="B105" s="20" t="inlineStr">
@@ -7949,50 +8337,54 @@
         <f>G105-F105</f>
         <v/>
       </c>
-      <c r="I105" s="26">
+      <c r="I105" s="23">
+        <f>ABS(G105-F105)</f>
+        <v/>
+      </c>
+      <c r="J105" s="26">
         <f>IF(F105&gt;0, G105/F105, IF(G105&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J105" s="27">
-        <f>IF(F105=0, IF(G105=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G105-F105)/F105))</f>
-        <v/>
-      </c>
-      <c r="K105" s="28" t="inlineStr">
+      <c r="K105" s="27">
+        <f>IF(F105&gt;0, 1.0 - (I105/F105), IF(G105=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L105" s="28" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
       </c>
-      <c r="L105" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M105" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N105" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O105" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P105" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q105" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R105" s="23">
-        <f>L105+N105+P105</f>
-        <v/>
-      </c>
-      <c r="S105" s="24">
+      <c r="M105" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q105" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" s="23">
         <f>M105+O105+Q105</f>
         <v/>
       </c>
-      <c r="T105" s="25">
-        <f>S105-R105</f>
-        <v/>
-      </c>
-      <c r="U105" s="31" t="inlineStr"/>
+      <c r="T105" s="24">
+        <f>N105+P105+R105</f>
+        <v/>
+      </c>
+      <c r="U105" s="25">
+        <f>T105-S105</f>
+        <v/>
+      </c>
+      <c r="V105" s="31" t="inlineStr"/>
     </row>
     <row r="106" ht="20" customHeight="1">
       <c r="B106" s="20" t="inlineStr">
@@ -8025,50 +8417,54 @@
         <f>G106-F106</f>
         <v/>
       </c>
-      <c r="I106" s="26">
+      <c r="I106" s="23">
+        <f>ABS(G106-F106)</f>
+        <v/>
+      </c>
+      <c r="J106" s="26">
         <f>IF(F106&gt;0, G106/F106, IF(G106&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J106" s="27">
-        <f>IF(F106=0, IF(G106=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G106-F106)/F106))</f>
-        <v/>
-      </c>
-      <c r="K106" s="28" t="inlineStr">
+      <c r="K106" s="27">
+        <f>IF(F106&gt;0, 1.0 - (I106/F106), IF(G106=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L106" s="28" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
       </c>
-      <c r="L106" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M106" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N106" s="29" t="n">
+      <c r="M106" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" s="29" t="n">
         <v>300</v>
       </c>
-      <c r="O106" s="30" t="n">
+      <c r="P106" s="30" t="n">
         <v>300</v>
       </c>
-      <c r="P106" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q106" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R106" s="23">
-        <f>L106+N106+P106</f>
-        <v/>
-      </c>
-      <c r="S106" s="24">
+      <c r="Q106" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" s="23">
         <f>M106+O106+Q106</f>
         <v/>
       </c>
-      <c r="T106" s="25">
-        <f>S106-R106</f>
-        <v/>
-      </c>
-      <c r="U106" s="31" t="inlineStr"/>
+      <c r="T106" s="24">
+        <f>N106+P106+R106</f>
+        <v/>
+      </c>
+      <c r="U106" s="25">
+        <f>T106-S106</f>
+        <v/>
+      </c>
+      <c r="V106" s="31" t="inlineStr"/>
     </row>
     <row r="107" ht="20" customHeight="1">
       <c r="B107" s="20" t="inlineStr">
@@ -8101,46 +8497,50 @@
         <f>G107-F107</f>
         <v/>
       </c>
-      <c r="I107" s="26">
+      <c r="I107" s="23">
+        <f>ABS(G107-F107)</f>
+        <v/>
+      </c>
+      <c r="J107" s="26">
         <f>IF(F107&gt;0, G107/F107, IF(G107&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J107" s="27">
-        <f>IF(F107=0, IF(G107=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G107-F107)/F107))</f>
-        <v/>
-      </c>
-      <c r="K107" s="28" t="inlineStr"/>
-      <c r="L107" s="29" t="n">
+      <c r="K107" s="27">
+        <f>IF(F107&gt;0, 1.0 - (I107/F107), IF(G107=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L107" s="28" t="inlineStr"/>
+      <c r="M107" s="29" t="n">
         <v>300</v>
       </c>
-      <c r="M107" s="30" t="n">
+      <c r="N107" s="30" t="n">
         <v>300</v>
       </c>
-      <c r="N107" s="29" t="n">
+      <c r="O107" s="29" t="n">
         <v>300</v>
       </c>
-      <c r="O107" s="30" t="n">
+      <c r="P107" s="30" t="n">
         <v>300</v>
       </c>
-      <c r="P107" s="29" t="n">
+      <c r="Q107" s="29" t="n">
         <v>300</v>
       </c>
-      <c r="Q107" s="30" t="n">
+      <c r="R107" s="30" t="n">
         <v>300</v>
       </c>
-      <c r="R107" s="23">
-        <f>L107+N107+P107</f>
-        <v/>
-      </c>
-      <c r="S107" s="24">
+      <c r="S107" s="23">
         <f>M107+O107+Q107</f>
         <v/>
       </c>
-      <c r="T107" s="25">
-        <f>S107-R107</f>
-        <v/>
-      </c>
-      <c r="U107" s="31" t="inlineStr"/>
+      <c r="T107" s="24">
+        <f>N107+P107+R107</f>
+        <v/>
+      </c>
+      <c r="U107" s="25">
+        <f>T107-S107</f>
+        <v/>
+      </c>
+      <c r="V107" s="31" t="inlineStr"/>
     </row>
     <row r="108" ht="20" customHeight="1">
       <c r="B108" s="20" t="inlineStr">
@@ -8173,46 +8573,50 @@
         <f>G108-F108</f>
         <v/>
       </c>
-      <c r="I108" s="26">
+      <c r="I108" s="23">
+        <f>ABS(G108-F108)</f>
+        <v/>
+      </c>
+      <c r="J108" s="26">
         <f>IF(F108&gt;0, G108/F108, IF(G108&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J108" s="27">
-        <f>IF(F108=0, IF(G108=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G108-F108)/F108))</f>
-        <v/>
-      </c>
-      <c r="K108" s="28" t="inlineStr"/>
-      <c r="L108" s="29" t="n">
+      <c r="K108" s="27">
+        <f>IF(F108&gt;0, 1.0 - (I108/F108), IF(G108=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L108" s="28" t="inlineStr"/>
+      <c r="M108" s="29" t="n">
         <v>100</v>
       </c>
-      <c r="M108" s="30" t="n">
+      <c r="N108" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="N108" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O108" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P108" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q108" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R108" s="23">
-        <f>L108+N108+P108</f>
-        <v/>
-      </c>
-      <c r="S108" s="24">
+      <c r="O108" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" s="23">
         <f>M108+O108+Q108</f>
         <v/>
       </c>
-      <c r="T108" s="25">
-        <f>S108-R108</f>
-        <v/>
-      </c>
-      <c r="U108" s="31" t="inlineStr"/>
+      <c r="T108" s="24">
+        <f>N108+P108+R108</f>
+        <v/>
+      </c>
+      <c r="U108" s="25">
+        <f>T108-S108</f>
+        <v/>
+      </c>
+      <c r="V108" s="31" t="inlineStr"/>
     </row>
     <row r="109" ht="20" customHeight="1">
       <c r="B109" s="20" t="inlineStr">
@@ -8245,46 +8649,50 @@
         <f>G109-F109</f>
         <v/>
       </c>
-      <c r="I109" s="26">
+      <c r="I109" s="23">
+        <f>ABS(G109-F109)</f>
+        <v/>
+      </c>
+      <c r="J109" s="26">
         <f>IF(F109&gt;0, G109/F109, IF(G109&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J109" s="27">
-        <f>IF(F109=0, IF(G109=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G109-F109)/F109))</f>
-        <v/>
-      </c>
-      <c r="K109" s="28" t="inlineStr"/>
-      <c r="L109" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M109" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N109" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O109" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P109" s="29" t="n">
+      <c r="K109" s="27">
+        <f>IF(F109&gt;0, 1.0 - (I109/F109), IF(G109=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L109" s="28" t="inlineStr"/>
+      <c r="M109" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" s="29" t="n">
         <v>3000</v>
       </c>
-      <c r="Q109" s="30" t="n">
+      <c r="R109" s="30" t="n">
         <v>3000</v>
       </c>
-      <c r="R109" s="23">
-        <f>L109+N109+P109</f>
-        <v/>
-      </c>
-      <c r="S109" s="24">
+      <c r="S109" s="23">
         <f>M109+O109+Q109</f>
         <v/>
       </c>
-      <c r="T109" s="25">
-        <f>S109-R109</f>
-        <v/>
-      </c>
-      <c r="U109" s="31" t="inlineStr"/>
+      <c r="T109" s="24">
+        <f>N109+P109+R109</f>
+        <v/>
+      </c>
+      <c r="U109" s="25">
+        <f>T109-S109</f>
+        <v/>
+      </c>
+      <c r="V109" s="31" t="inlineStr"/>
     </row>
     <row r="110" ht="20" customHeight="1">
       <c r="B110" s="20" t="inlineStr">
@@ -8317,50 +8725,54 @@
         <f>G110-F110</f>
         <v/>
       </c>
-      <c r="I110" s="26">
+      <c r="I110" s="23">
+        <f>ABS(G110-F110)</f>
+        <v/>
+      </c>
+      <c r="J110" s="26">
         <f>IF(F110&gt;0, G110/F110, IF(G110&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J110" s="27">
-        <f>IF(F110=0, IF(G110=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G110-F110)/F110))</f>
-        <v/>
-      </c>
-      <c r="K110" s="28" t="inlineStr">
+      <c r="K110" s="27">
+        <f>IF(F110&gt;0, 1.0 - (I110/F110), IF(G110=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L110" s="28" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
       </c>
-      <c r="L110" s="29" t="n">
+      <c r="M110" s="29" t="n">
         <v>200</v>
       </c>
-      <c r="M110" s="30" t="n">
+      <c r="N110" s="30" t="n">
         <v>200</v>
       </c>
-      <c r="N110" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O110" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P110" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q110" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R110" s="23">
-        <f>L110+N110+P110</f>
-        <v/>
-      </c>
-      <c r="S110" s="24">
+      <c r="O110" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q110" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S110" s="23">
         <f>M110+O110+Q110</f>
         <v/>
       </c>
-      <c r="T110" s="25">
-        <f>S110-R110</f>
-        <v/>
-      </c>
-      <c r="U110" s="31" t="inlineStr"/>
+      <c r="T110" s="24">
+        <f>N110+P110+R110</f>
+        <v/>
+      </c>
+      <c r="U110" s="25">
+        <f>T110-S110</f>
+        <v/>
+      </c>
+      <c r="V110" s="31" t="inlineStr"/>
     </row>
     <row r="111" ht="20" customHeight="1">
       <c r="B111" s="20" t="inlineStr">
@@ -8393,46 +8805,50 @@
         <f>G111-F111</f>
         <v/>
       </c>
-      <c r="I111" s="26">
+      <c r="I111" s="23">
+        <f>ABS(G111-F111)</f>
+        <v/>
+      </c>
+      <c r="J111" s="26">
         <f>IF(F111&gt;0, G111/F111, IF(G111&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J111" s="27">
-        <f>IF(F111=0, IF(G111=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G111-F111)/F111))</f>
-        <v/>
-      </c>
-      <c r="K111" s="28" t="inlineStr"/>
-      <c r="L111" s="29" t="n">
+      <c r="K111" s="27">
+        <f>IF(F111&gt;0, 1.0 - (I111/F111), IF(G111=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L111" s="28" t="inlineStr"/>
+      <c r="M111" s="29" t="n">
         <v>2000</v>
       </c>
-      <c r="M111" s="30" t="n">
+      <c r="N111" s="30" t="n">
         <v>2000</v>
       </c>
-      <c r="N111" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O111" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P111" s="29" t="n">
+      <c r="O111" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q111" s="29" t="n">
         <v>1000</v>
       </c>
-      <c r="Q111" s="30" t="n">
+      <c r="R111" s="30" t="n">
         <v>1000</v>
       </c>
-      <c r="R111" s="23">
-        <f>L111+N111+P111</f>
-        <v/>
-      </c>
-      <c r="S111" s="24">
+      <c r="S111" s="23">
         <f>M111+O111+Q111</f>
         <v/>
       </c>
-      <c r="T111" s="25">
-        <f>S111-R111</f>
-        <v/>
-      </c>
-      <c r="U111" s="31" t="inlineStr"/>
+      <c r="T111" s="24">
+        <f>N111+P111+R111</f>
+        <v/>
+      </c>
+      <c r="U111" s="25">
+        <f>T111-S111</f>
+        <v/>
+      </c>
+      <c r="V111" s="31" t="inlineStr"/>
     </row>
     <row r="112" ht="20" customHeight="1">
       <c r="B112" s="20" t="inlineStr">
@@ -8465,46 +8881,50 @@
         <f>G112-F112</f>
         <v/>
       </c>
-      <c r="I112" s="26">
+      <c r="I112" s="23">
+        <f>ABS(G112-F112)</f>
+        <v/>
+      </c>
+      <c r="J112" s="26">
         <f>IF(F112&gt;0, G112/F112, IF(G112&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J112" s="27">
-        <f>IF(F112=0, IF(G112=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G112-F112)/F112))</f>
-        <v/>
-      </c>
-      <c r="K112" s="28" t="inlineStr"/>
-      <c r="L112" s="29" t="n">
+      <c r="K112" s="27">
+        <f>IF(F112&gt;0, 1.0 - (I112/F112), IF(G112=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L112" s="28" t="inlineStr"/>
+      <c r="M112" s="29" t="n">
         <v>600</v>
       </c>
-      <c r="M112" s="30" t="n">
+      <c r="N112" s="30" t="n">
         <v>600</v>
       </c>
-      <c r="N112" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O112" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P112" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q112" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R112" s="23">
-        <f>L112+N112+P112</f>
-        <v/>
-      </c>
-      <c r="S112" s="24">
+      <c r="O112" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q112" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R112" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" s="23">
         <f>M112+O112+Q112</f>
         <v/>
       </c>
-      <c r="T112" s="25">
-        <f>S112-R112</f>
-        <v/>
-      </c>
-      <c r="U112" s="31" t="inlineStr"/>
+      <c r="T112" s="24">
+        <f>N112+P112+R112</f>
+        <v/>
+      </c>
+      <c r="U112" s="25">
+        <f>T112-S112</f>
+        <v/>
+      </c>
+      <c r="V112" s="31" t="inlineStr"/>
     </row>
     <row r="113" ht="20" customHeight="1">
       <c r="B113" s="20" t="inlineStr">
@@ -8537,46 +8957,50 @@
         <f>G113-F113</f>
         <v/>
       </c>
-      <c r="I113" s="26">
+      <c r="I113" s="23">
+        <f>ABS(G113-F113)</f>
+        <v/>
+      </c>
+      <c r="J113" s="26">
         <f>IF(F113&gt;0, G113/F113, IF(G113&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J113" s="27">
-        <f>IF(F113=0, IF(G113=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G113-F113)/F113))</f>
-        <v/>
-      </c>
-      <c r="K113" s="28" t="inlineStr"/>
-      <c r="L113" s="29" t="n">
+      <c r="K113" s="27">
+        <f>IF(F113&gt;0, 1.0 - (I113/F113), IF(G113=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L113" s="28" t="inlineStr"/>
+      <c r="M113" s="29" t="n">
         <v>5000</v>
       </c>
-      <c r="M113" s="30" t="n">
+      <c r="N113" s="30" t="n">
         <v>5000</v>
       </c>
-      <c r="N113" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O113" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P113" s="29" t="n">
+      <c r="O113" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" s="29" t="n">
         <v>5000</v>
       </c>
-      <c r="Q113" s="30" t="n">
+      <c r="R113" s="30" t="n">
         <v>5000</v>
       </c>
-      <c r="R113" s="23">
-        <f>L113+N113+P113</f>
-        <v/>
-      </c>
-      <c r="S113" s="24">
+      <c r="S113" s="23">
         <f>M113+O113+Q113</f>
         <v/>
       </c>
-      <c r="T113" s="25">
-        <f>S113-R113</f>
-        <v/>
-      </c>
-      <c r="U113" s="31" t="inlineStr"/>
+      <c r="T113" s="24">
+        <f>N113+P113+R113</f>
+        <v/>
+      </c>
+      <c r="U113" s="25">
+        <f>T113-S113</f>
+        <v/>
+      </c>
+      <c r="V113" s="31" t="inlineStr"/>
     </row>
     <row r="114" ht="20" customHeight="1">
       <c r="B114" s="20" t="inlineStr">
@@ -8609,46 +9033,50 @@
         <f>G114-F114</f>
         <v/>
       </c>
-      <c r="I114" s="26">
+      <c r="I114" s="23">
+        <f>ABS(G114-F114)</f>
+        <v/>
+      </c>
+      <c r="J114" s="26">
         <f>IF(F114&gt;0, G114/F114, IF(G114&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J114" s="27">
-        <f>IF(F114=0, IF(G114=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G114-F114)/F114))</f>
-        <v/>
-      </c>
-      <c r="K114" s="28" t="inlineStr"/>
-      <c r="L114" s="29" t="n">
+      <c r="K114" s="27">
+        <f>IF(F114&gt;0, 1.0 - (I114/F114), IF(G114=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L114" s="28" t="inlineStr"/>
+      <c r="M114" s="29" t="n">
         <v>5000</v>
       </c>
-      <c r="M114" s="30" t="n">
+      <c r="N114" s="30" t="n">
         <v>5000</v>
       </c>
-      <c r="N114" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O114" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P114" s="29" t="n">
+      <c r="O114" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P114" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q114" s="29" t="n">
         <v>5000</v>
       </c>
-      <c r="Q114" s="30" t="n">
+      <c r="R114" s="30" t="n">
         <v>5000</v>
       </c>
-      <c r="R114" s="23">
-        <f>L114+N114+P114</f>
-        <v/>
-      </c>
-      <c r="S114" s="24">
+      <c r="S114" s="23">
         <f>M114+O114+Q114</f>
         <v/>
       </c>
-      <c r="T114" s="25">
-        <f>S114-R114</f>
-        <v/>
-      </c>
-      <c r="U114" s="31" t="inlineStr"/>
+      <c r="T114" s="24">
+        <f>N114+P114+R114</f>
+        <v/>
+      </c>
+      <c r="U114" s="25">
+        <f>T114-S114</f>
+        <v/>
+      </c>
+      <c r="V114" s="31" t="inlineStr"/>
     </row>
     <row r="115" ht="20" customHeight="1">
       <c r="B115" s="20" t="inlineStr">
@@ -8681,46 +9109,50 @@
         <f>G115-F115</f>
         <v/>
       </c>
-      <c r="I115" s="26">
+      <c r="I115" s="23">
+        <f>ABS(G115-F115)</f>
+        <v/>
+      </c>
+      <c r="J115" s="26">
         <f>IF(F115&gt;0, G115/F115, IF(G115&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J115" s="27">
-        <f>IF(F115=0, IF(G115=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G115-F115)/F115))</f>
-        <v/>
-      </c>
-      <c r="K115" s="28" t="inlineStr"/>
-      <c r="L115" s="29" t="n">
+      <c r="K115" s="27">
+        <f>IF(F115&gt;0, 1.0 - (I115/F115), IF(G115=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L115" s="28" t="inlineStr"/>
+      <c r="M115" s="29" t="n">
         <v>3000</v>
       </c>
-      <c r="M115" s="30" t="n">
+      <c r="N115" s="30" t="n">
         <v>3000</v>
       </c>
-      <c r="N115" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O115" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P115" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q115" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R115" s="23">
-        <f>L115+N115+P115</f>
-        <v/>
-      </c>
-      <c r="S115" s="24">
+      <c r="O115" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R115" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" s="23">
         <f>M115+O115+Q115</f>
         <v/>
       </c>
-      <c r="T115" s="25">
-        <f>S115-R115</f>
-        <v/>
-      </c>
-      <c r="U115" s="31" t="inlineStr"/>
+      <c r="T115" s="24">
+        <f>N115+P115+R115</f>
+        <v/>
+      </c>
+      <c r="U115" s="25">
+        <f>T115-S115</f>
+        <v/>
+      </c>
+      <c r="V115" s="31" t="inlineStr"/>
     </row>
     <row r="116" ht="20" customHeight="1">
       <c r="B116" s="20" t="inlineStr">
@@ -8753,46 +9185,50 @@
         <f>G116-F116</f>
         <v/>
       </c>
-      <c r="I116" s="26">
+      <c r="I116" s="23">
+        <f>ABS(G116-F116)</f>
+        <v/>
+      </c>
+      <c r="J116" s="26">
         <f>IF(F116&gt;0, G116/F116, IF(G116&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J116" s="27">
-        <f>IF(F116=0, IF(G116=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G116-F116)/F116))</f>
-        <v/>
-      </c>
-      <c r="K116" s="28" t="inlineStr"/>
-      <c r="L116" s="29" t="n">
+      <c r="K116" s="27">
+        <f>IF(F116&gt;0, 1.0 - (I116/F116), IF(G116=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L116" s="28" t="inlineStr"/>
+      <c r="M116" s="29" t="n">
         <v>5000</v>
       </c>
-      <c r="M116" s="30" t="n">
+      <c r="N116" s="30" t="n">
         <v>5000</v>
       </c>
-      <c r="N116" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O116" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P116" s="29" t="n">
+      <c r="O116" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" s="29" t="n">
         <v>5000</v>
       </c>
-      <c r="Q116" s="30" t="n">
+      <c r="R116" s="30" t="n">
         <v>5000</v>
       </c>
-      <c r="R116" s="23">
-        <f>L116+N116+P116</f>
-        <v/>
-      </c>
-      <c r="S116" s="24">
+      <c r="S116" s="23">
         <f>M116+O116+Q116</f>
         <v/>
       </c>
-      <c r="T116" s="25">
-        <f>S116-R116</f>
-        <v/>
-      </c>
-      <c r="U116" s="31" t="inlineStr"/>
+      <c r="T116" s="24">
+        <f>N116+P116+R116</f>
+        <v/>
+      </c>
+      <c r="U116" s="25">
+        <f>T116-S116</f>
+        <v/>
+      </c>
+      <c r="V116" s="31" t="inlineStr"/>
     </row>
     <row r="117" ht="20" customHeight="1">
       <c r="B117" s="20" t="inlineStr">
@@ -8825,46 +9261,50 @@
         <f>G117-F117</f>
         <v/>
       </c>
-      <c r="I117" s="26">
+      <c r="I117" s="23">
+        <f>ABS(G117-F117)</f>
+        <v/>
+      </c>
+      <c r="J117" s="26">
         <f>IF(F117&gt;0, G117/F117, IF(G117&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J117" s="27">
-        <f>IF(F117=0, IF(G117=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G117-F117)/F117))</f>
-        <v/>
-      </c>
-      <c r="K117" s="28" t="inlineStr"/>
-      <c r="L117" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M117" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N117" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O117" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P117" s="29" t="n">
+      <c r="K117" s="27">
+        <f>IF(F117&gt;0, 1.0 - (I117/F117), IF(G117=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L117" s="28" t="inlineStr"/>
+      <c r="M117" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N117" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q117" s="29" t="n">
         <v>1000</v>
       </c>
-      <c r="Q117" s="30" t="n">
+      <c r="R117" s="30" t="n">
         <v>1000</v>
       </c>
-      <c r="R117" s="23">
-        <f>L117+N117+P117</f>
-        <v/>
-      </c>
-      <c r="S117" s="24">
+      <c r="S117" s="23">
         <f>M117+O117+Q117</f>
         <v/>
       </c>
-      <c r="T117" s="25">
-        <f>S117-R117</f>
-        <v/>
-      </c>
-      <c r="U117" s="31" t="inlineStr"/>
+      <c r="T117" s="24">
+        <f>N117+P117+R117</f>
+        <v/>
+      </c>
+      <c r="U117" s="25">
+        <f>T117-S117</f>
+        <v/>
+      </c>
+      <c r="V117" s="31" t="inlineStr"/>
     </row>
     <row r="118" ht="20" customHeight="1">
       <c r="B118" s="20" t="inlineStr">
@@ -8897,46 +9337,50 @@
         <f>G118-F118</f>
         <v/>
       </c>
-      <c r="I118" s="26">
+      <c r="I118" s="23">
+        <f>ABS(G118-F118)</f>
+        <v/>
+      </c>
+      <c r="J118" s="26">
         <f>IF(F118&gt;0, G118/F118, IF(G118&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J118" s="27">
-        <f>IF(F118=0, IF(G118=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G118-F118)/F118))</f>
-        <v/>
-      </c>
-      <c r="K118" s="28" t="inlineStr"/>
-      <c r="L118" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M118" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N118" s="29" t="n">
+      <c r="K118" s="27">
+        <f>IF(F118&gt;0, 1.0 - (I118/F118), IF(G118=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L118" s="28" t="inlineStr"/>
+      <c r="M118" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" s="29" t="n">
         <v>1000</v>
       </c>
-      <c r="O118" s="30" t="n">
+      <c r="P118" s="30" t="n">
         <v>1000</v>
       </c>
-      <c r="P118" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q118" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R118" s="23">
-        <f>L118+N118+P118</f>
-        <v/>
-      </c>
-      <c r="S118" s="24">
+      <c r="Q118" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R118" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" s="23">
         <f>M118+O118+Q118</f>
         <v/>
       </c>
-      <c r="T118" s="25">
-        <f>S118-R118</f>
-        <v/>
-      </c>
-      <c r="U118" s="31" t="inlineStr"/>
+      <c r="T118" s="24">
+        <f>N118+P118+R118</f>
+        <v/>
+      </c>
+      <c r="U118" s="25">
+        <f>T118-S118</f>
+        <v/>
+      </c>
+      <c r="V118" s="31" t="inlineStr"/>
     </row>
     <row r="119" ht="20" customHeight="1">
       <c r="B119" s="20" t="inlineStr">
@@ -8969,46 +9413,50 @@
         <f>G119-F119</f>
         <v/>
       </c>
-      <c r="I119" s="26">
+      <c r="I119" s="23">
+        <f>ABS(G119-F119)</f>
+        <v/>
+      </c>
+      <c r="J119" s="26">
         <f>IF(F119&gt;0, G119/F119, IF(G119&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J119" s="27">
-        <f>IF(F119=0, IF(G119=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G119-F119)/F119))</f>
-        <v/>
-      </c>
-      <c r="K119" s="28" t="inlineStr"/>
-      <c r="L119" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M119" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N119" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O119" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P119" s="29" t="n">
+      <c r="K119" s="27">
+        <f>IF(F119&gt;0, 1.0 - (I119/F119), IF(G119=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L119" s="28" t="inlineStr"/>
+      <c r="M119" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P119" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" s="29" t="n">
         <v>2000</v>
       </c>
-      <c r="Q119" s="30" t="n">
+      <c r="R119" s="30" t="n">
         <v>2000</v>
       </c>
-      <c r="R119" s="23">
-        <f>L119+N119+P119</f>
-        <v/>
-      </c>
-      <c r="S119" s="24">
+      <c r="S119" s="23">
         <f>M119+O119+Q119</f>
         <v/>
       </c>
-      <c r="T119" s="25">
-        <f>S119-R119</f>
-        <v/>
-      </c>
-      <c r="U119" s="31" t="inlineStr"/>
+      <c r="T119" s="24">
+        <f>N119+P119+R119</f>
+        <v/>
+      </c>
+      <c r="U119" s="25">
+        <f>T119-S119</f>
+        <v/>
+      </c>
+      <c r="V119" s="31" t="inlineStr"/>
     </row>
     <row r="120" ht="20" customHeight="1">
       <c r="B120" s="20" t="inlineStr">
@@ -9041,46 +9489,50 @@
         <f>G120-F120</f>
         <v/>
       </c>
-      <c r="I120" s="26">
+      <c r="I120" s="23">
+        <f>ABS(G120-F120)</f>
+        <v/>
+      </c>
+      <c r="J120" s="26">
         <f>IF(F120&gt;0, G120/F120, IF(G120&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J120" s="27">
-        <f>IF(F120=0, IF(G120=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G120-F120)/F120))</f>
-        <v/>
-      </c>
-      <c r="K120" s="28" t="inlineStr"/>
-      <c r="L120" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M120" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N120" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O120" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P120" s="29" t="n">
+      <c r="K120" s="27">
+        <f>IF(F120&gt;0, 1.0 - (I120/F120), IF(G120=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L120" s="28" t="inlineStr"/>
+      <c r="M120" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q120" s="29" t="n">
         <v>1000</v>
       </c>
-      <c r="Q120" s="30" t="n">
+      <c r="R120" s="30" t="n">
         <v>1000</v>
       </c>
-      <c r="R120" s="23">
-        <f>L120+N120+P120</f>
-        <v/>
-      </c>
-      <c r="S120" s="24">
+      <c r="S120" s="23">
         <f>M120+O120+Q120</f>
         <v/>
       </c>
-      <c r="T120" s="25">
-        <f>S120-R120</f>
-        <v/>
-      </c>
-      <c r="U120" s="31" t="inlineStr"/>
+      <c r="T120" s="24">
+        <f>N120+P120+R120</f>
+        <v/>
+      </c>
+      <c r="U120" s="25">
+        <f>T120-S120</f>
+        <v/>
+      </c>
+      <c r="V120" s="31" t="inlineStr"/>
     </row>
     <row r="121" ht="20" customHeight="1">
       <c r="B121" s="20" t="inlineStr">
@@ -9113,46 +9565,50 @@
         <f>G121-F121</f>
         <v/>
       </c>
-      <c r="I121" s="26">
+      <c r="I121" s="23">
+        <f>ABS(G121-F121)</f>
+        <v/>
+      </c>
+      <c r="J121" s="26">
         <f>IF(F121&gt;0, G121/F121, IF(G121&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J121" s="27">
-        <f>IF(F121=0, IF(G121=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G121-F121)/F121))</f>
-        <v/>
-      </c>
-      <c r="K121" s="28" t="inlineStr"/>
-      <c r="L121" s="29" t="n">
+      <c r="K121" s="27">
+        <f>IF(F121&gt;0, 1.0 - (I121/F121), IF(G121=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L121" s="28" t="inlineStr"/>
+      <c r="M121" s="29" t="n">
         <v>1600</v>
       </c>
-      <c r="M121" s="30" t="n">
+      <c r="N121" s="30" t="n">
         <v>1600</v>
       </c>
-      <c r="N121" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O121" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P121" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q121" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R121" s="23">
-        <f>L121+N121+P121</f>
-        <v/>
-      </c>
-      <c r="S121" s="24">
+      <c r="O121" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" s="23">
         <f>M121+O121+Q121</f>
         <v/>
       </c>
-      <c r="T121" s="25">
-        <f>S121-R121</f>
-        <v/>
-      </c>
-      <c r="U121" s="31" t="inlineStr"/>
+      <c r="T121" s="24">
+        <f>N121+P121+R121</f>
+        <v/>
+      </c>
+      <c r="U121" s="25">
+        <f>T121-S121</f>
+        <v/>
+      </c>
+      <c r="V121" s="31" t="inlineStr"/>
     </row>
     <row r="122" ht="20" customHeight="1">
       <c r="B122" s="20" t="inlineStr">
@@ -9185,46 +9641,50 @@
         <f>G122-F122</f>
         <v/>
       </c>
-      <c r="I122" s="26">
+      <c r="I122" s="23">
+        <f>ABS(G122-F122)</f>
+        <v/>
+      </c>
+      <c r="J122" s="26">
         <f>IF(F122&gt;0, G122/F122, IF(G122&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J122" s="27">
-        <f>IF(F122=0, IF(G122=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G122-F122)/F122))</f>
-        <v/>
-      </c>
-      <c r="K122" s="28" t="inlineStr"/>
-      <c r="L122" s="29" t="n">
+      <c r="K122" s="27">
+        <f>IF(F122&gt;0, 1.0 - (I122/F122), IF(G122=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L122" s="28" t="inlineStr"/>
+      <c r="M122" s="29" t="n">
         <v>600</v>
       </c>
-      <c r="M122" s="30" t="n">
+      <c r="N122" s="30" t="n">
         <v>600</v>
       </c>
-      <c r="N122" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O122" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P122" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q122" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R122" s="23">
-        <f>L122+N122+P122</f>
-        <v/>
-      </c>
-      <c r="S122" s="24">
+      <c r="O122" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" s="23">
         <f>M122+O122+Q122</f>
         <v/>
       </c>
-      <c r="T122" s="25">
-        <f>S122-R122</f>
-        <v/>
-      </c>
-      <c r="U122" s="31" t="inlineStr"/>
+      <c r="T122" s="24">
+        <f>N122+P122+R122</f>
+        <v/>
+      </c>
+      <c r="U122" s="25">
+        <f>T122-S122</f>
+        <v/>
+      </c>
+      <c r="V122" s="31" t="inlineStr"/>
     </row>
     <row r="123" ht="20" customHeight="1">
       <c r="B123" s="20" t="inlineStr">
@@ -9257,46 +9717,50 @@
         <f>G123-F123</f>
         <v/>
       </c>
-      <c r="I123" s="26">
+      <c r="I123" s="23">
+        <f>ABS(G123-F123)</f>
+        <v/>
+      </c>
+      <c r="J123" s="26">
         <f>IF(F123&gt;0, G123/F123, IF(G123&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J123" s="27">
-        <f>IF(F123=0, IF(G123=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G123-F123)/F123))</f>
-        <v/>
-      </c>
-      <c r="K123" s="28" t="inlineStr"/>
-      <c r="L123" s="29" t="n">
+      <c r="K123" s="27">
+        <f>IF(F123&gt;0, 1.0 - (I123/F123), IF(G123=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L123" s="28" t="inlineStr"/>
+      <c r="M123" s="29" t="n">
         <v>5000</v>
       </c>
-      <c r="M123" s="30" t="n">
+      <c r="N123" s="30" t="n">
         <v>5000</v>
       </c>
-      <c r="N123" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O123" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P123" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q123" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R123" s="23">
-        <f>L123+N123+P123</f>
-        <v/>
-      </c>
-      <c r="S123" s="24">
+      <c r="O123" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q123" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" s="23">
         <f>M123+O123+Q123</f>
         <v/>
       </c>
-      <c r="T123" s="25">
-        <f>S123-R123</f>
-        <v/>
-      </c>
-      <c r="U123" s="31" t="inlineStr"/>
+      <c r="T123" s="24">
+        <f>N123+P123+R123</f>
+        <v/>
+      </c>
+      <c r="U123" s="25">
+        <f>T123-S123</f>
+        <v/>
+      </c>
+      <c r="V123" s="31" t="inlineStr"/>
     </row>
     <row r="124" ht="20" customHeight="1">
       <c r="B124" s="20" t="inlineStr">
@@ -9329,46 +9793,50 @@
         <f>G124-F124</f>
         <v/>
       </c>
-      <c r="I124" s="26">
+      <c r="I124" s="23">
+        <f>ABS(G124-F124)</f>
+        <v/>
+      </c>
+      <c r="J124" s="26">
         <f>IF(F124&gt;0, G124/F124, IF(G124&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J124" s="27">
-        <f>IF(F124=0, IF(G124=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G124-F124)/F124))</f>
-        <v/>
-      </c>
-      <c r="K124" s="28" t="inlineStr"/>
-      <c r="L124" s="29" t="n">
+      <c r="K124" s="27">
+        <f>IF(F124&gt;0, 1.0 - (I124/F124), IF(G124=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L124" s="28" t="inlineStr"/>
+      <c r="M124" s="29" t="n">
         <v>2000</v>
       </c>
-      <c r="M124" s="30" t="n">
+      <c r="N124" s="30" t="n">
         <v>2000</v>
       </c>
-      <c r="N124" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O124" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P124" s="29" t="n">
+      <c r="O124" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" s="29" t="n">
         <v>2000</v>
       </c>
-      <c r="Q124" s="30" t="n">
+      <c r="R124" s="30" t="n">
         <v>2000</v>
       </c>
-      <c r="R124" s="23">
-        <f>L124+N124+P124</f>
-        <v/>
-      </c>
-      <c r="S124" s="24">
+      <c r="S124" s="23">
         <f>M124+O124+Q124</f>
         <v/>
       </c>
-      <c r="T124" s="25">
-        <f>S124-R124</f>
-        <v/>
-      </c>
-      <c r="U124" s="31" t="inlineStr"/>
+      <c r="T124" s="24">
+        <f>N124+P124+R124</f>
+        <v/>
+      </c>
+      <c r="U124" s="25">
+        <f>T124-S124</f>
+        <v/>
+      </c>
+      <c r="V124" s="31" t="inlineStr"/>
     </row>
     <row r="125" ht="20" customHeight="1">
       <c r="B125" s="20" t="inlineStr">
@@ -9401,46 +9869,50 @@
         <f>G125-F125</f>
         <v/>
       </c>
-      <c r="I125" s="26">
+      <c r="I125" s="23">
+        <f>ABS(G125-F125)</f>
+        <v/>
+      </c>
+      <c r="J125" s="26">
         <f>IF(F125&gt;0, G125/F125, IF(G125&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J125" s="27">
-        <f>IF(F125=0, IF(G125=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G125-F125)/F125))</f>
-        <v/>
-      </c>
-      <c r="K125" s="28" t="inlineStr"/>
-      <c r="L125" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M125" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N125" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O125" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P125" s="29" t="n">
+      <c r="K125" s="27">
+        <f>IF(F125&gt;0, 1.0 - (I125/F125), IF(G125=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L125" s="28" t="inlineStr"/>
+      <c r="M125" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" s="29" t="n">
         <v>1000</v>
       </c>
-      <c r="Q125" s="30" t="n">
+      <c r="R125" s="30" t="n">
         <v>1000</v>
       </c>
-      <c r="R125" s="23">
-        <f>L125+N125+P125</f>
-        <v/>
-      </c>
-      <c r="S125" s="24">
+      <c r="S125" s="23">
         <f>M125+O125+Q125</f>
         <v/>
       </c>
-      <c r="T125" s="25">
-        <f>S125-R125</f>
-        <v/>
-      </c>
-      <c r="U125" s="31" t="inlineStr"/>
+      <c r="T125" s="24">
+        <f>N125+P125+R125</f>
+        <v/>
+      </c>
+      <c r="U125" s="25">
+        <f>T125-S125</f>
+        <v/>
+      </c>
+      <c r="V125" s="31" t="inlineStr"/>
     </row>
     <row r="126" ht="20" customHeight="1">
       <c r="B126" s="20" t="inlineStr">
@@ -9473,46 +9945,50 @@
         <f>G126-F126</f>
         <v/>
       </c>
-      <c r="I126" s="26">
+      <c r="I126" s="23">
+        <f>ABS(G126-F126)</f>
+        <v/>
+      </c>
+      <c r="J126" s="26">
         <f>IF(F126&gt;0, G126/F126, IF(G126&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J126" s="27">
-        <f>IF(F126=0, IF(G126=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G126-F126)/F126))</f>
-        <v/>
-      </c>
-      <c r="K126" s="28" t="inlineStr"/>
-      <c r="L126" s="29" t="n">
+      <c r="K126" s="27">
+        <f>IF(F126&gt;0, 1.0 - (I126/F126), IF(G126=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L126" s="28" t="inlineStr"/>
+      <c r="M126" s="29" t="n">
         <v>1100</v>
       </c>
-      <c r="M126" s="30" t="n">
+      <c r="N126" s="30" t="n">
         <v>1100</v>
       </c>
-      <c r="N126" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O126" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P126" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q126" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R126" s="23">
-        <f>L126+N126+P126</f>
-        <v/>
-      </c>
-      <c r="S126" s="24">
+      <c r="O126" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" s="23">
         <f>M126+O126+Q126</f>
         <v/>
       </c>
-      <c r="T126" s="25">
-        <f>S126-R126</f>
-        <v/>
-      </c>
-      <c r="U126" s="31" t="inlineStr"/>
+      <c r="T126" s="24">
+        <f>N126+P126+R126</f>
+        <v/>
+      </c>
+      <c r="U126" s="25">
+        <f>T126-S126</f>
+        <v/>
+      </c>
+      <c r="V126" s="31" t="inlineStr"/>
     </row>
     <row r="127" ht="20" customHeight="1">
       <c r="B127" s="20" t="inlineStr">
@@ -9545,46 +10021,50 @@
         <f>G127-F127</f>
         <v/>
       </c>
-      <c r="I127" s="26">
+      <c r="I127" s="23">
+        <f>ABS(G127-F127)</f>
+        <v/>
+      </c>
+      <c r="J127" s="26">
         <f>IF(F127&gt;0, G127/F127, IF(G127&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J127" s="27">
-        <f>IF(F127=0, IF(G127=0, 1.0, 0.0), MAX(0, 1.0 - ABS(G127-F127)/F127))</f>
-        <v/>
-      </c>
-      <c r="K127" s="28" t="inlineStr"/>
-      <c r="L127" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M127" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N127" s="29" t="n">
+      <c r="K127" s="27">
+        <f>IF(F127&gt;0, 1.0 - (I127/F127), IF(G127=0, 1.0, 0.0))</f>
+        <v/>
+      </c>
+      <c r="L127" s="28" t="inlineStr"/>
+      <c r="M127" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" s="29" t="n">
         <v>640</v>
       </c>
-      <c r="O127" s="30" t="n">
+      <c r="P127" s="30" t="n">
         <v>640</v>
       </c>
-      <c r="P127" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q127" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R127" s="23">
-        <f>L127+N127+P127</f>
-        <v/>
-      </c>
-      <c r="S127" s="24">
+      <c r="Q127" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" s="23">
         <f>M127+O127+Q127</f>
         <v/>
       </c>
-      <c r="T127" s="25">
-        <f>S127-R127</f>
-        <v/>
-      </c>
-      <c r="U127" s="31" t="inlineStr"/>
+      <c r="T127" s="24">
+        <f>N127+P127+R127</f>
+        <v/>
+      </c>
+      <c r="U127" s="25">
+        <f>T127-S127</f>
+        <v/>
+      </c>
+      <c r="V127" s="31" t="inlineStr"/>
     </row>
     <row r="128" ht="25" customHeight="1">
       <c r="B128" s="32" t="inlineStr">
@@ -9607,19 +10087,19 @@
         <f>SUM(H10:H127)</f>
         <v/>
       </c>
-      <c r="I128" s="36">
+      <c r="I128" s="34">
+        <f>SUM(I10:I127)</f>
+        <v/>
+      </c>
+      <c r="J128" s="36">
         <f>IF(F128&gt;0, G128/F128, 1.0)</f>
         <v/>
       </c>
-      <c r="J128" s="36">
-        <f>IF(F128&gt;0, MAX(0, 1.0 - ABS(G128-F128)/F128), 1.0)</f>
-        <v/>
-      </c>
-      <c r="K128" s="37" t="n"/>
-      <c r="L128" s="34">
-        <f>SUM(L10:L127)</f>
-        <v/>
-      </c>
+      <c r="K128" s="36">
+        <f>IF(F128&gt;0, 1.0 - (I128/F128), 1.0)</f>
+        <v/>
+      </c>
+      <c r="L128" s="37" t="n"/>
       <c r="M128" s="34">
         <f>SUM(M10:M127)</f>
         <v/>
@@ -9648,39 +10128,43 @@
         <f>SUM(S10:S127)</f>
         <v/>
       </c>
-      <c r="T128" s="35">
+      <c r="T128" s="34">
         <f>SUM(T10:T127)</f>
         <v/>
       </c>
-      <c r="U128" s="37" t="n"/>
+      <c r="U128" s="35">
+        <f>SUM(U10:U127)</f>
+        <v/>
+      </c>
+      <c r="V128" s="37" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="O5:Q5"/>
-    <mergeCell ref="B4:U4"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="F8:K8"/>
-    <mergeCell ref="L8:Q8"/>
-    <mergeCell ref="B3:U3"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="B2:V2"/>
+    <mergeCell ref="S5:V5"/>
+    <mergeCell ref="M6:O6"/>
     <mergeCell ref="E6:G6"/>
-    <mergeCell ref="R5:U5"/>
     <mergeCell ref="H6:I6"/>
-    <mergeCell ref="R8:U8"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="B2:U2"/>
-    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M8:R8"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B5:D5"/>
-    <mergeCell ref="R6:U6"/>
+    <mergeCell ref="P5:R5"/>
+    <mergeCell ref="S8:V8"/>
+    <mergeCell ref="B4:V4"/>
+    <mergeCell ref="J5:L5"/>
     <mergeCell ref="B8:E8"/>
-    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="F8:L8"/>
     <mergeCell ref="E5:G5"/>
+    <mergeCell ref="B3:V3"/>
+    <mergeCell ref="M5:O5"/>
     <mergeCell ref="H5:I5"/>
     <mergeCell ref="B128:E128"/>
+    <mergeCell ref="S6:V6"/>
+    <mergeCell ref="P6:R6"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="K10:K43 K10:K127" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Motivo de Desviación" error="Por favor seleccione un motivo de la lista o escriba su comentario" type="list">
+    <dataValidation sqref="L10:L43 L10:L127" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Motivo de Desviación" error="Por favor seleccione un motivo de la lista o escriba su comentario" type="list">
       <formula1>"Adelanto de pedidos,Atraso de pedidos,Pedido extra no previsto,Campaña habitual,Cancelado / Sin siembra,Otro motivo"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Revision_Previsiones_Q4_2026/Revision_Previsiones_Q4_2026_Garcia.xlsx
+++ b/Revision_Previsiones_Q4_2026/Revision_Previsiones_Q4_2026_Garcia.xlsx
@@ -266,7 +266,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -336,9 +336,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -735,7 +732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:U128"/>
+  <dimension ref="B2:T128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -747,18 +744,17 @@
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="32" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="15" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="32" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="17" max="17"/>
     <col width="17" customWidth="1" min="18" max="18"/>
-    <col width="17" customWidth="1" min="19" max="19"/>
-    <col width="15" customWidth="1" min="20" max="20"/>
-    <col width="34" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="34" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="2" ht="36" customHeight="1">
@@ -771,14 +767,14 @@
     <row r="3" ht="20" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>DELEGADO COMERCIAL: GARCÍA | Cierre Septiembre Oficial (01/10/2026) vs Previsiones a Final de Año | Generado: 01/10/2026 14:02</t>
+          <t>DELEGADO COMERCIAL: GARCÍA | Cierre Septiembre Oficial (01/10/2026) vs Previsiones a Final de Año | Generado: 01/10/2026 14:16</t>
         </is>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>📌 INSTRUCCIONES: 1) Revise el bloque de SEPTIEMBRE (Previsto, Real, Desviación en Valor Absoluto y Forecast Accuracy) e indique en col. K el motivo de la desviación (adelanto, atraso, extra). 2) En las columnas verdes (M, O, Q), revise y actualice las cantidades estimadas de Octubre, Noviembre y Diciembre si prevé cambios. 3) Comente en col. U cualquier nota de campaña.</t>
+          <t>📌 INSTRUCCIONES: 1) Revise el bloque de SEPTIEMBRE (Previsto, Real, Desviación en Valor Absoluto y % Consecución) e indique en col. J el motivo de la desviación (adelanto, atraso, extra). 2) En las columnas verdes (L, N, P), revise y actualice las cantidades estimadas de Octubre, Noviembre y Diciembre si prevé cambios. 3) Comente en col. T cualquier nota de campaña.</t>
         </is>
       </c>
     </row>
@@ -803,34 +799,29 @@
         </is>
       </c>
       <c r="I5" s="5" t="n"/>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>FORECAST ACCURACY SEP (OFICIAL)</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>PREVISIÓN INICIAL Q4 (U)</t>
         </is>
       </c>
+      <c r="L5" s="5" t="n"/>
       <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="6" t="inlineStr">
+      <c r="N5" s="6" t="inlineStr">
         <is>
           <t>PREVISIÓN REVISADA Q4 (U)</t>
         </is>
       </c>
+      <c r="O5" s="5" t="n"/>
       <c r="P5" s="5" t="n"/>
-      <c r="Q5" s="5" t="n"/>
-      <c r="R5" s="8" t="inlineStr">
+      <c r="Q5" s="8" t="inlineStr">
         <is>
           <t>VARIACIÓN NETA Q4 (U)</t>
         </is>
       </c>
+      <c r="R5" s="5" t="n"/>
       <c r="S5" s="5" t="n"/>
       <c r="T5" s="5" t="n"/>
-      <c r="U5" s="5" t="n"/>
     </row>
     <row r="6" ht="26" customHeight="1">
       <c r="B6" s="9">
@@ -850,30 +841,26 @@
         <v/>
       </c>
       <c r="I6" s="5" t="n"/>
-      <c r="J6" s="11">
-        <f>J128</f>
-        <v/>
-      </c>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="9">
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="9">
+        <f>Q128</f>
+        <v/>
+      </c>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="10">
         <f>R128</f>
         <v/>
       </c>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="10">
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
+      <c r="Q6" s="12">
         <f>S128</f>
         <v/>
       </c>
-      <c r="P6" s="5" t="n"/>
-      <c r="Q6" s="5" t="n"/>
-      <c r="R6" s="12">
-        <f>T128</f>
-        <v/>
-      </c>
+      <c r="R6" s="5" t="n"/>
       <c r="S6" s="5" t="n"/>
       <c r="T6" s="5" t="n"/>
-      <c r="U6" s="5" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="B8" s="13" t="inlineStr">
@@ -883,15 +870,15 @@
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>CIERRE SEPTIEMBRE 2026 (CALIBRACIÓN Y ANÁLISIS DE EXACTITUD)</t>
-        </is>
-      </c>
-      <c r="L8" s="15" t="inlineStr">
+          <t>CIERRE SEPTIEMBRE 2026 (CALIBRACIÓN Y ANÁLISIS)</t>
+        </is>
+      </c>
+      <c r="K8" s="15" t="inlineStr">
         <is>
           <t>REVISIÓN PREVISIONES MES A MES (HASTA FINAL DE AÑO 2026)</t>
         </is>
       </c>
-      <c r="R8" s="16" t="inlineStr">
+      <c r="Q8" s="16" t="inlineStr">
         <is>
           <t>IMPACTO Q4 Y JUSTIFICACIÓN</t>
         </is>
@@ -940,60 +927,55 @@
       </c>
       <c r="J9" s="18" t="inlineStr">
         <is>
-          <t>Forecast Accuracy</t>
-        </is>
-      </c>
-      <c r="K9" s="18" t="inlineStr">
-        <is>
           <t>Comentario Sep (¿Adelanto/Atraso/Extra?)</t>
         </is>
       </c>
+      <c r="K9" s="19" t="inlineStr">
+        <is>
+          <t>Oct Anterior (u)</t>
+        </is>
+      </c>
       <c r="L9" s="19" t="inlineStr">
         <is>
-          <t>Oct Anterior (u)</t>
+          <t>Oct Revisado (u)</t>
         </is>
       </c>
       <c r="M9" s="19" t="inlineStr">
         <is>
-          <t>Oct Revisado (u)</t>
+          <t>Nov Anterior (u)</t>
         </is>
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Nov Anterior (u)</t>
+          <t>Nov Revisado (u)</t>
         </is>
       </c>
       <c r="O9" s="19" t="inlineStr">
         <is>
-          <t>Nov Revisado (u)</t>
+          <t>Dic Anterior (u)</t>
         </is>
       </c>
       <c r="P9" s="19" t="inlineStr">
         <is>
-          <t>Dic Anterior (u)</t>
-        </is>
-      </c>
-      <c r="Q9" s="19" t="inlineStr">
-        <is>
           <t>Dic Revisado (u)</t>
         </is>
       </c>
+      <c r="Q9" s="17" t="inlineStr">
+        <is>
+          <t>Total Q4 Ant (u)</t>
+        </is>
+      </c>
       <c r="R9" s="17" t="inlineStr">
         <is>
-          <t>Total Q4 Ant (u)</t>
+          <t>Total Q4 Rev (u)</t>
         </is>
       </c>
       <c r="S9" s="17" t="inlineStr">
         <is>
-          <t>Total Q4 Rev (u)</t>
+          <t>Dif Q4 (u)</t>
         </is>
       </c>
       <c r="T9" s="17" t="inlineStr">
-        <is>
-          <t>Dif Q4 (u)</t>
-        </is>
-      </c>
-      <c r="U9" s="17" t="inlineStr">
         <is>
           <t>Comentarios / Justificación Q4</t>
         </is>
@@ -1034,42 +1016,38 @@
         <f>IF(F10&gt;0, G10/F10, IF(G10&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J10" s="25">
-        <f>IF(F10&gt;0, 1.0 - (H10/F10), IF(G10=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K10" s="26" t="inlineStr"/>
+      <c r="J10" s="25" t="inlineStr"/>
+      <c r="K10" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L10" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M10" s="28" t="n">
+      <c r="M10" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N10" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O10" s="28" t="n">
-        <v>0</v>
+      <c r="O10" s="26" t="n">
+        <v>200</v>
       </c>
       <c r="P10" s="27" t="n">
         <v>200</v>
       </c>
-      <c r="Q10" s="28" t="n">
-        <v>200</v>
-      </c>
-      <c r="R10" s="22">
+      <c r="Q10" s="22">
+        <f>K10+M10+O10</f>
+        <v/>
+      </c>
+      <c r="R10" s="23">
         <f>L10+N10+P10</f>
         <v/>
       </c>
-      <c r="S10" s="23">
-        <f>M10+O10+Q10</f>
-        <v/>
-      </c>
-      <c r="T10" s="29">
-        <f>S10-R10</f>
-        <v/>
-      </c>
-      <c r="U10" s="30" t="inlineStr"/>
+      <c r="S10" s="28">
+        <f>R10-Q10</f>
+        <v/>
+      </c>
+      <c r="T10" s="29" t="inlineStr"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="B11" s="20" t="inlineStr">
@@ -1106,42 +1084,38 @@
         <f>IF(F11&gt;0, G11/F11, IF(G11&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J11" s="25">
-        <f>IF(F11&gt;0, 1.0 - (H11/F11), IF(G11=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K11" s="26" t="inlineStr"/>
+      <c r="J11" s="25" t="inlineStr"/>
+      <c r="K11" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L11" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M11" s="28" t="n">
-        <v>0</v>
+      <c r="M11" s="26" t="n">
+        <v>1280</v>
       </c>
       <c r="N11" s="27" t="n">
         <v>1280</v>
       </c>
-      <c r="O11" s="28" t="n">
-        <v>1280</v>
+      <c r="O11" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P11" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="22">
+      <c r="Q11" s="22">
+        <f>K11+M11+O11</f>
+        <v/>
+      </c>
+      <c r="R11" s="23">
         <f>L11+N11+P11</f>
         <v/>
       </c>
-      <c r="S11" s="23">
-        <f>M11+O11+Q11</f>
-        <v/>
-      </c>
-      <c r="T11" s="29">
-        <f>S11-R11</f>
-        <v/>
-      </c>
-      <c r="U11" s="30" t="inlineStr"/>
+      <c r="S11" s="28">
+        <f>R11-Q11</f>
+        <v/>
+      </c>
+      <c r="T11" s="29" t="inlineStr"/>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="B12" s="20" t="inlineStr">
@@ -1178,42 +1152,38 @@
         <f>IF(F12&gt;0, G12/F12, IF(G12&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J12" s="25">
-        <f>IF(F12&gt;0, 1.0 - (H12/F12), IF(G12=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K12" s="26" t="inlineStr"/>
+      <c r="J12" s="25" t="inlineStr"/>
+      <c r="K12" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L12" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M12" s="28" t="n">
-        <v>0</v>
+      <c r="M12" s="26" t="n">
+        <v>2000</v>
       </c>
       <c r="N12" s="27" t="n">
         <v>2000</v>
       </c>
-      <c r="O12" s="28" t="n">
-        <v>2000</v>
+      <c r="O12" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P12" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="22">
+      <c r="Q12" s="22">
+        <f>K12+M12+O12</f>
+        <v/>
+      </c>
+      <c r="R12" s="23">
         <f>L12+N12+P12</f>
         <v/>
       </c>
-      <c r="S12" s="23">
-        <f>M12+O12+Q12</f>
-        <v/>
-      </c>
-      <c r="T12" s="29">
-        <f>S12-R12</f>
-        <v/>
-      </c>
-      <c r="U12" s="30" t="inlineStr"/>
+      <c r="S12" s="28">
+        <f>R12-Q12</f>
+        <v/>
+      </c>
+      <c r="T12" s="29" t="inlineStr"/>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="B13" s="20" t="inlineStr">
@@ -1250,42 +1220,38 @@
         <f>IF(F13&gt;0, G13/F13, IF(G13&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J13" s="25">
-        <f>IF(F13&gt;0, 1.0 - (H13/F13), IF(G13=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K13" s="26" t="inlineStr"/>
+      <c r="J13" s="25" t="inlineStr"/>
+      <c r="K13" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L13" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M13" s="28" t="n">
+      <c r="M13" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N13" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O13" s="28" t="n">
+      <c r="O13" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P13" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="22">
+      <c r="Q13" s="22">
+        <f>K13+M13+O13</f>
+        <v/>
+      </c>
+      <c r="R13" s="23">
         <f>L13+N13+P13</f>
         <v/>
       </c>
-      <c r="S13" s="23">
-        <f>M13+O13+Q13</f>
-        <v/>
-      </c>
-      <c r="T13" s="29">
-        <f>S13-R13</f>
-        <v/>
-      </c>
-      <c r="U13" s="30" t="inlineStr"/>
+      <c r="S13" s="28">
+        <f>R13-Q13</f>
+        <v/>
+      </c>
+      <c r="T13" s="29" t="inlineStr"/>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="B14" s="20" t="inlineStr">
@@ -1322,46 +1288,42 @@
         <f>IF(F14&gt;0, G14/F14, IF(G14&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J14" s="25">
-        <f>IF(F14&gt;0, 1.0 - (H14/F14), IF(G14=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K14" s="26" t="inlineStr">
+      <c r="J14" s="25" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
       </c>
+      <c r="K14" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L14" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M14" s="28" t="n">
+      <c r="M14" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N14" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O14" s="28" t="n">
+      <c r="O14" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P14" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="22">
+      <c r="Q14" s="22">
+        <f>K14+M14+O14</f>
+        <v/>
+      </c>
+      <c r="R14" s="23">
         <f>L14+N14+P14</f>
         <v/>
       </c>
-      <c r="S14" s="23">
-        <f>M14+O14+Q14</f>
-        <v/>
-      </c>
-      <c r="T14" s="29">
-        <f>S14-R14</f>
-        <v/>
-      </c>
-      <c r="U14" s="30" t="inlineStr"/>
+      <c r="S14" s="28">
+        <f>R14-Q14</f>
+        <v/>
+      </c>
+      <c r="T14" s="29" t="inlineStr"/>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="B15" s="20" t="inlineStr">
@@ -1398,42 +1360,38 @@
         <f>IF(F15&gt;0, G15/F15, IF(G15&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J15" s="25">
-        <f>IF(F15&gt;0, 1.0 - (H15/F15), IF(G15=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K15" s="26" t="inlineStr"/>
+      <c r="J15" s="25" t="inlineStr"/>
+      <c r="K15" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L15" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M15" s="28" t="n">
-        <v>0</v>
+      <c r="M15" s="26" t="n">
+        <v>600</v>
       </c>
       <c r="N15" s="27" t="n">
         <v>600</v>
       </c>
-      <c r="O15" s="28" t="n">
-        <v>600</v>
+      <c r="O15" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P15" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="22">
+      <c r="Q15" s="22">
+        <f>K15+M15+O15</f>
+        <v/>
+      </c>
+      <c r="R15" s="23">
         <f>L15+N15+P15</f>
         <v/>
       </c>
-      <c r="S15" s="23">
-        <f>M15+O15+Q15</f>
-        <v/>
-      </c>
-      <c r="T15" s="29">
-        <f>S15-R15</f>
-        <v/>
-      </c>
-      <c r="U15" s="30" t="inlineStr"/>
+      <c r="S15" s="28">
+        <f>R15-Q15</f>
+        <v/>
+      </c>
+      <c r="T15" s="29" t="inlineStr"/>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="B16" s="20" t="inlineStr">
@@ -1470,42 +1428,38 @@
         <f>IF(F16&gt;0, G16/F16, IF(G16&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J16" s="25">
-        <f>IF(F16&gt;0, 1.0 - (H16/F16), IF(G16=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K16" s="26" t="inlineStr"/>
+      <c r="J16" s="25" t="inlineStr"/>
+      <c r="K16" s="26" t="n">
+        <v>1100</v>
+      </c>
       <c r="L16" s="27" t="n">
         <v>1100</v>
       </c>
-      <c r="M16" s="28" t="n">
-        <v>1100</v>
+      <c r="M16" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="N16" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O16" s="28" t="n">
+      <c r="O16" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P16" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="22">
+      <c r="Q16" s="22">
+        <f>K16+M16+O16</f>
+        <v/>
+      </c>
+      <c r="R16" s="23">
         <f>L16+N16+P16</f>
         <v/>
       </c>
-      <c r="S16" s="23">
-        <f>M16+O16+Q16</f>
-        <v/>
-      </c>
-      <c r="T16" s="29">
-        <f>S16-R16</f>
-        <v/>
-      </c>
-      <c r="U16" s="30" t="inlineStr"/>
+      <c r="S16" s="28">
+        <f>R16-Q16</f>
+        <v/>
+      </c>
+      <c r="T16" s="29" t="inlineStr"/>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="B17" s="20" t="inlineStr">
@@ -1542,42 +1496,38 @@
         <f>IF(F17&gt;0, G17/F17, IF(G17&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J17" s="25">
-        <f>IF(F17&gt;0, 1.0 - (H17/F17), IF(G17=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K17" s="26" t="inlineStr"/>
+      <c r="J17" s="25" t="inlineStr"/>
+      <c r="K17" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L17" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M17" s="28" t="n">
-        <v>0</v>
+      <c r="M17" s="26" t="n">
+        <v>1280</v>
       </c>
       <c r="N17" s="27" t="n">
         <v>1280</v>
       </c>
-      <c r="O17" s="28" t="n">
-        <v>1280</v>
+      <c r="O17" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P17" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" s="22">
+      <c r="Q17" s="22">
+        <f>K17+M17+O17</f>
+        <v/>
+      </c>
+      <c r="R17" s="23">
         <f>L17+N17+P17</f>
         <v/>
       </c>
-      <c r="S17" s="23">
-        <f>M17+O17+Q17</f>
-        <v/>
-      </c>
-      <c r="T17" s="29">
-        <f>S17-R17</f>
-        <v/>
-      </c>
-      <c r="U17" s="30" t="inlineStr"/>
+      <c r="S17" s="28">
+        <f>R17-Q17</f>
+        <v/>
+      </c>
+      <c r="T17" s="29" t="inlineStr"/>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="B18" s="20" t="inlineStr">
@@ -1614,42 +1564,38 @@
         <f>IF(F18&gt;0, G18/F18, IF(G18&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J18" s="25">
-        <f>IF(F18&gt;0, 1.0 - (H18/F18), IF(G18=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K18" s="26" t="inlineStr"/>
+      <c r="J18" s="25" t="inlineStr"/>
+      <c r="K18" s="26" t="n">
+        <v>5000</v>
+      </c>
       <c r="L18" s="27" t="n">
         <v>5000</v>
       </c>
-      <c r="M18" s="28" t="n">
+      <c r="M18" s="26" t="n">
         <v>5000</v>
       </c>
       <c r="N18" s="27" t="n">
         <v>5000</v>
       </c>
-      <c r="O18" s="28" t="n">
-        <v>5000</v>
+      <c r="O18" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P18" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" s="22">
+      <c r="Q18" s="22">
+        <f>K18+M18+O18</f>
+        <v/>
+      </c>
+      <c r="R18" s="23">
         <f>L18+N18+P18</f>
         <v/>
       </c>
-      <c r="S18" s="23">
-        <f>M18+O18+Q18</f>
-        <v/>
-      </c>
-      <c r="T18" s="29">
-        <f>S18-R18</f>
-        <v/>
-      </c>
-      <c r="U18" s="30" t="inlineStr"/>
+      <c r="S18" s="28">
+        <f>R18-Q18</f>
+        <v/>
+      </c>
+      <c r="T18" s="29" t="inlineStr"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="B19" s="20" t="inlineStr">
@@ -1686,42 +1632,38 @@
         <f>IF(F19&gt;0, G19/F19, IF(G19&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J19" s="25">
-        <f>IF(F19&gt;0, 1.0 - (H19/F19), IF(G19=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K19" s="26" t="inlineStr"/>
+      <c r="J19" s="25" t="inlineStr"/>
+      <c r="K19" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L19" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M19" s="28" t="n">
+      <c r="M19" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O19" s="28" t="n">
-        <v>0</v>
+      <c r="O19" s="26" t="n">
+        <v>750</v>
       </c>
       <c r="P19" s="27" t="n">
         <v>750</v>
       </c>
-      <c r="Q19" s="28" t="n">
-        <v>750</v>
-      </c>
-      <c r="R19" s="22">
+      <c r="Q19" s="22">
+        <f>K19+M19+O19</f>
+        <v/>
+      </c>
+      <c r="R19" s="23">
         <f>L19+N19+P19</f>
         <v/>
       </c>
-      <c r="S19" s="23">
-        <f>M19+O19+Q19</f>
-        <v/>
-      </c>
-      <c r="T19" s="29">
-        <f>S19-R19</f>
-        <v/>
-      </c>
-      <c r="U19" s="30" t="inlineStr"/>
+      <c r="S19" s="28">
+        <f>R19-Q19</f>
+        <v/>
+      </c>
+      <c r="T19" s="29" t="inlineStr"/>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="B20" s="20" t="inlineStr">
@@ -1758,42 +1700,38 @@
         <f>IF(F20&gt;0, G20/F20, IF(G20&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J20" s="25">
-        <f>IF(F20&gt;0, 1.0 - (H20/F20), IF(G20=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K20" s="26" t="inlineStr"/>
+      <c r="J20" s="25" t="inlineStr"/>
+      <c r="K20" s="26" t="n">
+        <v>2200</v>
+      </c>
       <c r="L20" s="27" t="n">
         <v>2200</v>
       </c>
-      <c r="M20" s="28" t="n">
-        <v>2200</v>
+      <c r="M20" s="26" t="n">
+        <v>3300</v>
       </c>
       <c r="N20" s="27" t="n">
         <v>3300</v>
       </c>
-      <c r="O20" s="28" t="n">
-        <v>3300</v>
+      <c r="O20" s="26" t="n">
+        <v>1100</v>
       </c>
       <c r="P20" s="27" t="n">
         <v>1100</v>
       </c>
-      <c r="Q20" s="28" t="n">
-        <v>1100</v>
-      </c>
-      <c r="R20" s="22">
+      <c r="Q20" s="22">
+        <f>K20+M20+O20</f>
+        <v/>
+      </c>
+      <c r="R20" s="23">
         <f>L20+N20+P20</f>
         <v/>
       </c>
-      <c r="S20" s="23">
-        <f>M20+O20+Q20</f>
-        <v/>
-      </c>
-      <c r="T20" s="29">
-        <f>S20-R20</f>
-        <v/>
-      </c>
-      <c r="U20" s="30" t="inlineStr"/>
+      <c r="S20" s="28">
+        <f>R20-Q20</f>
+        <v/>
+      </c>
+      <c r="T20" s="29" t="inlineStr"/>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="B21" s="20" t="inlineStr">
@@ -1830,42 +1768,38 @@
         <f>IF(F21&gt;0, G21/F21, IF(G21&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J21" s="25">
-        <f>IF(F21&gt;0, 1.0 - (H21/F21), IF(G21=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K21" s="26" t="inlineStr"/>
+      <c r="J21" s="25" t="inlineStr"/>
+      <c r="K21" s="26" t="n">
+        <v>1280</v>
+      </c>
       <c r="L21" s="27" t="n">
         <v>1280</v>
       </c>
-      <c r="M21" s="28" t="n">
-        <v>1280</v>
+      <c r="M21" s="26" t="n">
+        <v>640</v>
       </c>
       <c r="N21" s="27" t="n">
         <v>640</v>
       </c>
-      <c r="O21" s="28" t="n">
+      <c r="O21" s="26" t="n">
         <v>640</v>
       </c>
       <c r="P21" s="27" t="n">
         <v>640</v>
       </c>
-      <c r="Q21" s="28" t="n">
-        <v>640</v>
-      </c>
-      <c r="R21" s="22">
+      <c r="Q21" s="22">
+        <f>K21+M21+O21</f>
+        <v/>
+      </c>
+      <c r="R21" s="23">
         <f>L21+N21+P21</f>
         <v/>
       </c>
-      <c r="S21" s="23">
-        <f>M21+O21+Q21</f>
-        <v/>
-      </c>
-      <c r="T21" s="29">
-        <f>S21-R21</f>
-        <v/>
-      </c>
-      <c r="U21" s="30" t="inlineStr"/>
+      <c r="S21" s="28">
+        <f>R21-Q21</f>
+        <v/>
+      </c>
+      <c r="T21" s="29" t="inlineStr"/>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="B22" s="20" t="inlineStr">
@@ -1902,42 +1836,38 @@
         <f>IF(F22&gt;0, G22/F22, IF(G22&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J22" s="25">
-        <f>IF(F22&gt;0, 1.0 - (H22/F22), IF(G22=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K22" s="26" t="inlineStr"/>
+      <c r="J22" s="25" t="inlineStr"/>
+      <c r="K22" s="26" t="n">
+        <v>2000</v>
+      </c>
       <c r="L22" s="27" t="n">
         <v>2000</v>
       </c>
-      <c r="M22" s="28" t="n">
+      <c r="M22" s="26" t="n">
         <v>2000</v>
       </c>
       <c r="N22" s="27" t="n">
         <v>2000</v>
       </c>
-      <c r="O22" s="28" t="n">
-        <v>2000</v>
+      <c r="O22" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P22" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" s="22">
+      <c r="Q22" s="22">
+        <f>K22+M22+O22</f>
+        <v/>
+      </c>
+      <c r="R22" s="23">
         <f>L22+N22+P22</f>
         <v/>
       </c>
-      <c r="S22" s="23">
-        <f>M22+O22+Q22</f>
-        <v/>
-      </c>
-      <c r="T22" s="29">
-        <f>S22-R22</f>
-        <v/>
-      </c>
-      <c r="U22" s="30" t="inlineStr"/>
+      <c r="S22" s="28">
+        <f>R22-Q22</f>
+        <v/>
+      </c>
+      <c r="T22" s="29" t="inlineStr"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="B23" s="20" t="inlineStr">
@@ -1974,42 +1904,38 @@
         <f>IF(F23&gt;0, G23/F23, IF(G23&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J23" s="25">
-        <f>IF(F23&gt;0, 1.0 - (H23/F23), IF(G23=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K23" s="26" t="inlineStr"/>
+      <c r="J23" s="25" t="inlineStr"/>
+      <c r="K23" s="26" t="n">
+        <v>600</v>
+      </c>
       <c r="L23" s="27" t="n">
         <v>600</v>
       </c>
-      <c r="M23" s="28" t="n">
-        <v>600</v>
+      <c r="M23" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="N23" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O23" s="28" t="n">
+      <c r="O23" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P23" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" s="22">
+      <c r="Q23" s="22">
+        <f>K23+M23+O23</f>
+        <v/>
+      </c>
+      <c r="R23" s="23">
         <f>L23+N23+P23</f>
         <v/>
       </c>
-      <c r="S23" s="23">
-        <f>M23+O23+Q23</f>
-        <v/>
-      </c>
-      <c r="T23" s="29">
-        <f>S23-R23</f>
-        <v/>
-      </c>
-      <c r="U23" s="30" t="inlineStr"/>
+      <c r="S23" s="28">
+        <f>R23-Q23</f>
+        <v/>
+      </c>
+      <c r="T23" s="29" t="inlineStr"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="B24" s="20" t="inlineStr">
@@ -2046,42 +1972,38 @@
         <f>IF(F24&gt;0, G24/F24, IF(G24&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J24" s="25">
-        <f>IF(F24&gt;0, 1.0 - (H24/F24), IF(G24=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K24" s="26" t="inlineStr"/>
+      <c r="J24" s="25" t="inlineStr"/>
+      <c r="K24" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L24" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M24" s="28" t="n">
-        <v>0</v>
+      <c r="M24" s="26" t="n">
+        <v>200</v>
       </c>
       <c r="N24" s="27" t="n">
         <v>200</v>
       </c>
-      <c r="O24" s="28" t="n">
+      <c r="O24" s="26" t="n">
         <v>200</v>
       </c>
       <c r="P24" s="27" t="n">
         <v>200</v>
       </c>
-      <c r="Q24" s="28" t="n">
-        <v>200</v>
-      </c>
-      <c r="R24" s="22">
+      <c r="Q24" s="22">
+        <f>K24+M24+O24</f>
+        <v/>
+      </c>
+      <c r="R24" s="23">
         <f>L24+N24+P24</f>
         <v/>
       </c>
-      <c r="S24" s="23">
-        <f>M24+O24+Q24</f>
-        <v/>
-      </c>
-      <c r="T24" s="29">
-        <f>S24-R24</f>
-        <v/>
-      </c>
-      <c r="U24" s="30" t="inlineStr"/>
+      <c r="S24" s="28">
+        <f>R24-Q24</f>
+        <v/>
+      </c>
+      <c r="T24" s="29" t="inlineStr"/>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="B25" s="20" t="inlineStr">
@@ -2118,42 +2040,38 @@
         <f>IF(F25&gt;0, G25/F25, IF(G25&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J25" s="25">
-        <f>IF(F25&gt;0, 1.0 - (H25/F25), IF(G25=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K25" s="26" t="inlineStr"/>
+      <c r="J25" s="25" t="inlineStr"/>
+      <c r="K25" s="26" t="n">
+        <v>640</v>
+      </c>
       <c r="L25" s="27" t="n">
         <v>640</v>
       </c>
-      <c r="M25" s="28" t="n">
+      <c r="M25" s="26" t="n">
         <v>640</v>
       </c>
       <c r="N25" s="27" t="n">
         <v>640</v>
       </c>
-      <c r="O25" s="28" t="n">
-        <v>640</v>
+      <c r="O25" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P25" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" s="22">
+      <c r="Q25" s="22">
+        <f>K25+M25+O25</f>
+        <v/>
+      </c>
+      <c r="R25" s="23">
         <f>L25+N25+P25</f>
         <v/>
       </c>
-      <c r="S25" s="23">
-        <f>M25+O25+Q25</f>
-        <v/>
-      </c>
-      <c r="T25" s="29">
-        <f>S25-R25</f>
-        <v/>
-      </c>
-      <c r="U25" s="30" t="inlineStr"/>
+      <c r="S25" s="28">
+        <f>R25-Q25</f>
+        <v/>
+      </c>
+      <c r="T25" s="29" t="inlineStr"/>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="B26" s="20" t="inlineStr">
@@ -2190,42 +2108,38 @@
         <f>IF(F26&gt;0, G26/F26, IF(G26&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J26" s="25">
-        <f>IF(F26&gt;0, 1.0 - (H26/F26), IF(G26=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K26" s="26" t="inlineStr"/>
+      <c r="J26" s="25" t="inlineStr"/>
+      <c r="K26" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L26" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M26" s="28" t="n">
+      <c r="M26" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N26" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O26" s="28" t="n">
+      <c r="O26" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P26" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="22">
+      <c r="Q26" s="22">
+        <f>K26+M26+O26</f>
+        <v/>
+      </c>
+      <c r="R26" s="23">
         <f>L26+N26+P26</f>
         <v/>
       </c>
-      <c r="S26" s="23">
-        <f>M26+O26+Q26</f>
-        <v/>
-      </c>
-      <c r="T26" s="29">
-        <f>S26-R26</f>
-        <v/>
-      </c>
-      <c r="U26" s="30" t="inlineStr"/>
+      <c r="S26" s="28">
+        <f>R26-Q26</f>
+        <v/>
+      </c>
+      <c r="T26" s="29" t="inlineStr"/>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="B27" s="20" t="inlineStr">
@@ -2262,42 +2176,38 @@
         <f>IF(F27&gt;0, G27/F27, IF(G27&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J27" s="25">
-        <f>IF(F27&gt;0, 1.0 - (H27/F27), IF(G27=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K27" s="26" t="inlineStr"/>
+      <c r="J27" s="25" t="inlineStr"/>
+      <c r="K27" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L27" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M27" s="28" t="n">
+      <c r="M27" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N27" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O27" s="28" t="n">
+      <c r="O27" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P27" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" s="22">
+      <c r="Q27" s="22">
+        <f>K27+M27+O27</f>
+        <v/>
+      </c>
+      <c r="R27" s="23">
         <f>L27+N27+P27</f>
         <v/>
       </c>
-      <c r="S27" s="23">
-        <f>M27+O27+Q27</f>
-        <v/>
-      </c>
-      <c r="T27" s="29">
-        <f>S27-R27</f>
-        <v/>
-      </c>
-      <c r="U27" s="30" t="inlineStr"/>
+      <c r="S27" s="28">
+        <f>R27-Q27</f>
+        <v/>
+      </c>
+      <c r="T27" s="29" t="inlineStr"/>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="B28" s="20" t="inlineStr">
@@ -2334,42 +2244,38 @@
         <f>IF(F28&gt;0, G28/F28, IF(G28&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J28" s="25">
-        <f>IF(F28&gt;0, 1.0 - (H28/F28), IF(G28=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K28" s="26" t="inlineStr"/>
+      <c r="J28" s="25" t="inlineStr"/>
+      <c r="K28" s="26" t="n">
+        <v>100</v>
+      </c>
       <c r="L28" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="M28" s="28" t="n">
-        <v>100</v>
+      <c r="M28" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="N28" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O28" s="28" t="n">
+      <c r="O28" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P28" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" s="22">
+      <c r="Q28" s="22">
+        <f>K28+M28+O28</f>
+        <v/>
+      </c>
+      <c r="R28" s="23">
         <f>L28+N28+P28</f>
         <v/>
       </c>
-      <c r="S28" s="23">
-        <f>M28+O28+Q28</f>
-        <v/>
-      </c>
-      <c r="T28" s="29">
-        <f>S28-R28</f>
-        <v/>
-      </c>
-      <c r="U28" s="30" t="inlineStr"/>
+      <c r="S28" s="28">
+        <f>R28-Q28</f>
+        <v/>
+      </c>
+      <c r="T28" s="29" t="inlineStr"/>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="B29" s="20" t="inlineStr">
@@ -2406,42 +2312,38 @@
         <f>IF(F29&gt;0, G29/F29, IF(G29&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J29" s="25">
-        <f>IF(F29&gt;0, 1.0 - (H29/F29), IF(G29=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K29" s="26" t="inlineStr"/>
+      <c r="J29" s="25" t="inlineStr"/>
+      <c r="K29" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L29" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M29" s="28" t="n">
-        <v>0</v>
+      <c r="M29" s="26" t="n">
+        <v>200</v>
       </c>
       <c r="N29" s="27" t="n">
         <v>200</v>
       </c>
-      <c r="O29" s="28" t="n">
-        <v>200</v>
+      <c r="O29" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P29" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" s="22">
+      <c r="Q29" s="22">
+        <f>K29+M29+O29</f>
+        <v/>
+      </c>
+      <c r="R29" s="23">
         <f>L29+N29+P29</f>
         <v/>
       </c>
-      <c r="S29" s="23">
-        <f>M29+O29+Q29</f>
-        <v/>
-      </c>
-      <c r="T29" s="29">
-        <f>S29-R29</f>
-        <v/>
-      </c>
-      <c r="U29" s="30" t="inlineStr"/>
+      <c r="S29" s="28">
+        <f>R29-Q29</f>
+        <v/>
+      </c>
+      <c r="T29" s="29" t="inlineStr"/>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="B30" s="20" t="inlineStr">
@@ -2478,42 +2380,38 @@
         <f>IF(F30&gt;0, G30/F30, IF(G30&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J30" s="25">
-        <f>IF(F30&gt;0, 1.0 - (H30/F30), IF(G30=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K30" s="26" t="inlineStr"/>
+      <c r="J30" s="25" t="inlineStr"/>
+      <c r="K30" s="26" t="n">
+        <v>100</v>
+      </c>
       <c r="L30" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="M30" s="28" t="n">
+      <c r="M30" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="26" t="n">
         <v>100</v>
-      </c>
-      <c r="N30" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="28" t="n">
-        <v>0</v>
       </c>
       <c r="P30" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="Q30" s="28" t="n">
-        <v>100</v>
-      </c>
-      <c r="R30" s="22">
+      <c r="Q30" s="22">
+        <f>K30+M30+O30</f>
+        <v/>
+      </c>
+      <c r="R30" s="23">
         <f>L30+N30+P30</f>
         <v/>
       </c>
-      <c r="S30" s="23">
-        <f>M30+O30+Q30</f>
-        <v/>
-      </c>
-      <c r="T30" s="29">
-        <f>S30-R30</f>
-        <v/>
-      </c>
-      <c r="U30" s="30" t="inlineStr"/>
+      <c r="S30" s="28">
+        <f>R30-Q30</f>
+        <v/>
+      </c>
+      <c r="T30" s="29" t="inlineStr"/>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="B31" s="20" t="inlineStr">
@@ -2550,42 +2448,38 @@
         <f>IF(F31&gt;0, G31/F31, IF(G31&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J31" s="25">
-        <f>IF(F31&gt;0, 1.0 - (H31/F31), IF(G31=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K31" s="26" t="inlineStr"/>
+      <c r="J31" s="25" t="inlineStr"/>
+      <c r="K31" s="26" t="n">
+        <v>300</v>
+      </c>
       <c r="L31" s="27" t="n">
         <v>300</v>
       </c>
-      <c r="M31" s="28" t="n">
+      <c r="M31" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="26" t="n">
         <v>300</v>
-      </c>
-      <c r="N31" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="28" t="n">
-        <v>0</v>
       </c>
       <c r="P31" s="27" t="n">
         <v>300</v>
       </c>
-      <c r="Q31" s="28" t="n">
-        <v>300</v>
-      </c>
-      <c r="R31" s="22">
+      <c r="Q31" s="22">
+        <f>K31+M31+O31</f>
+        <v/>
+      </c>
+      <c r="R31" s="23">
         <f>L31+N31+P31</f>
         <v/>
       </c>
-      <c r="S31" s="23">
-        <f>M31+O31+Q31</f>
-        <v/>
-      </c>
-      <c r="T31" s="29">
-        <f>S31-R31</f>
-        <v/>
-      </c>
-      <c r="U31" s="30" t="inlineStr"/>
+      <c r="S31" s="28">
+        <f>R31-Q31</f>
+        <v/>
+      </c>
+      <c r="T31" s="29" t="inlineStr"/>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="B32" s="20" t="inlineStr">
@@ -2622,42 +2516,38 @@
         <f>IF(F32&gt;0, G32/F32, IF(G32&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J32" s="25">
-        <f>IF(F32&gt;0, 1.0 - (H32/F32), IF(G32=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K32" s="26" t="inlineStr"/>
+      <c r="J32" s="25" t="inlineStr"/>
+      <c r="K32" s="26" t="n">
+        <v>200</v>
+      </c>
       <c r="L32" s="27" t="n">
         <v>200</v>
       </c>
-      <c r="M32" s="28" t="n">
+      <c r="M32" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="26" t="n">
         <v>200</v>
-      </c>
-      <c r="N32" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="28" t="n">
-        <v>0</v>
       </c>
       <c r="P32" s="27" t="n">
         <v>200</v>
       </c>
-      <c r="Q32" s="28" t="n">
-        <v>200</v>
-      </c>
-      <c r="R32" s="22">
+      <c r="Q32" s="22">
+        <f>K32+M32+O32</f>
+        <v/>
+      </c>
+      <c r="R32" s="23">
         <f>L32+N32+P32</f>
         <v/>
       </c>
-      <c r="S32" s="23">
-        <f>M32+O32+Q32</f>
-        <v/>
-      </c>
-      <c r="T32" s="29">
-        <f>S32-R32</f>
-        <v/>
-      </c>
-      <c r="U32" s="30" t="inlineStr"/>
+      <c r="S32" s="28">
+        <f>R32-Q32</f>
+        <v/>
+      </c>
+      <c r="T32" s="29" t="inlineStr"/>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="B33" s="20" t="inlineStr">
@@ -2694,42 +2584,38 @@
         <f>IF(F33&gt;0, G33/F33, IF(G33&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J33" s="25">
-        <f>IF(F33&gt;0, 1.0 - (H33/F33), IF(G33=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K33" s="26" t="inlineStr"/>
+      <c r="J33" s="25" t="inlineStr"/>
+      <c r="K33" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L33" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M33" s="28" t="n">
+      <c r="M33" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N33" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O33" s="28" t="n">
-        <v>0</v>
+      <c r="O33" s="26" t="n">
+        <v>200</v>
       </c>
       <c r="P33" s="27" t="n">
         <v>200</v>
       </c>
-      <c r="Q33" s="28" t="n">
-        <v>200</v>
-      </c>
-      <c r="R33" s="22">
+      <c r="Q33" s="22">
+        <f>K33+M33+O33</f>
+        <v/>
+      </c>
+      <c r="R33" s="23">
         <f>L33+N33+P33</f>
         <v/>
       </c>
-      <c r="S33" s="23">
-        <f>M33+O33+Q33</f>
-        <v/>
-      </c>
-      <c r="T33" s="29">
-        <f>S33-R33</f>
-        <v/>
-      </c>
-      <c r="U33" s="30" t="inlineStr"/>
+      <c r="S33" s="28">
+        <f>R33-Q33</f>
+        <v/>
+      </c>
+      <c r="T33" s="29" t="inlineStr"/>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="B34" s="20" t="inlineStr">
@@ -2766,42 +2652,38 @@
         <f>IF(F34&gt;0, G34/F34, IF(G34&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J34" s="25">
-        <f>IF(F34&gt;0, 1.0 - (H34/F34), IF(G34=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K34" s="26" t="inlineStr"/>
+      <c r="J34" s="25" t="inlineStr"/>
+      <c r="K34" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L34" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M34" s="28" t="n">
+      <c r="M34" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N34" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O34" s="28" t="n">
-        <v>0</v>
+      <c r="O34" s="26" t="n">
+        <v>5000</v>
       </c>
       <c r="P34" s="27" t="n">
         <v>5000</v>
       </c>
-      <c r="Q34" s="28" t="n">
-        <v>5000</v>
-      </c>
-      <c r="R34" s="22">
+      <c r="Q34" s="22">
+        <f>K34+M34+O34</f>
+        <v/>
+      </c>
+      <c r="R34" s="23">
         <f>L34+N34+P34</f>
         <v/>
       </c>
-      <c r="S34" s="23">
-        <f>M34+O34+Q34</f>
-        <v/>
-      </c>
-      <c r="T34" s="29">
-        <f>S34-R34</f>
-        <v/>
-      </c>
-      <c r="U34" s="30" t="inlineStr"/>
+      <c r="S34" s="28">
+        <f>R34-Q34</f>
+        <v/>
+      </c>
+      <c r="T34" s="29" t="inlineStr"/>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="B35" s="20" t="inlineStr">
@@ -2838,42 +2720,38 @@
         <f>IF(F35&gt;0, G35/F35, IF(G35&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J35" s="25">
-        <f>IF(F35&gt;0, 1.0 - (H35/F35), IF(G35=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K35" s="26" t="inlineStr"/>
+      <c r="J35" s="25" t="inlineStr"/>
+      <c r="K35" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L35" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M35" s="28" t="n">
+      <c r="M35" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N35" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O35" s="28" t="n">
-        <v>0</v>
+      <c r="O35" s="26" t="n">
+        <v>5000</v>
       </c>
       <c r="P35" s="27" t="n">
         <v>5000</v>
       </c>
-      <c r="Q35" s="28" t="n">
-        <v>5000</v>
-      </c>
-      <c r="R35" s="22">
+      <c r="Q35" s="22">
+        <f>K35+M35+O35</f>
+        <v/>
+      </c>
+      <c r="R35" s="23">
         <f>L35+N35+P35</f>
         <v/>
       </c>
-      <c r="S35" s="23">
-        <f>M35+O35+Q35</f>
-        <v/>
-      </c>
-      <c r="T35" s="29">
-        <f>S35-R35</f>
-        <v/>
-      </c>
-      <c r="U35" s="30" t="inlineStr"/>
+      <c r="S35" s="28">
+        <f>R35-Q35</f>
+        <v/>
+      </c>
+      <c r="T35" s="29" t="inlineStr"/>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="B36" s="20" t="inlineStr">
@@ -2910,42 +2788,38 @@
         <f>IF(F36&gt;0, G36/F36, IF(G36&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J36" s="25">
-        <f>IF(F36&gt;0, 1.0 - (H36/F36), IF(G36=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K36" s="26" t="inlineStr"/>
+      <c r="J36" s="25" t="inlineStr"/>
+      <c r="K36" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L36" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M36" s="28" t="n">
+      <c r="M36" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N36" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O36" s="28" t="n">
-        <v>0</v>
+      <c r="O36" s="26" t="n">
+        <v>7700</v>
       </c>
       <c r="P36" s="27" t="n">
         <v>7700</v>
       </c>
-      <c r="Q36" s="28" t="n">
-        <v>7700</v>
-      </c>
-      <c r="R36" s="22">
+      <c r="Q36" s="22">
+        <f>K36+M36+O36</f>
+        <v/>
+      </c>
+      <c r="R36" s="23">
         <f>L36+N36+P36</f>
         <v/>
       </c>
-      <c r="S36" s="23">
-        <f>M36+O36+Q36</f>
-        <v/>
-      </c>
-      <c r="T36" s="29">
-        <f>S36-R36</f>
-        <v/>
-      </c>
-      <c r="U36" s="30" t="inlineStr"/>
+      <c r="S36" s="28">
+        <f>R36-Q36</f>
+        <v/>
+      </c>
+      <c r="T36" s="29" t="inlineStr"/>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="B37" s="20" t="inlineStr">
@@ -2982,42 +2856,38 @@
         <f>IF(F37&gt;0, G37/F37, IF(G37&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J37" s="25">
-        <f>IF(F37&gt;0, 1.0 - (H37/F37), IF(G37=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K37" s="26" t="inlineStr"/>
+      <c r="J37" s="25" t="inlineStr"/>
+      <c r="K37" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L37" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M37" s="28" t="n">
+      <c r="M37" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N37" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O37" s="28" t="n">
-        <v>0</v>
+      <c r="O37" s="26" t="n">
+        <v>10000</v>
       </c>
       <c r="P37" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="Q37" s="28" t="n">
-        <v>10000</v>
-      </c>
-      <c r="R37" s="22">
+      <c r="Q37" s="22">
+        <f>K37+M37+O37</f>
+        <v/>
+      </c>
+      <c r="R37" s="23">
         <f>L37+N37+P37</f>
         <v/>
       </c>
-      <c r="S37" s="23">
-        <f>M37+O37+Q37</f>
-        <v/>
-      </c>
-      <c r="T37" s="29">
-        <f>S37-R37</f>
-        <v/>
-      </c>
-      <c r="U37" s="30" t="inlineStr"/>
+      <c r="S37" s="28">
+        <f>R37-Q37</f>
+        <v/>
+      </c>
+      <c r="T37" s="29" t="inlineStr"/>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="B38" s="20" t="inlineStr">
@@ -3054,42 +2924,38 @@
         <f>IF(F38&gt;0, G38/F38, IF(G38&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J38" s="25">
-        <f>IF(F38&gt;0, 1.0 - (H38/F38), IF(G38=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K38" s="26" t="inlineStr"/>
+      <c r="J38" s="25" t="inlineStr"/>
+      <c r="K38" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L38" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M38" s="28" t="n">
+      <c r="M38" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N38" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O38" s="28" t="n">
-        <v>0</v>
+      <c r="O38" s="26" t="n">
+        <v>1000</v>
       </c>
       <c r="P38" s="27" t="n">
         <v>1000</v>
       </c>
-      <c r="Q38" s="28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="R38" s="22">
+      <c r="Q38" s="22">
+        <f>K38+M38+O38</f>
+        <v/>
+      </c>
+      <c r="R38" s="23">
         <f>L38+N38+P38</f>
         <v/>
       </c>
-      <c r="S38" s="23">
-        <f>M38+O38+Q38</f>
-        <v/>
-      </c>
-      <c r="T38" s="29">
-        <f>S38-R38</f>
-        <v/>
-      </c>
-      <c r="U38" s="30" t="inlineStr"/>
+      <c r="S38" s="28">
+        <f>R38-Q38</f>
+        <v/>
+      </c>
+      <c r="T38" s="29" t="inlineStr"/>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="B39" s="20" t="inlineStr">
@@ -3126,42 +2992,38 @@
         <f>IF(F39&gt;0, G39/F39, IF(G39&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J39" s="25">
-        <f>IF(F39&gt;0, 1.0 - (H39/F39), IF(G39=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K39" s="26" t="inlineStr"/>
+      <c r="J39" s="25" t="inlineStr"/>
+      <c r="K39" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L39" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M39" s="28" t="n">
+      <c r="M39" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N39" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O39" s="28" t="n">
-        <v>0</v>
+      <c r="O39" s="26" t="n">
+        <v>5000</v>
       </c>
       <c r="P39" s="27" t="n">
         <v>5000</v>
       </c>
-      <c r="Q39" s="28" t="n">
-        <v>5000</v>
-      </c>
-      <c r="R39" s="22">
+      <c r="Q39" s="22">
+        <f>K39+M39+O39</f>
+        <v/>
+      </c>
+      <c r="R39" s="23">
         <f>L39+N39+P39</f>
         <v/>
       </c>
-      <c r="S39" s="23">
-        <f>M39+O39+Q39</f>
-        <v/>
-      </c>
-      <c r="T39" s="29">
-        <f>S39-R39</f>
-        <v/>
-      </c>
-      <c r="U39" s="30" t="inlineStr"/>
+      <c r="S39" s="28">
+        <f>R39-Q39</f>
+        <v/>
+      </c>
+      <c r="T39" s="29" t="inlineStr"/>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="B40" s="20" t="inlineStr">
@@ -3198,42 +3060,38 @@
         <f>IF(F40&gt;0, G40/F40, IF(G40&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J40" s="25">
-        <f>IF(F40&gt;0, 1.0 - (H40/F40), IF(G40=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K40" s="26" t="inlineStr"/>
+      <c r="J40" s="25" t="inlineStr"/>
+      <c r="K40" s="26" t="n">
+        <v>3000</v>
+      </c>
       <c r="L40" s="27" t="n">
         <v>3000</v>
       </c>
-      <c r="M40" s="28" t="n">
-        <v>3000</v>
+      <c r="M40" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="N40" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O40" s="28" t="n">
+      <c r="O40" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P40" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" s="22">
+      <c r="Q40" s="22">
+        <f>K40+M40+O40</f>
+        <v/>
+      </c>
+      <c r="R40" s="23">
         <f>L40+N40+P40</f>
         <v/>
       </c>
-      <c r="S40" s="23">
-        <f>M40+O40+Q40</f>
-        <v/>
-      </c>
-      <c r="T40" s="29">
-        <f>S40-R40</f>
-        <v/>
-      </c>
-      <c r="U40" s="30" t="inlineStr"/>
+      <c r="S40" s="28">
+        <f>R40-Q40</f>
+        <v/>
+      </c>
+      <c r="T40" s="29" t="inlineStr"/>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="B41" s="20" t="inlineStr">
@@ -3270,42 +3128,38 @@
         <f>IF(F41&gt;0, G41/F41, IF(G41&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J41" s="25">
-        <f>IF(F41&gt;0, 1.0 - (H41/F41), IF(G41=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K41" s="26" t="inlineStr"/>
+      <c r="J41" s="25" t="inlineStr"/>
+      <c r="K41" s="26" t="n">
+        <v>2000</v>
+      </c>
       <c r="L41" s="27" t="n">
         <v>2000</v>
       </c>
-      <c r="M41" s="28" t="n">
-        <v>2000</v>
+      <c r="M41" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="N41" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O41" s="28" t="n">
+      <c r="O41" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P41" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" s="22">
+      <c r="Q41" s="22">
+        <f>K41+M41+O41</f>
+        <v/>
+      </c>
+      <c r="R41" s="23">
         <f>L41+N41+P41</f>
         <v/>
       </c>
-      <c r="S41" s="23">
-        <f>M41+O41+Q41</f>
-        <v/>
-      </c>
-      <c r="T41" s="29">
-        <f>S41-R41</f>
-        <v/>
-      </c>
-      <c r="U41" s="30" t="inlineStr"/>
+      <c r="S41" s="28">
+        <f>R41-Q41</f>
+        <v/>
+      </c>
+      <c r="T41" s="29" t="inlineStr"/>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="B42" s="20" t="inlineStr">
@@ -3342,42 +3196,38 @@
         <f>IF(F42&gt;0, G42/F42, IF(G42&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J42" s="25">
-        <f>IF(F42&gt;0, 1.0 - (H42/F42), IF(G42=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K42" s="26" t="inlineStr"/>
+      <c r="J42" s="25" t="inlineStr"/>
+      <c r="K42" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L42" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M42" s="28" t="n">
-        <v>0</v>
+      <c r="M42" s="26" t="n">
+        <v>20000</v>
       </c>
       <c r="N42" s="27" t="n">
         <v>20000</v>
       </c>
-      <c r="O42" s="28" t="n">
-        <v>20000</v>
+      <c r="O42" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P42" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" s="22">
+      <c r="Q42" s="22">
+        <f>K42+M42+O42</f>
+        <v/>
+      </c>
+      <c r="R42" s="23">
         <f>L42+N42+P42</f>
         <v/>
       </c>
-      <c r="S42" s="23">
-        <f>M42+O42+Q42</f>
-        <v/>
-      </c>
-      <c r="T42" s="29">
-        <f>S42-R42</f>
-        <v/>
-      </c>
-      <c r="U42" s="30" t="inlineStr"/>
+      <c r="S42" s="28">
+        <f>R42-Q42</f>
+        <v/>
+      </c>
+      <c r="T42" s="29" t="inlineStr"/>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="B43" s="20" t="inlineStr">
@@ -3414,42 +3264,38 @@
         <f>IF(F43&gt;0, G43/F43, IF(G43&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J43" s="25">
-        <f>IF(F43&gt;0, 1.0 - (H43/F43), IF(G43=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K43" s="26" t="inlineStr"/>
+      <c r="J43" s="25" t="inlineStr"/>
+      <c r="K43" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L43" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M43" s="28" t="n">
+      <c r="M43" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N43" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O43" s="28" t="n">
-        <v>0</v>
+      <c r="O43" s="26" t="n">
+        <v>3000</v>
       </c>
       <c r="P43" s="27" t="n">
         <v>3000</v>
       </c>
-      <c r="Q43" s="28" t="n">
-        <v>3000</v>
-      </c>
-      <c r="R43" s="22">
+      <c r="Q43" s="22">
+        <f>K43+M43+O43</f>
+        <v/>
+      </c>
+      <c r="R43" s="23">
         <f>L43+N43+P43</f>
         <v/>
       </c>
-      <c r="S43" s="23">
-        <f>M43+O43+Q43</f>
-        <v/>
-      </c>
-      <c r="T43" s="29">
-        <f>S43-R43</f>
-        <v/>
-      </c>
-      <c r="U43" s="30" t="inlineStr"/>
+      <c r="S43" s="28">
+        <f>R43-Q43</f>
+        <v/>
+      </c>
+      <c r="T43" s="29" t="inlineStr"/>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="B44" s="20" t="inlineStr">
@@ -3486,42 +3332,38 @@
         <f>IF(F44&gt;0, G44/F44, IF(G44&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J44" s="25">
-        <f>IF(F44&gt;0, 1.0 - (H44/F44), IF(G44=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K44" s="26" t="inlineStr"/>
+      <c r="J44" s="25" t="inlineStr"/>
+      <c r="K44" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L44" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M44" s="28" t="n">
-        <v>0</v>
+      <c r="M44" s="26" t="n">
+        <v>7920</v>
       </c>
       <c r="N44" s="27" t="n">
         <v>7920</v>
       </c>
-      <c r="O44" s="28" t="n">
-        <v>7920</v>
+      <c r="O44" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P44" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" s="22">
+      <c r="Q44" s="22">
+        <f>K44+M44+O44</f>
+        <v/>
+      </c>
+      <c r="R44" s="23">
         <f>L44+N44+P44</f>
         <v/>
       </c>
-      <c r="S44" s="23">
-        <f>M44+O44+Q44</f>
-        <v/>
-      </c>
-      <c r="T44" s="29">
-        <f>S44-R44</f>
-        <v/>
-      </c>
-      <c r="U44" s="30" t="inlineStr"/>
+      <c r="S44" s="28">
+        <f>R44-Q44</f>
+        <v/>
+      </c>
+      <c r="T44" s="29" t="inlineStr"/>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="B45" s="20" t="inlineStr">
@@ -3558,42 +3400,38 @@
         <f>IF(F45&gt;0, G45/F45, IF(G45&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J45" s="25">
-        <f>IF(F45&gt;0, 1.0 - (H45/F45), IF(G45=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K45" s="26" t="inlineStr"/>
+      <c r="J45" s="25" t="inlineStr"/>
+      <c r="K45" s="26" t="n">
+        <v>5000</v>
+      </c>
       <c r="L45" s="27" t="n">
         <v>5000</v>
       </c>
-      <c r="M45" s="28" t="n">
-        <v>5000</v>
+      <c r="M45" s="26" t="n">
+        <v>10000</v>
       </c>
       <c r="N45" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="O45" s="28" t="n">
-        <v>10000</v>
+      <c r="O45" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P45" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" s="22">
+      <c r="Q45" s="22">
+        <f>K45+M45+O45</f>
+        <v/>
+      </c>
+      <c r="R45" s="23">
         <f>L45+N45+P45</f>
         <v/>
       </c>
-      <c r="S45" s="23">
-        <f>M45+O45+Q45</f>
-        <v/>
-      </c>
-      <c r="T45" s="29">
-        <f>S45-R45</f>
-        <v/>
-      </c>
-      <c r="U45" s="30" t="inlineStr"/>
+      <c r="S45" s="28">
+        <f>R45-Q45</f>
+        <v/>
+      </c>
+      <c r="T45" s="29" t="inlineStr"/>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="B46" s="20" t="inlineStr">
@@ -3630,42 +3468,38 @@
         <f>IF(F46&gt;0, G46/F46, IF(G46&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J46" s="25">
-        <f>IF(F46&gt;0, 1.0 - (H46/F46), IF(G46=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K46" s="26" t="inlineStr"/>
+      <c r="J46" s="25" t="inlineStr"/>
+      <c r="K46" s="26" t="n">
+        <v>20000</v>
+      </c>
       <c r="L46" s="27" t="n">
         <v>20000</v>
       </c>
-      <c r="M46" s="28" t="n">
-        <v>20000</v>
+      <c r="M46" s="26" t="n">
+        <v>30000</v>
       </c>
       <c r="N46" s="27" t="n">
         <v>30000</v>
       </c>
-      <c r="O46" s="28" t="n">
-        <v>30000</v>
+      <c r="O46" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P46" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" s="22">
+      <c r="Q46" s="22">
+        <f>K46+M46+O46</f>
+        <v/>
+      </c>
+      <c r="R46" s="23">
         <f>L46+N46+P46</f>
         <v/>
       </c>
-      <c r="S46" s="23">
-        <f>M46+O46+Q46</f>
-        <v/>
-      </c>
-      <c r="T46" s="29">
-        <f>S46-R46</f>
-        <v/>
-      </c>
-      <c r="U46" s="30" t="inlineStr"/>
+      <c r="S46" s="28">
+        <f>R46-Q46</f>
+        <v/>
+      </c>
+      <c r="T46" s="29" t="inlineStr"/>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="B47" s="20" t="inlineStr">
@@ -3702,42 +3536,38 @@
         <f>IF(F47&gt;0, G47/F47, IF(G47&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J47" s="25">
-        <f>IF(F47&gt;0, 1.0 - (H47/F47), IF(G47=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K47" s="26" t="inlineStr"/>
+      <c r="J47" s="25" t="inlineStr"/>
+      <c r="K47" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L47" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M47" s="28" t="n">
-        <v>0</v>
+      <c r="M47" s="26" t="n">
+        <v>10000</v>
       </c>
       <c r="N47" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="O47" s="28" t="n">
-        <v>10000</v>
+      <c r="O47" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P47" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" s="22">
+      <c r="Q47" s="22">
+        <f>K47+M47+O47</f>
+        <v/>
+      </c>
+      <c r="R47" s="23">
         <f>L47+N47+P47</f>
         <v/>
       </c>
-      <c r="S47" s="23">
-        <f>M47+O47+Q47</f>
-        <v/>
-      </c>
-      <c r="T47" s="29">
-        <f>S47-R47</f>
-        <v/>
-      </c>
-      <c r="U47" s="30" t="inlineStr"/>
+      <c r="S47" s="28">
+        <f>R47-Q47</f>
+        <v/>
+      </c>
+      <c r="T47" s="29" t="inlineStr"/>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="B48" s="20" t="inlineStr">
@@ -3774,46 +3604,42 @@
         <f>IF(F48&gt;0, G48/F48, IF(G48&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J48" s="25">
-        <f>IF(F48&gt;0, 1.0 - (H48/F48), IF(G48=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K48" s="26" t="inlineStr">
+      <c r="J48" s="25" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
       </c>
+      <c r="K48" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L48" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M48" s="28" t="n">
+      <c r="M48" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N48" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O48" s="28" t="n">
+      <c r="O48" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P48" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" s="22">
+      <c r="Q48" s="22">
+        <f>K48+M48+O48</f>
+        <v/>
+      </c>
+      <c r="R48" s="23">
         <f>L48+N48+P48</f>
         <v/>
       </c>
-      <c r="S48" s="23">
-        <f>M48+O48+Q48</f>
-        <v/>
-      </c>
-      <c r="T48" s="29">
-        <f>S48-R48</f>
-        <v/>
-      </c>
-      <c r="U48" s="30" t="inlineStr"/>
+      <c r="S48" s="28">
+        <f>R48-Q48</f>
+        <v/>
+      </c>
+      <c r="T48" s="29" t="inlineStr"/>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="B49" s="20" t="inlineStr">
@@ -3850,46 +3676,42 @@
         <f>IF(F49&gt;0, G49/F49, IF(G49&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J49" s="25">
-        <f>IF(F49&gt;0, 1.0 - (H49/F49), IF(G49=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K49" s="26" t="inlineStr">
+      <c r="J49" s="25" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
       </c>
+      <c r="K49" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L49" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M49" s="28" t="n">
+      <c r="M49" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N49" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O49" s="28" t="n">
+      <c r="O49" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P49" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" s="22">
+      <c r="Q49" s="22">
+        <f>K49+M49+O49</f>
+        <v/>
+      </c>
+      <c r="R49" s="23">
         <f>L49+N49+P49</f>
         <v/>
       </c>
-      <c r="S49" s="23">
-        <f>M49+O49+Q49</f>
-        <v/>
-      </c>
-      <c r="T49" s="29">
-        <f>S49-R49</f>
-        <v/>
-      </c>
-      <c r="U49" s="30" t="inlineStr"/>
+      <c r="S49" s="28">
+        <f>R49-Q49</f>
+        <v/>
+      </c>
+      <c r="T49" s="29" t="inlineStr"/>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="B50" s="20" t="inlineStr">
@@ -3926,46 +3748,42 @@
         <f>IF(F50&gt;0, G50/F50, IF(G50&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J50" s="25">
-        <f>IF(F50&gt;0, 1.0 - (H50/F50), IF(G50=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K50" s="26" t="inlineStr">
+      <c r="J50" s="25" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
       </c>
+      <c r="K50" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L50" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M50" s="28" t="n">
+      <c r="M50" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N50" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O50" s="28" t="n">
+      <c r="O50" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P50" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" s="22">
+      <c r="Q50" s="22">
+        <f>K50+M50+O50</f>
+        <v/>
+      </c>
+      <c r="R50" s="23">
         <f>L50+N50+P50</f>
         <v/>
       </c>
-      <c r="S50" s="23">
-        <f>M50+O50+Q50</f>
-        <v/>
-      </c>
-      <c r="T50" s="29">
-        <f>S50-R50</f>
-        <v/>
-      </c>
-      <c r="U50" s="30" t="inlineStr"/>
+      <c r="S50" s="28">
+        <f>R50-Q50</f>
+        <v/>
+      </c>
+      <c r="T50" s="29" t="inlineStr"/>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="B51" s="20" t="inlineStr">
@@ -4002,46 +3820,42 @@
         <f>IF(F51&gt;0, G51/F51, IF(G51&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J51" s="25">
-        <f>IF(F51&gt;0, 1.0 - (H51/F51), IF(G51=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K51" s="26" t="inlineStr">
+      <c r="J51" s="25" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
       </c>
+      <c r="K51" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L51" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M51" s="28" t="n">
+      <c r="M51" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N51" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O51" s="28" t="n">
+      <c r="O51" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P51" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" s="22">
+      <c r="Q51" s="22">
+        <f>K51+M51+O51</f>
+        <v/>
+      </c>
+      <c r="R51" s="23">
         <f>L51+N51+P51</f>
         <v/>
       </c>
-      <c r="S51" s="23">
-        <f>M51+O51+Q51</f>
-        <v/>
-      </c>
-      <c r="T51" s="29">
-        <f>S51-R51</f>
-        <v/>
-      </c>
-      <c r="U51" s="30" t="inlineStr"/>
+      <c r="S51" s="28">
+        <f>R51-Q51</f>
+        <v/>
+      </c>
+      <c r="T51" s="29" t="inlineStr"/>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="B52" s="20" t="inlineStr">
@@ -4078,46 +3892,42 @@
         <f>IF(F52&gt;0, G52/F52, IF(G52&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J52" s="25">
-        <f>IF(F52&gt;0, 1.0 - (H52/F52), IF(G52=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K52" s="26" t="inlineStr">
+      <c r="J52" s="25" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
       </c>
+      <c r="K52" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L52" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M52" s="28" t="n">
+      <c r="M52" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N52" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O52" s="28" t="n">
+      <c r="O52" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P52" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" s="22">
+      <c r="Q52" s="22">
+        <f>K52+M52+O52</f>
+        <v/>
+      </c>
+      <c r="R52" s="23">
         <f>L52+N52+P52</f>
         <v/>
       </c>
-      <c r="S52" s="23">
-        <f>M52+O52+Q52</f>
-        <v/>
-      </c>
-      <c r="T52" s="29">
-        <f>S52-R52</f>
-        <v/>
-      </c>
-      <c r="U52" s="30" t="inlineStr"/>
+      <c r="S52" s="28">
+        <f>R52-Q52</f>
+        <v/>
+      </c>
+      <c r="T52" s="29" t="inlineStr"/>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="B53" s="20" t="inlineStr">
@@ -4154,42 +3964,38 @@
         <f>IF(F53&gt;0, G53/F53, IF(G53&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J53" s="25">
-        <f>IF(F53&gt;0, 1.0 - (H53/F53), IF(G53=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K53" s="26" t="inlineStr"/>
+      <c r="J53" s="25" t="inlineStr"/>
+      <c r="K53" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L53" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M53" s="28" t="n">
+      <c r="M53" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N53" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O53" s="28" t="n">
-        <v>0</v>
+      <c r="O53" s="26" t="n">
+        <v>640</v>
       </c>
       <c r="P53" s="27" t="n">
         <v>640</v>
       </c>
-      <c r="Q53" s="28" t="n">
-        <v>640</v>
-      </c>
-      <c r="R53" s="22">
+      <c r="Q53" s="22">
+        <f>K53+M53+O53</f>
+        <v/>
+      </c>
+      <c r="R53" s="23">
         <f>L53+N53+P53</f>
         <v/>
       </c>
-      <c r="S53" s="23">
-        <f>M53+O53+Q53</f>
-        <v/>
-      </c>
-      <c r="T53" s="29">
-        <f>S53-R53</f>
-        <v/>
-      </c>
-      <c r="U53" s="30" t="inlineStr"/>
+      <c r="S53" s="28">
+        <f>R53-Q53</f>
+        <v/>
+      </c>
+      <c r="T53" s="29" t="inlineStr"/>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="B54" s="20" t="inlineStr">
@@ -4226,46 +4032,42 @@
         <f>IF(F54&gt;0, G54/F54, IF(G54&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J54" s="25">
-        <f>IF(F54&gt;0, 1.0 - (H54/F54), IF(G54=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K54" s="26" t="inlineStr">
+      <c r="J54" s="25" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
       </c>
+      <c r="K54" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L54" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M54" s="28" t="n">
+      <c r="M54" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N54" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O54" s="28" t="n">
+      <c r="O54" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P54" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" s="22">
+      <c r="Q54" s="22">
+        <f>K54+M54+O54</f>
+        <v/>
+      </c>
+      <c r="R54" s="23">
         <f>L54+N54+P54</f>
         <v/>
       </c>
-      <c r="S54" s="23">
-        <f>M54+O54+Q54</f>
-        <v/>
-      </c>
-      <c r="T54" s="29">
-        <f>S54-R54</f>
-        <v/>
-      </c>
-      <c r="U54" s="30" t="inlineStr"/>
+      <c r="S54" s="28">
+        <f>R54-Q54</f>
+        <v/>
+      </c>
+      <c r="T54" s="29" t="inlineStr"/>
     </row>
     <row r="55" ht="20" customHeight="1">
       <c r="B55" s="20" t="inlineStr">
@@ -4302,42 +4104,38 @@
         <f>IF(F55&gt;0, G55/F55, IF(G55&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J55" s="25">
-        <f>IF(F55&gt;0, 1.0 - (H55/F55), IF(G55=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K55" s="26" t="inlineStr"/>
+      <c r="J55" s="25" t="inlineStr"/>
+      <c r="K55" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L55" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M55" s="28" t="n">
+      <c r="M55" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N55" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O55" s="28" t="n">
-        <v>0</v>
+      <c r="O55" s="26" t="n">
+        <v>8000</v>
       </c>
       <c r="P55" s="27" t="n">
         <v>8000</v>
       </c>
-      <c r="Q55" s="28" t="n">
-        <v>8000</v>
-      </c>
-      <c r="R55" s="22">
+      <c r="Q55" s="22">
+        <f>K55+M55+O55</f>
+        <v/>
+      </c>
+      <c r="R55" s="23">
         <f>L55+N55+P55</f>
         <v/>
       </c>
-      <c r="S55" s="23">
-        <f>M55+O55+Q55</f>
-        <v/>
-      </c>
-      <c r="T55" s="29">
-        <f>S55-R55</f>
-        <v/>
-      </c>
-      <c r="U55" s="30" t="inlineStr"/>
+      <c r="S55" s="28">
+        <f>R55-Q55</f>
+        <v/>
+      </c>
+      <c r="T55" s="29" t="inlineStr"/>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="B56" s="20" t="inlineStr">
@@ -4374,42 +4172,38 @@
         <f>IF(F56&gt;0, G56/F56, IF(G56&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J56" s="25">
-        <f>IF(F56&gt;0, 1.0 - (H56/F56), IF(G56=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K56" s="26" t="inlineStr"/>
+      <c r="J56" s="25" t="inlineStr"/>
+      <c r="K56" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L56" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M56" s="28" t="n">
+      <c r="M56" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N56" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O56" s="28" t="n">
-        <v>0</v>
+      <c r="O56" s="26" t="n">
+        <v>4000</v>
       </c>
       <c r="P56" s="27" t="n">
         <v>4000</v>
       </c>
-      <c r="Q56" s="28" t="n">
-        <v>4000</v>
-      </c>
-      <c r="R56" s="22">
+      <c r="Q56" s="22">
+        <f>K56+M56+O56</f>
+        <v/>
+      </c>
+      <c r="R56" s="23">
         <f>L56+N56+P56</f>
         <v/>
       </c>
-      <c r="S56" s="23">
-        <f>M56+O56+Q56</f>
-        <v/>
-      </c>
-      <c r="T56" s="29">
-        <f>S56-R56</f>
-        <v/>
-      </c>
-      <c r="U56" s="30" t="inlineStr"/>
+      <c r="S56" s="28">
+        <f>R56-Q56</f>
+        <v/>
+      </c>
+      <c r="T56" s="29" t="inlineStr"/>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="B57" s="20" t="inlineStr">
@@ -4446,42 +4240,38 @@
         <f>IF(F57&gt;0, G57/F57, IF(G57&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J57" s="25">
-        <f>IF(F57&gt;0, 1.0 - (H57/F57), IF(G57=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K57" s="26" t="inlineStr"/>
+      <c r="J57" s="25" t="inlineStr"/>
+      <c r="K57" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L57" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M57" s="28" t="n">
+      <c r="M57" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N57" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O57" s="28" t="n">
-        <v>0</v>
+      <c r="O57" s="26" t="n">
+        <v>10000</v>
       </c>
       <c r="P57" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="Q57" s="28" t="n">
-        <v>10000</v>
-      </c>
-      <c r="R57" s="22">
+      <c r="Q57" s="22">
+        <f>K57+M57+O57</f>
+        <v/>
+      </c>
+      <c r="R57" s="23">
         <f>L57+N57+P57</f>
         <v/>
       </c>
-      <c r="S57" s="23">
-        <f>M57+O57+Q57</f>
-        <v/>
-      </c>
-      <c r="T57" s="29">
-        <f>S57-R57</f>
-        <v/>
-      </c>
-      <c r="U57" s="30" t="inlineStr"/>
+      <c r="S57" s="28">
+        <f>R57-Q57</f>
+        <v/>
+      </c>
+      <c r="T57" s="29" t="inlineStr"/>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="B58" s="20" t="inlineStr">
@@ -4518,42 +4308,38 @@
         <f>IF(F58&gt;0, G58/F58, IF(G58&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J58" s="25">
-        <f>IF(F58&gt;0, 1.0 - (H58/F58), IF(G58=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K58" s="26" t="inlineStr"/>
+      <c r="J58" s="25" t="inlineStr"/>
+      <c r="K58" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L58" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M58" s="28" t="n">
+      <c r="M58" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N58" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O58" s="28" t="n">
-        <v>0</v>
+      <c r="O58" s="26" t="n">
+        <v>10000</v>
       </c>
       <c r="P58" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="Q58" s="28" t="n">
-        <v>10000</v>
-      </c>
-      <c r="R58" s="22">
+      <c r="Q58" s="22">
+        <f>K58+M58+O58</f>
+        <v/>
+      </c>
+      <c r="R58" s="23">
         <f>L58+N58+P58</f>
         <v/>
       </c>
-      <c r="S58" s="23">
-        <f>M58+O58+Q58</f>
-        <v/>
-      </c>
-      <c r="T58" s="29">
-        <f>S58-R58</f>
-        <v/>
-      </c>
-      <c r="U58" s="30" t="inlineStr"/>
+      <c r="S58" s="28">
+        <f>R58-Q58</f>
+        <v/>
+      </c>
+      <c r="T58" s="29" t="inlineStr"/>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="B59" s="20" t="inlineStr">
@@ -4590,42 +4376,38 @@
         <f>IF(F59&gt;0, G59/F59, IF(G59&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J59" s="25">
-        <f>IF(F59&gt;0, 1.0 - (H59/F59), IF(G59=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K59" s="26" t="inlineStr"/>
+      <c r="J59" s="25" t="inlineStr"/>
+      <c r="K59" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L59" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M59" s="28" t="n">
+      <c r="M59" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N59" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O59" s="28" t="n">
-        <v>0</v>
+      <c r="O59" s="26" t="n">
+        <v>2000</v>
       </c>
       <c r="P59" s="27" t="n">
         <v>2000</v>
       </c>
-      <c r="Q59" s="28" t="n">
-        <v>2000</v>
-      </c>
-      <c r="R59" s="22">
+      <c r="Q59" s="22">
+        <f>K59+M59+O59</f>
+        <v/>
+      </c>
+      <c r="R59" s="23">
         <f>L59+N59+P59</f>
         <v/>
       </c>
-      <c r="S59" s="23">
-        <f>M59+O59+Q59</f>
-        <v/>
-      </c>
-      <c r="T59" s="29">
-        <f>S59-R59</f>
-        <v/>
-      </c>
-      <c r="U59" s="30" t="inlineStr"/>
+      <c r="S59" s="28">
+        <f>R59-Q59</f>
+        <v/>
+      </c>
+      <c r="T59" s="29" t="inlineStr"/>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="B60" s="20" t="inlineStr">
@@ -4662,42 +4444,38 @@
         <f>IF(F60&gt;0, G60/F60, IF(G60&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J60" s="25">
-        <f>IF(F60&gt;0, 1.0 - (H60/F60), IF(G60=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K60" s="26" t="inlineStr"/>
+      <c r="J60" s="25" t="inlineStr"/>
+      <c r="K60" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L60" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M60" s="28" t="n">
+      <c r="M60" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N60" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O60" s="28" t="n">
-        <v>0</v>
+      <c r="O60" s="26" t="n">
+        <v>1280</v>
       </c>
       <c r="P60" s="27" t="n">
         <v>1280</v>
       </c>
-      <c r="Q60" s="28" t="n">
-        <v>1280</v>
-      </c>
-      <c r="R60" s="22">
+      <c r="Q60" s="22">
+        <f>K60+M60+O60</f>
+        <v/>
+      </c>
+      <c r="R60" s="23">
         <f>L60+N60+P60</f>
         <v/>
       </c>
-      <c r="S60" s="23">
-        <f>M60+O60+Q60</f>
-        <v/>
-      </c>
-      <c r="T60" s="29">
-        <f>S60-R60</f>
-        <v/>
-      </c>
-      <c r="U60" s="30" t="inlineStr"/>
+      <c r="S60" s="28">
+        <f>R60-Q60</f>
+        <v/>
+      </c>
+      <c r="T60" s="29" t="inlineStr"/>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="B61" s="20" t="inlineStr">
@@ -4734,42 +4512,38 @@
         <f>IF(F61&gt;0, G61/F61, IF(G61&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J61" s="25">
-        <f>IF(F61&gt;0, 1.0 - (H61/F61), IF(G61=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K61" s="26" t="inlineStr"/>
+      <c r="J61" s="25" t="inlineStr"/>
+      <c r="K61" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L61" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M61" s="28" t="n">
+      <c r="M61" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N61" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O61" s="28" t="n">
-        <v>0</v>
+      <c r="O61" s="26" t="n">
+        <v>25</v>
       </c>
       <c r="P61" s="27" t="n">
         <v>25</v>
       </c>
-      <c r="Q61" s="28" t="n">
-        <v>25</v>
-      </c>
-      <c r="R61" s="22">
+      <c r="Q61" s="22">
+        <f>K61+M61+O61</f>
+        <v/>
+      </c>
+      <c r="R61" s="23">
         <f>L61+N61+P61</f>
         <v/>
       </c>
-      <c r="S61" s="23">
-        <f>M61+O61+Q61</f>
-        <v/>
-      </c>
-      <c r="T61" s="29">
-        <f>S61-R61</f>
-        <v/>
-      </c>
-      <c r="U61" s="30" t="inlineStr"/>
+      <c r="S61" s="28">
+        <f>R61-Q61</f>
+        <v/>
+      </c>
+      <c r="T61" s="29" t="inlineStr"/>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="B62" s="20" t="inlineStr">
@@ -4806,42 +4580,38 @@
         <f>IF(F62&gt;0, G62/F62, IF(G62&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J62" s="25">
-        <f>IF(F62&gt;0, 1.0 - (H62/F62), IF(G62=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K62" s="26" t="inlineStr"/>
+      <c r="J62" s="25" t="inlineStr"/>
+      <c r="K62" s="26" t="n">
+        <v>1920</v>
+      </c>
       <c r="L62" s="27" t="n">
         <v>1920</v>
       </c>
-      <c r="M62" s="28" t="n">
-        <v>1920</v>
+      <c r="M62" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="N62" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O62" s="28" t="n">
+      <c r="O62" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P62" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" s="22">
+      <c r="Q62" s="22">
+        <f>K62+M62+O62</f>
+        <v/>
+      </c>
+      <c r="R62" s="23">
         <f>L62+N62+P62</f>
         <v/>
       </c>
-      <c r="S62" s="23">
-        <f>M62+O62+Q62</f>
-        <v/>
-      </c>
-      <c r="T62" s="29">
-        <f>S62-R62</f>
-        <v/>
-      </c>
-      <c r="U62" s="30" t="inlineStr"/>
+      <c r="S62" s="28">
+        <f>R62-Q62</f>
+        <v/>
+      </c>
+      <c r="T62" s="29" t="inlineStr"/>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="B63" s="20" t="inlineStr">
@@ -4878,42 +4648,38 @@
         <f>IF(F63&gt;0, G63/F63, IF(G63&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J63" s="25">
-        <f>IF(F63&gt;0, 1.0 - (H63/F63), IF(G63=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K63" s="26" t="inlineStr"/>
+      <c r="J63" s="25" t="inlineStr"/>
+      <c r="K63" s="26" t="n">
+        <v>75</v>
+      </c>
       <c r="L63" s="27" t="n">
         <v>75</v>
       </c>
-      <c r="M63" s="28" t="n">
-        <v>75</v>
+      <c r="M63" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="N63" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O63" s="28" t="n">
+      <c r="O63" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P63" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" s="22">
+      <c r="Q63" s="22">
+        <f>K63+M63+O63</f>
+        <v/>
+      </c>
+      <c r="R63" s="23">
         <f>L63+N63+P63</f>
         <v/>
       </c>
-      <c r="S63" s="23">
-        <f>M63+O63+Q63</f>
-        <v/>
-      </c>
-      <c r="T63" s="29">
-        <f>S63-R63</f>
-        <v/>
-      </c>
-      <c r="U63" s="30" t="inlineStr"/>
+      <c r="S63" s="28">
+        <f>R63-Q63</f>
+        <v/>
+      </c>
+      <c r="T63" s="29" t="inlineStr"/>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="B64" s="20" t="inlineStr">
@@ -4950,42 +4716,38 @@
         <f>IF(F64&gt;0, G64/F64, IF(G64&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J64" s="25">
-        <f>IF(F64&gt;0, 1.0 - (H64/F64), IF(G64=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K64" s="26" t="inlineStr"/>
+      <c r="J64" s="25" t="inlineStr"/>
+      <c r="K64" s="26" t="n">
+        <v>80</v>
+      </c>
       <c r="L64" s="27" t="n">
         <v>80</v>
       </c>
-      <c r="M64" s="28" t="n">
-        <v>80</v>
+      <c r="M64" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="N64" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O64" s="28" t="n">
-        <v>0</v>
+      <c r="O64" s="26" t="n">
+        <v>240</v>
       </c>
       <c r="P64" s="27" t="n">
         <v>240</v>
       </c>
-      <c r="Q64" s="28" t="n">
-        <v>240</v>
-      </c>
-      <c r="R64" s="22">
+      <c r="Q64" s="22">
+        <f>K64+M64+O64</f>
+        <v/>
+      </c>
+      <c r="R64" s="23">
         <f>L64+N64+P64</f>
         <v/>
       </c>
-      <c r="S64" s="23">
-        <f>M64+O64+Q64</f>
-        <v/>
-      </c>
-      <c r="T64" s="29">
-        <f>S64-R64</f>
-        <v/>
-      </c>
-      <c r="U64" s="30" t="inlineStr"/>
+      <c r="S64" s="28">
+        <f>R64-Q64</f>
+        <v/>
+      </c>
+      <c r="T64" s="29" t="inlineStr"/>
     </row>
     <row r="65" ht="20" customHeight="1">
       <c r="B65" s="20" t="inlineStr">
@@ -5022,42 +4784,38 @@
         <f>IF(F65&gt;0, G65/F65, IF(G65&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J65" s="25">
-        <f>IF(F65&gt;0, 1.0 - (H65/F65), IF(G65=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K65" s="26" t="inlineStr"/>
+      <c r="J65" s="25" t="inlineStr"/>
+      <c r="K65" s="26" t="n">
+        <v>800</v>
+      </c>
       <c r="L65" s="27" t="n">
         <v>800</v>
       </c>
-      <c r="M65" s="28" t="n">
-        <v>800</v>
+      <c r="M65" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="N65" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O65" s="28" t="n">
+      <c r="O65" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P65" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" s="22">
+      <c r="Q65" s="22">
+        <f>K65+M65+O65</f>
+        <v/>
+      </c>
+      <c r="R65" s="23">
         <f>L65+N65+P65</f>
         <v/>
       </c>
-      <c r="S65" s="23">
-        <f>M65+O65+Q65</f>
-        <v/>
-      </c>
-      <c r="T65" s="29">
-        <f>S65-R65</f>
-        <v/>
-      </c>
-      <c r="U65" s="30" t="inlineStr"/>
+      <c r="S65" s="28">
+        <f>R65-Q65</f>
+        <v/>
+      </c>
+      <c r="T65" s="29" t="inlineStr"/>
     </row>
     <row r="66" ht="20" customHeight="1">
       <c r="B66" s="20" t="inlineStr">
@@ -5094,46 +4852,42 @@
         <f>IF(F66&gt;0, G66/F66, IF(G66&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J66" s="25">
-        <f>IF(F66&gt;0, 1.0 - (H66/F66), IF(G66=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K66" s="26" t="inlineStr">
+      <c r="J66" s="25" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
+      </c>
+      <c r="K66" s="26" t="n">
+        <v>1056</v>
       </c>
       <c r="L66" s="27" t="n">
         <v>1056</v>
       </c>
-      <c r="M66" s="28" t="n">
-        <v>1056</v>
+      <c r="M66" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="N66" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O66" s="28" t="n">
+      <c r="O66" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P66" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R66" s="22">
+      <c r="Q66" s="22">
+        <f>K66+M66+O66</f>
+        <v/>
+      </c>
+      <c r="R66" s="23">
         <f>L66+N66+P66</f>
         <v/>
       </c>
-      <c r="S66" s="23">
-        <f>M66+O66+Q66</f>
-        <v/>
-      </c>
-      <c r="T66" s="29">
-        <f>S66-R66</f>
-        <v/>
-      </c>
-      <c r="U66" s="30" t="inlineStr"/>
+      <c r="S66" s="28">
+        <f>R66-Q66</f>
+        <v/>
+      </c>
+      <c r="T66" s="29" t="inlineStr"/>
     </row>
     <row r="67" ht="20" customHeight="1">
       <c r="B67" s="20" t="inlineStr">
@@ -5170,46 +4924,42 @@
         <f>IF(F67&gt;0, G67/F67, IF(G67&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J67" s="25">
-        <f>IF(F67&gt;0, 1.0 - (H67/F67), IF(G67=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K67" s="26" t="inlineStr">
+      <c r="J67" s="25" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
+      </c>
+      <c r="K67" s="26" t="n">
+        <v>528</v>
       </c>
       <c r="L67" s="27" t="n">
         <v>528</v>
       </c>
-      <c r="M67" s="28" t="n">
-        <v>528</v>
+      <c r="M67" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="N67" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O67" s="28" t="n">
+      <c r="O67" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P67" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R67" s="22">
+      <c r="Q67" s="22">
+        <f>K67+M67+O67</f>
+        <v/>
+      </c>
+      <c r="R67" s="23">
         <f>L67+N67+P67</f>
         <v/>
       </c>
-      <c r="S67" s="23">
-        <f>M67+O67+Q67</f>
-        <v/>
-      </c>
-      <c r="T67" s="29">
-        <f>S67-R67</f>
-        <v/>
-      </c>
-      <c r="U67" s="30" t="inlineStr"/>
+      <c r="S67" s="28">
+        <f>R67-Q67</f>
+        <v/>
+      </c>
+      <c r="T67" s="29" t="inlineStr"/>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="B68" s="20" t="inlineStr">
@@ -5246,42 +4996,38 @@
         <f>IF(F68&gt;0, G68/F68, IF(G68&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J68" s="25">
-        <f>IF(F68&gt;0, 1.0 - (H68/F68), IF(G68=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K68" s="26" t="inlineStr"/>
+      <c r="J68" s="25" t="inlineStr"/>
+      <c r="K68" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L68" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M68" s="28" t="n">
-        <v>0</v>
+      <c r="M68" s="26" t="n">
+        <v>640</v>
       </c>
       <c r="N68" s="27" t="n">
         <v>640</v>
       </c>
-      <c r="O68" s="28" t="n">
-        <v>640</v>
+      <c r="O68" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P68" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R68" s="22">
+      <c r="Q68" s="22">
+        <f>K68+M68+O68</f>
+        <v/>
+      </c>
+      <c r="R68" s="23">
         <f>L68+N68+P68</f>
         <v/>
       </c>
-      <c r="S68" s="23">
-        <f>M68+O68+Q68</f>
-        <v/>
-      </c>
-      <c r="T68" s="29">
-        <f>S68-R68</f>
-        <v/>
-      </c>
-      <c r="U68" s="30" t="inlineStr"/>
+      <c r="S68" s="28">
+        <f>R68-Q68</f>
+        <v/>
+      </c>
+      <c r="T68" s="29" t="inlineStr"/>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="B69" s="20" t="inlineStr">
@@ -5318,42 +5064,38 @@
         <f>IF(F69&gt;0, G69/F69, IF(G69&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J69" s="25">
-        <f>IF(F69&gt;0, 1.0 - (H69/F69), IF(G69=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K69" s="26" t="inlineStr"/>
+      <c r="J69" s="25" t="inlineStr"/>
+      <c r="K69" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L69" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M69" s="28" t="n">
-        <v>0</v>
+      <c r="M69" s="26" t="n">
+        <v>1000</v>
       </c>
       <c r="N69" s="27" t="n">
         <v>1000</v>
       </c>
-      <c r="O69" s="28" t="n">
-        <v>1000</v>
+      <c r="O69" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P69" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R69" s="22">
+      <c r="Q69" s="22">
+        <f>K69+M69+O69</f>
+        <v/>
+      </c>
+      <c r="R69" s="23">
         <f>L69+N69+P69</f>
         <v/>
       </c>
-      <c r="S69" s="23">
-        <f>M69+O69+Q69</f>
-        <v/>
-      </c>
-      <c r="T69" s="29">
-        <f>S69-R69</f>
-        <v/>
-      </c>
-      <c r="U69" s="30" t="inlineStr"/>
+      <c r="S69" s="28">
+        <f>R69-Q69</f>
+        <v/>
+      </c>
+      <c r="T69" s="29" t="inlineStr"/>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="B70" s="20" t="inlineStr">
@@ -5390,42 +5132,38 @@
         <f>IF(F70&gt;0, G70/F70, IF(G70&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J70" s="25">
-        <f>IF(F70&gt;0, 1.0 - (H70/F70), IF(G70=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K70" s="26" t="inlineStr"/>
+      <c r="J70" s="25" t="inlineStr"/>
+      <c r="K70" s="26" t="n">
+        <v>396</v>
+      </c>
       <c r="L70" s="27" t="n">
         <v>396</v>
       </c>
-      <c r="M70" s="28" t="n">
-        <v>396</v>
+      <c r="M70" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="N70" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O70" s="28" t="n">
+      <c r="O70" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P70" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R70" s="22">
+      <c r="Q70" s="22">
+        <f>K70+M70+O70</f>
+        <v/>
+      </c>
+      <c r="R70" s="23">
         <f>L70+N70+P70</f>
         <v/>
       </c>
-      <c r="S70" s="23">
-        <f>M70+O70+Q70</f>
-        <v/>
-      </c>
-      <c r="T70" s="29">
-        <f>S70-R70</f>
-        <v/>
-      </c>
-      <c r="U70" s="30" t="inlineStr"/>
+      <c r="S70" s="28">
+        <f>R70-Q70</f>
+        <v/>
+      </c>
+      <c r="T70" s="29" t="inlineStr"/>
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="B71" s="20" t="inlineStr">
@@ -5462,46 +5200,42 @@
         <f>IF(F71&gt;0, G71/F71, IF(G71&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J71" s="25">
-        <f>IF(F71&gt;0, 1.0 - (H71/F71), IF(G71=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K71" s="26" t="inlineStr">
+      <c r="J71" s="25" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
       </c>
+      <c r="K71" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L71" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M71" s="28" t="n">
+      <c r="M71" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N71" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O71" s="28" t="n">
+      <c r="O71" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P71" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R71" s="22">
+      <c r="Q71" s="22">
+        <f>K71+M71+O71</f>
+        <v/>
+      </c>
+      <c r="R71" s="23">
         <f>L71+N71+P71</f>
         <v/>
       </c>
-      <c r="S71" s="23">
-        <f>M71+O71+Q71</f>
-        <v/>
-      </c>
-      <c r="T71" s="29">
-        <f>S71-R71</f>
-        <v/>
-      </c>
-      <c r="U71" s="30" t="inlineStr"/>
+      <c r="S71" s="28">
+        <f>R71-Q71</f>
+        <v/>
+      </c>
+      <c r="T71" s="29" t="inlineStr"/>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="B72" s="20" t="inlineStr">
@@ -5538,42 +5272,38 @@
         <f>IF(F72&gt;0, G72/F72, IF(G72&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J72" s="25">
-        <f>IF(F72&gt;0, 1.0 - (H72/F72), IF(G72=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K72" s="26" t="inlineStr"/>
+      <c r="J72" s="25" t="inlineStr"/>
+      <c r="K72" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L72" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M72" s="28" t="n">
-        <v>0</v>
+      <c r="M72" s="26" t="n">
+        <v>1100</v>
       </c>
       <c r="N72" s="27" t="n">
         <v>1100</v>
       </c>
-      <c r="O72" s="28" t="n">
-        <v>1100</v>
+      <c r="O72" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P72" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R72" s="22">
+      <c r="Q72" s="22">
+        <f>K72+M72+O72</f>
+        <v/>
+      </c>
+      <c r="R72" s="23">
         <f>L72+N72+P72</f>
         <v/>
       </c>
-      <c r="S72" s="23">
-        <f>M72+O72+Q72</f>
-        <v/>
-      </c>
-      <c r="T72" s="29">
-        <f>S72-R72</f>
-        <v/>
-      </c>
-      <c r="U72" s="30" t="inlineStr"/>
+      <c r="S72" s="28">
+        <f>R72-Q72</f>
+        <v/>
+      </c>
+      <c r="T72" s="29" t="inlineStr"/>
     </row>
     <row r="73" ht="20" customHeight="1">
       <c r="B73" s="20" t="inlineStr">
@@ -5610,42 +5340,38 @@
         <f>IF(F73&gt;0, G73/F73, IF(G73&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J73" s="25">
-        <f>IF(F73&gt;0, 1.0 - (H73/F73), IF(G73=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K73" s="26" t="inlineStr"/>
+      <c r="J73" s="25" t="inlineStr"/>
+      <c r="K73" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L73" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M73" s="28" t="n">
-        <v>0</v>
+      <c r="M73" s="26" t="n">
+        <v>300</v>
       </c>
       <c r="N73" s="27" t="n">
         <v>300</v>
       </c>
-      <c r="O73" s="28" t="n">
-        <v>300</v>
+      <c r="O73" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P73" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R73" s="22">
+      <c r="Q73" s="22">
+        <f>K73+M73+O73</f>
+        <v/>
+      </c>
+      <c r="R73" s="23">
         <f>L73+N73+P73</f>
         <v/>
       </c>
-      <c r="S73" s="23">
-        <f>M73+O73+Q73</f>
-        <v/>
-      </c>
-      <c r="T73" s="29">
-        <f>S73-R73</f>
-        <v/>
-      </c>
-      <c r="U73" s="30" t="inlineStr"/>
+      <c r="S73" s="28">
+        <f>R73-Q73</f>
+        <v/>
+      </c>
+      <c r="T73" s="29" t="inlineStr"/>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="B74" s="20" t="inlineStr">
@@ -5682,42 +5408,38 @@
         <f>IF(F74&gt;0, G74/F74, IF(G74&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J74" s="25">
-        <f>IF(F74&gt;0, 1.0 - (H74/F74), IF(G74=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K74" s="26" t="inlineStr"/>
+      <c r="J74" s="25" t="inlineStr"/>
+      <c r="K74" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L74" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M74" s="28" t="n">
-        <v>0</v>
+      <c r="M74" s="26" t="n">
+        <v>400</v>
       </c>
       <c r="N74" s="27" t="n">
         <v>400</v>
       </c>
-      <c r="O74" s="28" t="n">
-        <v>400</v>
+      <c r="O74" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P74" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R74" s="22">
+      <c r="Q74" s="22">
+        <f>K74+M74+O74</f>
+        <v/>
+      </c>
+      <c r="R74" s="23">
         <f>L74+N74+P74</f>
         <v/>
       </c>
-      <c r="S74" s="23">
-        <f>M74+O74+Q74</f>
-        <v/>
-      </c>
-      <c r="T74" s="29">
-        <f>S74-R74</f>
-        <v/>
-      </c>
-      <c r="U74" s="30" t="inlineStr"/>
+      <c r="S74" s="28">
+        <f>R74-Q74</f>
+        <v/>
+      </c>
+      <c r="T74" s="29" t="inlineStr"/>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="B75" s="20" t="inlineStr">
@@ -5754,42 +5476,38 @@
         <f>IF(F75&gt;0, G75/F75, IF(G75&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J75" s="25">
-        <f>IF(F75&gt;0, 1.0 - (H75/F75), IF(G75=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K75" s="26" t="inlineStr"/>
+      <c r="J75" s="25" t="inlineStr"/>
+      <c r="K75" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L75" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M75" s="28" t="n">
-        <v>0</v>
+      <c r="M75" s="26" t="n">
+        <v>660</v>
       </c>
       <c r="N75" s="27" t="n">
         <v>660</v>
       </c>
-      <c r="O75" s="28" t="n">
-        <v>660</v>
+      <c r="O75" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P75" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R75" s="22">
+      <c r="Q75" s="22">
+        <f>K75+M75+O75</f>
+        <v/>
+      </c>
+      <c r="R75" s="23">
         <f>L75+N75+P75</f>
         <v/>
       </c>
-      <c r="S75" s="23">
-        <f>M75+O75+Q75</f>
-        <v/>
-      </c>
-      <c r="T75" s="29">
-        <f>S75-R75</f>
-        <v/>
-      </c>
-      <c r="U75" s="30" t="inlineStr"/>
+      <c r="S75" s="28">
+        <f>R75-Q75</f>
+        <v/>
+      </c>
+      <c r="T75" s="29" t="inlineStr"/>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="B76" s="20" t="inlineStr">
@@ -5826,42 +5544,38 @@
         <f>IF(F76&gt;0, G76/F76, IF(G76&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J76" s="25">
-        <f>IF(F76&gt;0, 1.0 - (H76/F76), IF(G76=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K76" s="26" t="inlineStr"/>
+      <c r="J76" s="25" t="inlineStr"/>
+      <c r="K76" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L76" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M76" s="28" t="n">
-        <v>0</v>
+      <c r="M76" s="26" t="n">
+        <v>640</v>
       </c>
       <c r="N76" s="27" t="n">
         <v>640</v>
       </c>
-      <c r="O76" s="28" t="n">
-        <v>640</v>
+      <c r="O76" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P76" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R76" s="22">
+      <c r="Q76" s="22">
+        <f>K76+M76+O76</f>
+        <v/>
+      </c>
+      <c r="R76" s="23">
         <f>L76+N76+P76</f>
         <v/>
       </c>
-      <c r="S76" s="23">
-        <f>M76+O76+Q76</f>
-        <v/>
-      </c>
-      <c r="T76" s="29">
-        <f>S76-R76</f>
-        <v/>
-      </c>
-      <c r="U76" s="30" t="inlineStr"/>
+      <c r="S76" s="28">
+        <f>R76-Q76</f>
+        <v/>
+      </c>
+      <c r="T76" s="29" t="inlineStr"/>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="B77" s="20" t="inlineStr">
@@ -5898,42 +5612,38 @@
         <f>IF(F77&gt;0, G77/F77, IF(G77&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J77" s="25">
-        <f>IF(F77&gt;0, 1.0 - (H77/F77), IF(G77=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K77" s="26" t="inlineStr"/>
+      <c r="J77" s="25" t="inlineStr"/>
+      <c r="K77" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L77" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M77" s="28" t="n">
-        <v>0</v>
+      <c r="M77" s="26" t="n">
+        <v>1000</v>
       </c>
       <c r="N77" s="27" t="n">
         <v>1000</v>
       </c>
-      <c r="O77" s="28" t="n">
-        <v>1000</v>
+      <c r="O77" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P77" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R77" s="22">
+      <c r="Q77" s="22">
+        <f>K77+M77+O77</f>
+        <v/>
+      </c>
+      <c r="R77" s="23">
         <f>L77+N77+P77</f>
         <v/>
       </c>
-      <c r="S77" s="23">
-        <f>M77+O77+Q77</f>
-        <v/>
-      </c>
-      <c r="T77" s="29">
-        <f>S77-R77</f>
-        <v/>
-      </c>
-      <c r="U77" s="30" t="inlineStr"/>
+      <c r="S77" s="28">
+        <f>R77-Q77</f>
+        <v/>
+      </c>
+      <c r="T77" s="29" t="inlineStr"/>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="B78" s="20" t="inlineStr">
@@ -5970,46 +5680,42 @@
         <f>IF(F78&gt;0, G78/F78, IF(G78&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J78" s="25">
-        <f>IF(F78&gt;0, 1.0 - (H78/F78), IF(G78=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K78" s="26" t="inlineStr">
+      <c r="J78" s="25" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
+      </c>
+      <c r="K78" s="26" t="n">
+        <v>792</v>
       </c>
       <c r="L78" s="27" t="n">
         <v>792</v>
       </c>
-      <c r="M78" s="28" t="n">
-        <v>792</v>
+      <c r="M78" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="N78" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O78" s="28" t="n">
+      <c r="O78" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P78" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R78" s="22">
+      <c r="Q78" s="22">
+        <f>K78+M78+O78</f>
+        <v/>
+      </c>
+      <c r="R78" s="23">
         <f>L78+N78+P78</f>
         <v/>
       </c>
-      <c r="S78" s="23">
-        <f>M78+O78+Q78</f>
-        <v/>
-      </c>
-      <c r="T78" s="29">
-        <f>S78-R78</f>
-        <v/>
-      </c>
-      <c r="U78" s="30" t="inlineStr"/>
+      <c r="S78" s="28">
+        <f>R78-Q78</f>
+        <v/>
+      </c>
+      <c r="T78" s="29" t="inlineStr"/>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="B79" s="20" t="inlineStr">
@@ -6046,46 +5752,42 @@
         <f>IF(F79&gt;0, G79/F79, IF(G79&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J79" s="25">
-        <f>IF(F79&gt;0, 1.0 - (H79/F79), IF(G79=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K79" s="26" t="inlineStr">
+      <c r="J79" s="25" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
+      </c>
+      <c r="K79" s="26" t="n">
+        <v>600</v>
       </c>
       <c r="L79" s="27" t="n">
         <v>600</v>
       </c>
-      <c r="M79" s="28" t="n">
-        <v>600</v>
+      <c r="M79" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="N79" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O79" s="28" t="n">
+      <c r="O79" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P79" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R79" s="22">
+      <c r="Q79" s="22">
+        <f>K79+M79+O79</f>
+        <v/>
+      </c>
+      <c r="R79" s="23">
         <f>L79+N79+P79</f>
         <v/>
       </c>
-      <c r="S79" s="23">
-        <f>M79+O79+Q79</f>
-        <v/>
-      </c>
-      <c r="T79" s="29">
-        <f>S79-R79</f>
-        <v/>
-      </c>
-      <c r="U79" s="30" t="inlineStr"/>
+      <c r="S79" s="28">
+        <f>R79-Q79</f>
+        <v/>
+      </c>
+      <c r="T79" s="29" t="inlineStr"/>
     </row>
     <row r="80" ht="20" customHeight="1">
       <c r="B80" s="20" t="inlineStr">
@@ -6122,46 +5824,42 @@
         <f>IF(F80&gt;0, G80/F80, IF(G80&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J80" s="25">
-        <f>IF(F80&gt;0, 1.0 - (H80/F80), IF(G80=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K80" s="26" t="inlineStr">
+      <c r="J80" s="25" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
+      </c>
+      <c r="K80" s="26" t="n">
+        <v>640</v>
       </c>
       <c r="L80" s="27" t="n">
         <v>640</v>
       </c>
-      <c r="M80" s="28" t="n">
-        <v>640</v>
+      <c r="M80" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="N80" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O80" s="28" t="n">
+      <c r="O80" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P80" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R80" s="22">
+      <c r="Q80" s="22">
+        <f>K80+M80+O80</f>
+        <v/>
+      </c>
+      <c r="R80" s="23">
         <f>L80+N80+P80</f>
         <v/>
       </c>
-      <c r="S80" s="23">
-        <f>M80+O80+Q80</f>
-        <v/>
-      </c>
-      <c r="T80" s="29">
-        <f>S80-R80</f>
-        <v/>
-      </c>
-      <c r="U80" s="30" t="inlineStr"/>
+      <c r="S80" s="28">
+        <f>R80-Q80</f>
+        <v/>
+      </c>
+      <c r="T80" s="29" t="inlineStr"/>
     </row>
     <row r="81" ht="20" customHeight="1">
       <c r="B81" s="20" t="inlineStr">
@@ -6198,42 +5896,38 @@
         <f>IF(F81&gt;0, G81/F81, IF(G81&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J81" s="25">
-        <f>IF(F81&gt;0, 1.0 - (H81/F81), IF(G81=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K81" s="26" t="inlineStr"/>
+      <c r="J81" s="25" t="inlineStr"/>
+      <c r="K81" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L81" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M81" s="28" t="n">
-        <v>0</v>
+      <c r="M81" s="26" t="n">
+        <v>660</v>
       </c>
       <c r="N81" s="27" t="n">
         <v>660</v>
       </c>
-      <c r="O81" s="28" t="n">
-        <v>660</v>
+      <c r="O81" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P81" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R81" s="22">
+      <c r="Q81" s="22">
+        <f>K81+M81+O81</f>
+        <v/>
+      </c>
+      <c r="R81" s="23">
         <f>L81+N81+P81</f>
         <v/>
       </c>
-      <c r="S81" s="23">
-        <f>M81+O81+Q81</f>
-        <v/>
-      </c>
-      <c r="T81" s="29">
-        <f>S81-R81</f>
-        <v/>
-      </c>
-      <c r="U81" s="30" t="inlineStr"/>
+      <c r="S81" s="28">
+        <f>R81-Q81</f>
+        <v/>
+      </c>
+      <c r="T81" s="29" t="inlineStr"/>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="B82" s="20" t="inlineStr">
@@ -6270,42 +5964,38 @@
         <f>IF(F82&gt;0, G82/F82, IF(G82&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J82" s="25">
-        <f>IF(F82&gt;0, 1.0 - (H82/F82), IF(G82=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K82" s="26" t="inlineStr"/>
+      <c r="J82" s="25" t="inlineStr"/>
+      <c r="K82" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L82" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M82" s="28" t="n">
-        <v>0</v>
+      <c r="M82" s="26" t="n">
+        <v>320</v>
       </c>
       <c r="N82" s="27" t="n">
         <v>320</v>
       </c>
-      <c r="O82" s="28" t="n">
-        <v>320</v>
+      <c r="O82" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P82" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R82" s="22">
+      <c r="Q82" s="22">
+        <f>K82+M82+O82</f>
+        <v/>
+      </c>
+      <c r="R82" s="23">
         <f>L82+N82+P82</f>
         <v/>
       </c>
-      <c r="S82" s="23">
-        <f>M82+O82+Q82</f>
-        <v/>
-      </c>
-      <c r="T82" s="29">
-        <f>S82-R82</f>
-        <v/>
-      </c>
-      <c r="U82" s="30" t="inlineStr"/>
+      <c r="S82" s="28">
+        <f>R82-Q82</f>
+        <v/>
+      </c>
+      <c r="T82" s="29" t="inlineStr"/>
     </row>
     <row r="83" ht="20" customHeight="1">
       <c r="B83" s="20" t="inlineStr">
@@ -6342,46 +6032,42 @@
         <f>IF(F83&gt;0, G83/F83, IF(G83&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J83" s="25">
-        <f>IF(F83&gt;0, 1.0 - (H83/F83), IF(G83=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K83" s="26" t="inlineStr">
+      <c r="J83" s="25" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
+      </c>
+      <c r="K83" s="26" t="n">
+        <v>792</v>
       </c>
       <c r="L83" s="27" t="n">
         <v>792</v>
       </c>
-      <c r="M83" s="28" t="n">
-        <v>792</v>
+      <c r="M83" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="N83" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O83" s="28" t="n">
+      <c r="O83" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P83" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R83" s="22">
+      <c r="Q83" s="22">
+        <f>K83+M83+O83</f>
+        <v/>
+      </c>
+      <c r="R83" s="23">
         <f>L83+N83+P83</f>
         <v/>
       </c>
-      <c r="S83" s="23">
-        <f>M83+O83+Q83</f>
-        <v/>
-      </c>
-      <c r="T83" s="29">
-        <f>S83-R83</f>
-        <v/>
-      </c>
-      <c r="U83" s="30" t="inlineStr"/>
+      <c r="S83" s="28">
+        <f>R83-Q83</f>
+        <v/>
+      </c>
+      <c r="T83" s="29" t="inlineStr"/>
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="B84" s="20" t="inlineStr">
@@ -6418,42 +6104,38 @@
         <f>IF(F84&gt;0, G84/F84, IF(G84&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J84" s="25">
-        <f>IF(F84&gt;0, 1.0 - (H84/F84), IF(G84=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K84" s="26" t="inlineStr"/>
+      <c r="J84" s="25" t="inlineStr"/>
+      <c r="K84" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L84" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M84" s="28" t="n">
-        <v>0</v>
+      <c r="M84" s="26" t="n">
+        <v>300</v>
       </c>
       <c r="N84" s="27" t="n">
         <v>300</v>
       </c>
-      <c r="O84" s="28" t="n">
-        <v>300</v>
+      <c r="O84" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P84" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R84" s="22">
+      <c r="Q84" s="22">
+        <f>K84+M84+O84</f>
+        <v/>
+      </c>
+      <c r="R84" s="23">
         <f>L84+N84+P84</f>
         <v/>
       </c>
-      <c r="S84" s="23">
-        <f>M84+O84+Q84</f>
-        <v/>
-      </c>
-      <c r="T84" s="29">
-        <f>S84-R84</f>
-        <v/>
-      </c>
-      <c r="U84" s="30" t="inlineStr"/>
+      <c r="S84" s="28">
+        <f>R84-Q84</f>
+        <v/>
+      </c>
+      <c r="T84" s="29" t="inlineStr"/>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="B85" s="20" t="inlineStr">
@@ -6490,42 +6172,38 @@
         <f>IF(F85&gt;0, G85/F85, IF(G85&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J85" s="25">
-        <f>IF(F85&gt;0, 1.0 - (H85/F85), IF(G85=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K85" s="26" t="inlineStr"/>
+      <c r="J85" s="25" t="inlineStr"/>
+      <c r="K85" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L85" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M85" s="28" t="n">
-        <v>0</v>
+      <c r="M85" s="26" t="n">
+        <v>660</v>
       </c>
       <c r="N85" s="27" t="n">
         <v>660</v>
       </c>
-      <c r="O85" s="28" t="n">
-        <v>660</v>
+      <c r="O85" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P85" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R85" s="22">
+      <c r="Q85" s="22">
+        <f>K85+M85+O85</f>
+        <v/>
+      </c>
+      <c r="R85" s="23">
         <f>L85+N85+P85</f>
         <v/>
       </c>
-      <c r="S85" s="23">
-        <f>M85+O85+Q85</f>
-        <v/>
-      </c>
-      <c r="T85" s="29">
-        <f>S85-R85</f>
-        <v/>
-      </c>
-      <c r="U85" s="30" t="inlineStr"/>
+      <c r="S85" s="28">
+        <f>R85-Q85</f>
+        <v/>
+      </c>
+      <c r="T85" s="29" t="inlineStr"/>
     </row>
     <row r="86" ht="20" customHeight="1">
       <c r="B86" s="20" t="inlineStr">
@@ -6562,42 +6240,38 @@
         <f>IF(F86&gt;0, G86/F86, IF(G86&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J86" s="25">
-        <f>IF(F86&gt;0, 1.0 - (H86/F86), IF(G86=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K86" s="26" t="inlineStr"/>
+      <c r="J86" s="25" t="inlineStr"/>
+      <c r="K86" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L86" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M86" s="28" t="n">
-        <v>0</v>
+      <c r="M86" s="26" t="n">
+        <v>400</v>
       </c>
       <c r="N86" s="27" t="n">
         <v>400</v>
       </c>
-      <c r="O86" s="28" t="n">
-        <v>400</v>
+      <c r="O86" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P86" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R86" s="22">
+      <c r="Q86" s="22">
+        <f>K86+M86+O86</f>
+        <v/>
+      </c>
+      <c r="R86" s="23">
         <f>L86+N86+P86</f>
         <v/>
       </c>
-      <c r="S86" s="23">
-        <f>M86+O86+Q86</f>
-        <v/>
-      </c>
-      <c r="T86" s="29">
-        <f>S86-R86</f>
-        <v/>
-      </c>
-      <c r="U86" s="30" t="inlineStr"/>
+      <c r="S86" s="28">
+        <f>R86-Q86</f>
+        <v/>
+      </c>
+      <c r="T86" s="29" t="inlineStr"/>
     </row>
     <row r="87" ht="20" customHeight="1">
       <c r="B87" s="20" t="inlineStr">
@@ -6634,46 +6308,42 @@
         <f>IF(F87&gt;0, G87/F87, IF(G87&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J87" s="25">
-        <f>IF(F87&gt;0, 1.0 - (H87/F87), IF(G87=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K87" s="26" t="inlineStr">
+      <c r="J87" s="25" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
       </c>
+      <c r="K87" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L87" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M87" s="28" t="n">
+      <c r="M87" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N87" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O87" s="28" t="n">
+      <c r="O87" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P87" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q87" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R87" s="22">
+      <c r="Q87" s="22">
+        <f>K87+M87+O87</f>
+        <v/>
+      </c>
+      <c r="R87" s="23">
         <f>L87+N87+P87</f>
         <v/>
       </c>
-      <c r="S87" s="23">
-        <f>M87+O87+Q87</f>
-        <v/>
-      </c>
-      <c r="T87" s="29">
-        <f>S87-R87</f>
-        <v/>
-      </c>
-      <c r="U87" s="30" t="inlineStr"/>
+      <c r="S87" s="28">
+        <f>R87-Q87</f>
+        <v/>
+      </c>
+      <c r="T87" s="29" t="inlineStr"/>
     </row>
     <row r="88" ht="20" customHeight="1">
       <c r="B88" s="20" t="inlineStr">
@@ -6710,42 +6380,38 @@
         <f>IF(F88&gt;0, G88/F88, IF(G88&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J88" s="25">
-        <f>IF(F88&gt;0, 1.0 - (H88/F88), IF(G88=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K88" s="26" t="inlineStr"/>
+      <c r="J88" s="25" t="inlineStr"/>
+      <c r="K88" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L88" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M88" s="28" t="n">
-        <v>0</v>
+      <c r="M88" s="26" t="n">
+        <v>300</v>
       </c>
       <c r="N88" s="27" t="n">
         <v>300</v>
       </c>
-      <c r="O88" s="28" t="n">
-        <v>300</v>
+      <c r="O88" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P88" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R88" s="22">
+      <c r="Q88" s="22">
+        <f>K88+M88+O88</f>
+        <v/>
+      </c>
+      <c r="R88" s="23">
         <f>L88+N88+P88</f>
         <v/>
       </c>
-      <c r="S88" s="23">
-        <f>M88+O88+Q88</f>
-        <v/>
-      </c>
-      <c r="T88" s="29">
-        <f>S88-R88</f>
-        <v/>
-      </c>
-      <c r="U88" s="30" t="inlineStr"/>
+      <c r="S88" s="28">
+        <f>R88-Q88</f>
+        <v/>
+      </c>
+      <c r="T88" s="29" t="inlineStr"/>
     </row>
     <row r="89" ht="20" customHeight="1">
       <c r="B89" s="20" t="inlineStr">
@@ -6782,42 +6448,38 @@
         <f>IF(F89&gt;0, G89/F89, IF(G89&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J89" s="25">
-        <f>IF(F89&gt;0, 1.0 - (H89/F89), IF(G89=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K89" s="26" t="inlineStr"/>
+      <c r="J89" s="25" t="inlineStr"/>
+      <c r="K89" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L89" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M89" s="28" t="n">
-        <v>0</v>
+      <c r="M89" s="26" t="n">
+        <v>640</v>
       </c>
       <c r="N89" s="27" t="n">
         <v>640</v>
       </c>
-      <c r="O89" s="28" t="n">
-        <v>640</v>
+      <c r="O89" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P89" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R89" s="22">
+      <c r="Q89" s="22">
+        <f>K89+M89+O89</f>
+        <v/>
+      </c>
+      <c r="R89" s="23">
         <f>L89+N89+P89</f>
         <v/>
       </c>
-      <c r="S89" s="23">
-        <f>M89+O89+Q89</f>
-        <v/>
-      </c>
-      <c r="T89" s="29">
-        <f>S89-R89</f>
-        <v/>
-      </c>
-      <c r="U89" s="30" t="inlineStr"/>
+      <c r="S89" s="28">
+        <f>R89-Q89</f>
+        <v/>
+      </c>
+      <c r="T89" s="29" t="inlineStr"/>
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="B90" s="20" t="inlineStr">
@@ -6854,42 +6516,38 @@
         <f>IF(F90&gt;0, G90/F90, IF(G90&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J90" s="25">
-        <f>IF(F90&gt;0, 1.0 - (H90/F90), IF(G90=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K90" s="26" t="inlineStr"/>
+      <c r="J90" s="25" t="inlineStr"/>
+      <c r="K90" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L90" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M90" s="28" t="n">
-        <v>0</v>
+      <c r="M90" s="26" t="n">
+        <v>660</v>
       </c>
       <c r="N90" s="27" t="n">
         <v>660</v>
       </c>
-      <c r="O90" s="28" t="n">
-        <v>660</v>
+      <c r="O90" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P90" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R90" s="22">
+      <c r="Q90" s="22">
+        <f>K90+M90+O90</f>
+        <v/>
+      </c>
+      <c r="R90" s="23">
         <f>L90+N90+P90</f>
         <v/>
       </c>
-      <c r="S90" s="23">
-        <f>M90+O90+Q90</f>
-        <v/>
-      </c>
-      <c r="T90" s="29">
-        <f>S90-R90</f>
-        <v/>
-      </c>
-      <c r="U90" s="30" t="inlineStr"/>
+      <c r="S90" s="28">
+        <f>R90-Q90</f>
+        <v/>
+      </c>
+      <c r="T90" s="29" t="inlineStr"/>
     </row>
     <row r="91" ht="20" customHeight="1">
       <c r="B91" s="20" t="inlineStr">
@@ -6926,42 +6584,38 @@
         <f>IF(F91&gt;0, G91/F91, IF(G91&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J91" s="25">
-        <f>IF(F91&gt;0, 1.0 - (H91/F91), IF(G91=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K91" s="26" t="inlineStr"/>
+      <c r="J91" s="25" t="inlineStr"/>
+      <c r="K91" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L91" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M91" s="28" t="n">
-        <v>0</v>
+      <c r="M91" s="26" t="n">
+        <v>600</v>
       </c>
       <c r="N91" s="27" t="n">
         <v>600</v>
       </c>
-      <c r="O91" s="28" t="n">
-        <v>600</v>
+      <c r="O91" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P91" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R91" s="22">
+      <c r="Q91" s="22">
+        <f>K91+M91+O91</f>
+        <v/>
+      </c>
+      <c r="R91" s="23">
         <f>L91+N91+P91</f>
         <v/>
       </c>
-      <c r="S91" s="23">
-        <f>M91+O91+Q91</f>
-        <v/>
-      </c>
-      <c r="T91" s="29">
-        <f>S91-R91</f>
-        <v/>
-      </c>
-      <c r="U91" s="30" t="inlineStr"/>
+      <c r="S91" s="28">
+        <f>R91-Q91</f>
+        <v/>
+      </c>
+      <c r="T91" s="29" t="inlineStr"/>
     </row>
     <row r="92" ht="20" customHeight="1">
       <c r="B92" s="20" t="inlineStr">
@@ -6998,42 +6652,38 @@
         <f>IF(F92&gt;0, G92/F92, IF(G92&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J92" s="25">
-        <f>IF(F92&gt;0, 1.0 - (H92/F92), IF(G92=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K92" s="26" t="inlineStr"/>
+      <c r="J92" s="25" t="inlineStr"/>
+      <c r="K92" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L92" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M92" s="28" t="n">
-        <v>0</v>
+      <c r="M92" s="26" t="n">
+        <v>600</v>
       </c>
       <c r="N92" s="27" t="n">
         <v>600</v>
       </c>
-      <c r="O92" s="28" t="n">
-        <v>600</v>
+      <c r="O92" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P92" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R92" s="22">
+      <c r="Q92" s="22">
+        <f>K92+M92+O92</f>
+        <v/>
+      </c>
+      <c r="R92" s="23">
         <f>L92+N92+P92</f>
         <v/>
       </c>
-      <c r="S92" s="23">
-        <f>M92+O92+Q92</f>
-        <v/>
-      </c>
-      <c r="T92" s="29">
-        <f>S92-R92</f>
-        <v/>
-      </c>
-      <c r="U92" s="30" t="inlineStr"/>
+      <c r="S92" s="28">
+        <f>R92-Q92</f>
+        <v/>
+      </c>
+      <c r="T92" s="29" t="inlineStr"/>
     </row>
     <row r="93" ht="20" customHeight="1">
       <c r="B93" s="20" t="inlineStr">
@@ -7070,46 +6720,42 @@
         <f>IF(F93&gt;0, G93/F93, IF(G93&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J93" s="25">
-        <f>IF(F93&gt;0, 1.0 - (H93/F93), IF(G93=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K93" s="26" t="inlineStr">
+      <c r="J93" s="25" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
+      </c>
+      <c r="K93" s="26" t="n">
+        <v>792</v>
       </c>
       <c r="L93" s="27" t="n">
         <v>792</v>
       </c>
-      <c r="M93" s="28" t="n">
-        <v>792</v>
+      <c r="M93" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="N93" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O93" s="28" t="n">
+      <c r="O93" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P93" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R93" s="22">
+      <c r="Q93" s="22">
+        <f>K93+M93+O93</f>
+        <v/>
+      </c>
+      <c r="R93" s="23">
         <f>L93+N93+P93</f>
         <v/>
       </c>
-      <c r="S93" s="23">
-        <f>M93+O93+Q93</f>
-        <v/>
-      </c>
-      <c r="T93" s="29">
-        <f>S93-R93</f>
-        <v/>
-      </c>
-      <c r="U93" s="30" t="inlineStr"/>
+      <c r="S93" s="28">
+        <f>R93-Q93</f>
+        <v/>
+      </c>
+      <c r="T93" s="29" t="inlineStr"/>
     </row>
     <row r="94" ht="20" customHeight="1">
       <c r="B94" s="20" t="inlineStr">
@@ -7146,46 +6792,42 @@
         <f>IF(F94&gt;0, G94/F94, IF(G94&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J94" s="25">
-        <f>IF(F94&gt;0, 1.0 - (H94/F94), IF(G94=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K94" s="26" t="inlineStr">
+      <c r="J94" s="25" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
+      </c>
+      <c r="K94" s="26" t="n">
+        <v>640</v>
       </c>
       <c r="L94" s="27" t="n">
         <v>640</v>
       </c>
-      <c r="M94" s="28" t="n">
-        <v>640</v>
+      <c r="M94" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="N94" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O94" s="28" t="n">
+      <c r="O94" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P94" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R94" s="22">
+      <c r="Q94" s="22">
+        <f>K94+M94+O94</f>
+        <v/>
+      </c>
+      <c r="R94" s="23">
         <f>L94+N94+P94</f>
         <v/>
       </c>
-      <c r="S94" s="23">
-        <f>M94+O94+Q94</f>
-        <v/>
-      </c>
-      <c r="T94" s="29">
-        <f>S94-R94</f>
-        <v/>
-      </c>
-      <c r="U94" s="30" t="inlineStr"/>
+      <c r="S94" s="28">
+        <f>R94-Q94</f>
+        <v/>
+      </c>
+      <c r="T94" s="29" t="inlineStr"/>
     </row>
     <row r="95" ht="20" customHeight="1">
       <c r="B95" s="20" t="inlineStr">
@@ -7222,46 +6864,42 @@
         <f>IF(F95&gt;0, G95/F95, IF(G95&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J95" s="25">
-        <f>IF(F95&gt;0, 1.0 - (H95/F95), IF(G95=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K95" s="26" t="inlineStr">
+      <c r="J95" s="25" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
+      </c>
+      <c r="K95" s="26" t="n">
+        <v>1056</v>
       </c>
       <c r="L95" s="27" t="n">
         <v>1056</v>
       </c>
-      <c r="M95" s="28" t="n">
-        <v>1056</v>
+      <c r="M95" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="N95" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O95" s="28" t="n">
+      <c r="O95" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P95" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q95" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R95" s="22">
+      <c r="Q95" s="22">
+        <f>K95+M95+O95</f>
+        <v/>
+      </c>
+      <c r="R95" s="23">
         <f>L95+N95+P95</f>
         <v/>
       </c>
-      <c r="S95" s="23">
-        <f>M95+O95+Q95</f>
-        <v/>
-      </c>
-      <c r="T95" s="29">
-        <f>S95-R95</f>
-        <v/>
-      </c>
-      <c r="U95" s="30" t="inlineStr"/>
+      <c r="S95" s="28">
+        <f>R95-Q95</f>
+        <v/>
+      </c>
+      <c r="T95" s="29" t="inlineStr"/>
     </row>
     <row r="96" ht="20" customHeight="1">
       <c r="B96" s="20" t="inlineStr">
@@ -7298,42 +6936,38 @@
         <f>IF(F96&gt;0, G96/F96, IF(G96&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J96" s="25">
-        <f>IF(F96&gt;0, 1.0 - (H96/F96), IF(G96=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K96" s="26" t="inlineStr"/>
+      <c r="J96" s="25" t="inlineStr"/>
+      <c r="K96" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L96" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M96" s="28" t="n">
-        <v>0</v>
+      <c r="M96" s="26" t="n">
+        <v>600</v>
       </c>
       <c r="N96" s="27" t="n">
         <v>600</v>
       </c>
-      <c r="O96" s="28" t="n">
-        <v>600</v>
+      <c r="O96" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P96" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R96" s="22">
+      <c r="Q96" s="22">
+        <f>K96+M96+O96</f>
+        <v/>
+      </c>
+      <c r="R96" s="23">
         <f>L96+N96+P96</f>
         <v/>
       </c>
-      <c r="S96" s="23">
-        <f>M96+O96+Q96</f>
-        <v/>
-      </c>
-      <c r="T96" s="29">
-        <f>S96-R96</f>
-        <v/>
-      </c>
-      <c r="U96" s="30" t="inlineStr"/>
+      <c r="S96" s="28">
+        <f>R96-Q96</f>
+        <v/>
+      </c>
+      <c r="T96" s="29" t="inlineStr"/>
     </row>
     <row r="97" ht="20" customHeight="1">
       <c r="B97" s="20" t="inlineStr">
@@ -7370,42 +7004,38 @@
         <f>IF(F97&gt;0, G97/F97, IF(G97&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J97" s="25">
-        <f>IF(F97&gt;0, 1.0 - (H97/F97), IF(G97=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K97" s="26" t="inlineStr"/>
+      <c r="J97" s="25" t="inlineStr"/>
+      <c r="K97" s="26" t="n">
+        <v>200</v>
+      </c>
       <c r="L97" s="27" t="n">
         <v>200</v>
       </c>
-      <c r="M97" s="28" t="n">
+      <c r="M97" s="26" t="n">
         <v>200</v>
       </c>
       <c r="N97" s="27" t="n">
         <v>200</v>
       </c>
-      <c r="O97" s="28" t="n">
-        <v>200</v>
+      <c r="O97" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P97" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R97" s="22">
+      <c r="Q97" s="22">
+        <f>K97+M97+O97</f>
+        <v/>
+      </c>
+      <c r="R97" s="23">
         <f>L97+N97+P97</f>
         <v/>
       </c>
-      <c r="S97" s="23">
-        <f>M97+O97+Q97</f>
-        <v/>
-      </c>
-      <c r="T97" s="29">
-        <f>S97-R97</f>
-        <v/>
-      </c>
-      <c r="U97" s="30" t="inlineStr"/>
+      <c r="S97" s="28">
+        <f>R97-Q97</f>
+        <v/>
+      </c>
+      <c r="T97" s="29" t="inlineStr"/>
     </row>
     <row r="98" ht="20" customHeight="1">
       <c r="B98" s="20" t="inlineStr">
@@ -7442,46 +7072,42 @@
         <f>IF(F98&gt;0, G98/F98, IF(G98&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J98" s="25">
-        <f>IF(F98&gt;0, 1.0 - (H98/F98), IF(G98=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K98" s="26" t="inlineStr">
+      <c r="J98" s="25" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
+      </c>
+      <c r="K98" s="26" t="n">
+        <v>640</v>
       </c>
       <c r="L98" s="27" t="n">
         <v>640</v>
       </c>
-      <c r="M98" s="28" t="n">
+      <c r="M98" s="26" t="n">
         <v>640</v>
       </c>
       <c r="N98" s="27" t="n">
         <v>640</v>
       </c>
-      <c r="O98" s="28" t="n">
+      <c r="O98" s="26" t="n">
         <v>640</v>
       </c>
       <c r="P98" s="27" t="n">
         <v>640</v>
       </c>
-      <c r="Q98" s="28" t="n">
-        <v>640</v>
-      </c>
-      <c r="R98" s="22">
+      <c r="Q98" s="22">
+        <f>K98+M98+O98</f>
+        <v/>
+      </c>
+      <c r="R98" s="23">
         <f>L98+N98+P98</f>
         <v/>
       </c>
-      <c r="S98" s="23">
-        <f>M98+O98+Q98</f>
-        <v/>
-      </c>
-      <c r="T98" s="29">
-        <f>S98-R98</f>
-        <v/>
-      </c>
-      <c r="U98" s="30" t="inlineStr"/>
+      <c r="S98" s="28">
+        <f>R98-Q98</f>
+        <v/>
+      </c>
+      <c r="T98" s="29" t="inlineStr"/>
     </row>
     <row r="99" ht="20" customHeight="1">
       <c r="B99" s="20" t="inlineStr">
@@ -7518,42 +7144,38 @@
         <f>IF(F99&gt;0, G99/F99, IF(G99&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J99" s="25">
-        <f>IF(F99&gt;0, 1.0 - (H99/F99), IF(G99=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K99" s="26" t="inlineStr"/>
+      <c r="J99" s="25" t="inlineStr"/>
+      <c r="K99" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L99" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M99" s="28" t="n">
-        <v>0</v>
+      <c r="M99" s="26" t="n">
+        <v>50</v>
       </c>
       <c r="N99" s="27" t="n">
         <v>50</v>
       </c>
-      <c r="O99" s="28" t="n">
-        <v>50</v>
+      <c r="O99" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P99" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R99" s="22">
+      <c r="Q99" s="22">
+        <f>K99+M99+O99</f>
+        <v/>
+      </c>
+      <c r="R99" s="23">
         <f>L99+N99+P99</f>
         <v/>
       </c>
-      <c r="S99" s="23">
-        <f>M99+O99+Q99</f>
-        <v/>
-      </c>
-      <c r="T99" s="29">
-        <f>S99-R99</f>
-        <v/>
-      </c>
-      <c r="U99" s="30" t="inlineStr"/>
+      <c r="S99" s="28">
+        <f>R99-Q99</f>
+        <v/>
+      </c>
+      <c r="T99" s="29" t="inlineStr"/>
     </row>
     <row r="100" ht="20" customHeight="1">
       <c r="B100" s="20" t="inlineStr">
@@ -7590,42 +7212,38 @@
         <f>IF(F100&gt;0, G100/F100, IF(G100&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J100" s="25">
-        <f>IF(F100&gt;0, 1.0 - (H100/F100), IF(G100=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K100" s="26" t="inlineStr"/>
+      <c r="J100" s="25" t="inlineStr"/>
+      <c r="K100" s="26" t="n">
+        <v>100</v>
+      </c>
       <c r="L100" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="M100" s="28" t="n">
+      <c r="M100" s="26" t="n">
         <v>100</v>
       </c>
       <c r="N100" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="O100" s="28" t="n">
-        <v>100</v>
+      <c r="O100" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P100" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R100" s="22">
+      <c r="Q100" s="22">
+        <f>K100+M100+O100</f>
+        <v/>
+      </c>
+      <c r="R100" s="23">
         <f>L100+N100+P100</f>
         <v/>
       </c>
-      <c r="S100" s="23">
-        <f>M100+O100+Q100</f>
-        <v/>
-      </c>
-      <c r="T100" s="29">
-        <f>S100-R100</f>
-        <v/>
-      </c>
-      <c r="U100" s="30" t="inlineStr"/>
+      <c r="S100" s="28">
+        <f>R100-Q100</f>
+        <v/>
+      </c>
+      <c r="T100" s="29" t="inlineStr"/>
     </row>
     <row r="101" ht="20" customHeight="1">
       <c r="B101" s="20" t="inlineStr">
@@ -7662,42 +7280,38 @@
         <f>IF(F101&gt;0, G101/F101, IF(G101&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J101" s="25">
-        <f>IF(F101&gt;0, 1.0 - (H101/F101), IF(G101=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K101" s="26" t="inlineStr"/>
+      <c r="J101" s="25" t="inlineStr"/>
+      <c r="K101" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L101" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M101" s="28" t="n">
-        <v>0</v>
+      <c r="M101" s="26" t="n">
+        <v>12</v>
       </c>
       <c r="N101" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="O101" s="28" t="n">
+      <c r="O101" s="26" t="n">
         <v>12</v>
       </c>
       <c r="P101" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="Q101" s="28" t="n">
-        <v>12</v>
-      </c>
-      <c r="R101" s="22">
+      <c r="Q101" s="22">
+        <f>K101+M101+O101</f>
+        <v/>
+      </c>
+      <c r="R101" s="23">
         <f>L101+N101+P101</f>
         <v/>
       </c>
-      <c r="S101" s="23">
-        <f>M101+O101+Q101</f>
-        <v/>
-      </c>
-      <c r="T101" s="29">
-        <f>S101-R101</f>
-        <v/>
-      </c>
-      <c r="U101" s="30" t="inlineStr"/>
+      <c r="S101" s="28">
+        <f>R101-Q101</f>
+        <v/>
+      </c>
+      <c r="T101" s="29" t="inlineStr"/>
     </row>
     <row r="102" ht="20" customHeight="1">
       <c r="B102" s="20" t="inlineStr">
@@ -7734,42 +7348,38 @@
         <f>IF(F102&gt;0, G102/F102, IF(G102&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J102" s="25">
-        <f>IF(F102&gt;0, 1.0 - (H102/F102), IF(G102=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K102" s="26" t="inlineStr"/>
+      <c r="J102" s="25" t="inlineStr"/>
+      <c r="K102" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L102" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M102" s="28" t="n">
-        <v>0</v>
+      <c r="M102" s="26" t="n">
+        <v>20</v>
       </c>
       <c r="N102" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="O102" s="28" t="n">
-        <v>20</v>
+      <c r="O102" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P102" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R102" s="22">
+      <c r="Q102" s="22">
+        <f>K102+M102+O102</f>
+        <v/>
+      </c>
+      <c r="R102" s="23">
         <f>L102+N102+P102</f>
         <v/>
       </c>
-      <c r="S102" s="23">
-        <f>M102+O102+Q102</f>
-        <v/>
-      </c>
-      <c r="T102" s="29">
-        <f>S102-R102</f>
-        <v/>
-      </c>
-      <c r="U102" s="30" t="inlineStr"/>
+      <c r="S102" s="28">
+        <f>R102-Q102</f>
+        <v/>
+      </c>
+      <c r="T102" s="29" t="inlineStr"/>
     </row>
     <row r="103" ht="20" customHeight="1">
       <c r="B103" s="20" t="inlineStr">
@@ -7806,42 +7416,38 @@
         <f>IF(F103&gt;0, G103/F103, IF(G103&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J103" s="25">
-        <f>IF(F103&gt;0, 1.0 - (H103/F103), IF(G103=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K103" s="26" t="inlineStr"/>
+      <c r="J103" s="25" t="inlineStr"/>
+      <c r="K103" s="26" t="n">
+        <v>300</v>
+      </c>
       <c r="L103" s="27" t="n">
         <v>300</v>
       </c>
-      <c r="M103" s="28" t="n">
+      <c r="M103" s="26" t="n">
         <v>300</v>
       </c>
       <c r="N103" s="27" t="n">
         <v>300</v>
       </c>
-      <c r="O103" s="28" t="n">
-        <v>300</v>
+      <c r="O103" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P103" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R103" s="22">
+      <c r="Q103" s="22">
+        <f>K103+M103+O103</f>
+        <v/>
+      </c>
+      <c r="R103" s="23">
         <f>L103+N103+P103</f>
         <v/>
       </c>
-      <c r="S103" s="23">
-        <f>M103+O103+Q103</f>
-        <v/>
-      </c>
-      <c r="T103" s="29">
-        <f>S103-R103</f>
-        <v/>
-      </c>
-      <c r="U103" s="30" t="inlineStr"/>
+      <c r="S103" s="28">
+        <f>R103-Q103</f>
+        <v/>
+      </c>
+      <c r="T103" s="29" t="inlineStr"/>
     </row>
     <row r="104" ht="20" customHeight="1">
       <c r="B104" s="20" t="inlineStr">
@@ -7878,42 +7484,38 @@
         <f>IF(F104&gt;0, G104/F104, IF(G104&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J104" s="25">
-        <f>IF(F104&gt;0, 1.0 - (H104/F104), IF(G104=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K104" s="26" t="inlineStr"/>
+      <c r="J104" s="25" t="inlineStr"/>
+      <c r="K104" s="26" t="n">
+        <v>600</v>
+      </c>
       <c r="L104" s="27" t="n">
         <v>600</v>
       </c>
-      <c r="M104" s="28" t="n">
+      <c r="M104" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" s="26" t="n">
         <v>600</v>
-      </c>
-      <c r="N104" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O104" s="28" t="n">
-        <v>0</v>
       </c>
       <c r="P104" s="27" t="n">
         <v>600</v>
       </c>
-      <c r="Q104" s="28" t="n">
-        <v>600</v>
-      </c>
-      <c r="R104" s="22">
+      <c r="Q104" s="22">
+        <f>K104+M104+O104</f>
+        <v/>
+      </c>
+      <c r="R104" s="23">
         <f>L104+N104+P104</f>
         <v/>
       </c>
-      <c r="S104" s="23">
-        <f>M104+O104+Q104</f>
-        <v/>
-      </c>
-      <c r="T104" s="29">
-        <f>S104-R104</f>
-        <v/>
-      </c>
-      <c r="U104" s="30" t="inlineStr"/>
+      <c r="S104" s="28">
+        <f>R104-Q104</f>
+        <v/>
+      </c>
+      <c r="T104" s="29" t="inlineStr"/>
     </row>
     <row r="105" ht="20" customHeight="1">
       <c r="B105" s="20" t="inlineStr">
@@ -7950,46 +7552,42 @@
         <f>IF(F105&gt;0, G105/F105, IF(G105&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J105" s="25">
-        <f>IF(F105&gt;0, 1.0 - (H105/F105), IF(G105=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K105" s="26" t="inlineStr">
+      <c r="J105" s="25" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
       </c>
+      <c r="K105" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L105" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M105" s="28" t="n">
+      <c r="M105" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N105" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O105" s="28" t="n">
+      <c r="O105" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P105" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R105" s="22">
+      <c r="Q105" s="22">
+        <f>K105+M105+O105</f>
+        <v/>
+      </c>
+      <c r="R105" s="23">
         <f>L105+N105+P105</f>
         <v/>
       </c>
-      <c r="S105" s="23">
-        <f>M105+O105+Q105</f>
-        <v/>
-      </c>
-      <c r="T105" s="29">
-        <f>S105-R105</f>
-        <v/>
-      </c>
-      <c r="U105" s="30" t="inlineStr"/>
+      <c r="S105" s="28">
+        <f>R105-Q105</f>
+        <v/>
+      </c>
+      <c r="T105" s="29" t="inlineStr"/>
     </row>
     <row r="106" ht="20" customHeight="1">
       <c r="B106" s="20" t="inlineStr">
@@ -8026,46 +7624,42 @@
         <f>IF(F106&gt;0, G106/F106, IF(G106&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J106" s="25">
-        <f>IF(F106&gt;0, 1.0 - (H106/F106), IF(G106=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K106" s="26" t="inlineStr">
+      <c r="J106" s="25" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
       </c>
+      <c r="K106" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L106" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M106" s="28" t="n">
-        <v>0</v>
+      <c r="M106" s="26" t="n">
+        <v>300</v>
       </c>
       <c r="N106" s="27" t="n">
         <v>300</v>
       </c>
-      <c r="O106" s="28" t="n">
-        <v>300</v>
+      <c r="O106" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P106" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R106" s="22">
+      <c r="Q106" s="22">
+        <f>K106+M106+O106</f>
+        <v/>
+      </c>
+      <c r="R106" s="23">
         <f>L106+N106+P106</f>
         <v/>
       </c>
-      <c r="S106" s="23">
-        <f>M106+O106+Q106</f>
-        <v/>
-      </c>
-      <c r="T106" s="29">
-        <f>S106-R106</f>
-        <v/>
-      </c>
-      <c r="U106" s="30" t="inlineStr"/>
+      <c r="S106" s="28">
+        <f>R106-Q106</f>
+        <v/>
+      </c>
+      <c r="T106" s="29" t="inlineStr"/>
     </row>
     <row r="107" ht="20" customHeight="1">
       <c r="B107" s="20" t="inlineStr">
@@ -8102,42 +7696,38 @@
         <f>IF(F107&gt;0, G107/F107, IF(G107&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J107" s="25">
-        <f>IF(F107&gt;0, 1.0 - (H107/F107), IF(G107=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K107" s="26" t="inlineStr"/>
+      <c r="J107" s="25" t="inlineStr"/>
+      <c r="K107" s="26" t="n">
+        <v>300</v>
+      </c>
       <c r="L107" s="27" t="n">
         <v>300</v>
       </c>
-      <c r="M107" s="28" t="n">
+      <c r="M107" s="26" t="n">
         <v>300</v>
       </c>
       <c r="N107" s="27" t="n">
         <v>300</v>
       </c>
-      <c r="O107" s="28" t="n">
+      <c r="O107" s="26" t="n">
         <v>300</v>
       </c>
       <c r="P107" s="27" t="n">
         <v>300</v>
       </c>
-      <c r="Q107" s="28" t="n">
-        <v>300</v>
-      </c>
-      <c r="R107" s="22">
+      <c r="Q107" s="22">
+        <f>K107+M107+O107</f>
+        <v/>
+      </c>
+      <c r="R107" s="23">
         <f>L107+N107+P107</f>
         <v/>
       </c>
-      <c r="S107" s="23">
-        <f>M107+O107+Q107</f>
-        <v/>
-      </c>
-      <c r="T107" s="29">
-        <f>S107-R107</f>
-        <v/>
-      </c>
-      <c r="U107" s="30" t="inlineStr"/>
+      <c r="S107" s="28">
+        <f>R107-Q107</f>
+        <v/>
+      </c>
+      <c r="T107" s="29" t="inlineStr"/>
     </row>
     <row r="108" ht="20" customHeight="1">
       <c r="B108" s="20" t="inlineStr">
@@ -8174,42 +7764,38 @@
         <f>IF(F108&gt;0, G108/F108, IF(G108&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J108" s="25">
-        <f>IF(F108&gt;0, 1.0 - (H108/F108), IF(G108=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K108" s="26" t="inlineStr"/>
+      <c r="J108" s="25" t="inlineStr"/>
+      <c r="K108" s="26" t="n">
+        <v>100</v>
+      </c>
       <c r="L108" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="M108" s="28" t="n">
-        <v>100</v>
+      <c r="M108" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="N108" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O108" s="28" t="n">
+      <c r="O108" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P108" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R108" s="22">
+      <c r="Q108" s="22">
+        <f>K108+M108+O108</f>
+        <v/>
+      </c>
+      <c r="R108" s="23">
         <f>L108+N108+P108</f>
         <v/>
       </c>
-      <c r="S108" s="23">
-        <f>M108+O108+Q108</f>
-        <v/>
-      </c>
-      <c r="T108" s="29">
-        <f>S108-R108</f>
-        <v/>
-      </c>
-      <c r="U108" s="30" t="inlineStr"/>
+      <c r="S108" s="28">
+        <f>R108-Q108</f>
+        <v/>
+      </c>
+      <c r="T108" s="29" t="inlineStr"/>
     </row>
     <row r="109" ht="20" customHeight="1">
       <c r="B109" s="20" t="inlineStr">
@@ -8246,42 +7832,38 @@
         <f>IF(F109&gt;0, G109/F109, IF(G109&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J109" s="25">
-        <f>IF(F109&gt;0, 1.0 - (H109/F109), IF(G109=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K109" s="26" t="inlineStr"/>
+      <c r="J109" s="25" t="inlineStr"/>
+      <c r="K109" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L109" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M109" s="28" t="n">
+      <c r="M109" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N109" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O109" s="28" t="n">
-        <v>0</v>
+      <c r="O109" s="26" t="n">
+        <v>3000</v>
       </c>
       <c r="P109" s="27" t="n">
         <v>3000</v>
       </c>
-      <c r="Q109" s="28" t="n">
-        <v>3000</v>
-      </c>
-      <c r="R109" s="22">
+      <c r="Q109" s="22">
+        <f>K109+M109+O109</f>
+        <v/>
+      </c>
+      <c r="R109" s="23">
         <f>L109+N109+P109</f>
         <v/>
       </c>
-      <c r="S109" s="23">
-        <f>M109+O109+Q109</f>
-        <v/>
-      </c>
-      <c r="T109" s="29">
-        <f>S109-R109</f>
-        <v/>
-      </c>
-      <c r="U109" s="30" t="inlineStr"/>
+      <c r="S109" s="28">
+        <f>R109-Q109</f>
+        <v/>
+      </c>
+      <c r="T109" s="29" t="inlineStr"/>
     </row>
     <row r="110" ht="20" customHeight="1">
       <c r="B110" s="20" t="inlineStr">
@@ -8318,46 +7900,42 @@
         <f>IF(F110&gt;0, G110/F110, IF(G110&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J110" s="25">
-        <f>IF(F110&gt;0, 1.0 - (H110/F110), IF(G110=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K110" s="26" t="inlineStr">
+      <c r="J110" s="25" t="inlineStr">
         <is>
           <t>Pedido extra no previsto</t>
         </is>
+      </c>
+      <c r="K110" s="26" t="n">
+        <v>200</v>
       </c>
       <c r="L110" s="27" t="n">
         <v>200</v>
       </c>
-      <c r="M110" s="28" t="n">
-        <v>200</v>
+      <c r="M110" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="N110" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O110" s="28" t="n">
+      <c r="O110" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P110" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R110" s="22">
+      <c r="Q110" s="22">
+        <f>K110+M110+O110</f>
+        <v/>
+      </c>
+      <c r="R110" s="23">
         <f>L110+N110+P110</f>
         <v/>
       </c>
-      <c r="S110" s="23">
-        <f>M110+O110+Q110</f>
-        <v/>
-      </c>
-      <c r="T110" s="29">
-        <f>S110-R110</f>
-        <v/>
-      </c>
-      <c r="U110" s="30" t="inlineStr"/>
+      <c r="S110" s="28">
+        <f>R110-Q110</f>
+        <v/>
+      </c>
+      <c r="T110" s="29" t="inlineStr"/>
     </row>
     <row r="111" ht="20" customHeight="1">
       <c r="B111" s="20" t="inlineStr">
@@ -8394,42 +7972,38 @@
         <f>IF(F111&gt;0, G111/F111, IF(G111&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J111" s="25">
-        <f>IF(F111&gt;0, 1.0 - (H111/F111), IF(G111=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K111" s="26" t="inlineStr"/>
+      <c r="J111" s="25" t="inlineStr"/>
+      <c r="K111" s="26" t="n">
+        <v>2000</v>
+      </c>
       <c r="L111" s="27" t="n">
         <v>2000</v>
       </c>
-      <c r="M111" s="28" t="n">
-        <v>2000</v>
+      <c r="M111" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="N111" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O111" s="28" t="n">
-        <v>0</v>
+      <c r="O111" s="26" t="n">
+        <v>1000</v>
       </c>
       <c r="P111" s="27" t="n">
         <v>1000</v>
       </c>
-      <c r="Q111" s="28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="R111" s="22">
+      <c r="Q111" s="22">
+        <f>K111+M111+O111</f>
+        <v/>
+      </c>
+      <c r="R111" s="23">
         <f>L111+N111+P111</f>
         <v/>
       </c>
-      <c r="S111" s="23">
-        <f>M111+O111+Q111</f>
-        <v/>
-      </c>
-      <c r="T111" s="29">
-        <f>S111-R111</f>
-        <v/>
-      </c>
-      <c r="U111" s="30" t="inlineStr"/>
+      <c r="S111" s="28">
+        <f>R111-Q111</f>
+        <v/>
+      </c>
+      <c r="T111" s="29" t="inlineStr"/>
     </row>
     <row r="112" ht="20" customHeight="1">
       <c r="B112" s="20" t="inlineStr">
@@ -8466,42 +8040,38 @@
         <f>IF(F112&gt;0, G112/F112, IF(G112&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J112" s="25">
-        <f>IF(F112&gt;0, 1.0 - (H112/F112), IF(G112=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K112" s="26" t="inlineStr"/>
+      <c r="J112" s="25" t="inlineStr"/>
+      <c r="K112" s="26" t="n">
+        <v>600</v>
+      </c>
       <c r="L112" s="27" t="n">
         <v>600</v>
       </c>
-      <c r="M112" s="28" t="n">
-        <v>600</v>
+      <c r="M112" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="N112" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O112" s="28" t="n">
+      <c r="O112" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P112" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R112" s="22">
+      <c r="Q112" s="22">
+        <f>K112+M112+O112</f>
+        <v/>
+      </c>
+      <c r="R112" s="23">
         <f>L112+N112+P112</f>
         <v/>
       </c>
-      <c r="S112" s="23">
-        <f>M112+O112+Q112</f>
-        <v/>
-      </c>
-      <c r="T112" s="29">
-        <f>S112-R112</f>
-        <v/>
-      </c>
-      <c r="U112" s="30" t="inlineStr"/>
+      <c r="S112" s="28">
+        <f>R112-Q112</f>
+        <v/>
+      </c>
+      <c r="T112" s="29" t="inlineStr"/>
     </row>
     <row r="113" ht="20" customHeight="1">
       <c r="B113" s="20" t="inlineStr">
@@ -8538,42 +8108,38 @@
         <f>IF(F113&gt;0, G113/F113, IF(G113&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J113" s="25">
-        <f>IF(F113&gt;0, 1.0 - (H113/F113), IF(G113=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K113" s="26" t="inlineStr"/>
+      <c r="J113" s="25" t="inlineStr"/>
+      <c r="K113" s="26" t="n">
+        <v>5000</v>
+      </c>
       <c r="L113" s="27" t="n">
         <v>5000</v>
       </c>
-      <c r="M113" s="28" t="n">
+      <c r="M113" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" s="26" t="n">
         <v>5000</v>
-      </c>
-      <c r="N113" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O113" s="28" t="n">
-        <v>0</v>
       </c>
       <c r="P113" s="27" t="n">
         <v>5000</v>
       </c>
-      <c r="Q113" s="28" t="n">
-        <v>5000</v>
-      </c>
-      <c r="R113" s="22">
+      <c r="Q113" s="22">
+        <f>K113+M113+O113</f>
+        <v/>
+      </c>
+      <c r="R113" s="23">
         <f>L113+N113+P113</f>
         <v/>
       </c>
-      <c r="S113" s="23">
-        <f>M113+O113+Q113</f>
-        <v/>
-      </c>
-      <c r="T113" s="29">
-        <f>S113-R113</f>
-        <v/>
-      </c>
-      <c r="U113" s="30" t="inlineStr"/>
+      <c r="S113" s="28">
+        <f>R113-Q113</f>
+        <v/>
+      </c>
+      <c r="T113" s="29" t="inlineStr"/>
     </row>
     <row r="114" ht="20" customHeight="1">
       <c r="B114" s="20" t="inlineStr">
@@ -8610,42 +8176,38 @@
         <f>IF(F114&gt;0, G114/F114, IF(G114&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J114" s="25">
-        <f>IF(F114&gt;0, 1.0 - (H114/F114), IF(G114=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K114" s="26" t="inlineStr"/>
+      <c r="J114" s="25" t="inlineStr"/>
+      <c r="K114" s="26" t="n">
+        <v>5000</v>
+      </c>
       <c r="L114" s="27" t="n">
         <v>5000</v>
       </c>
-      <c r="M114" s="28" t="n">
+      <c r="M114" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" s="26" t="n">
         <v>5000</v>
-      </c>
-      <c r="N114" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O114" s="28" t="n">
-        <v>0</v>
       </c>
       <c r="P114" s="27" t="n">
         <v>5000</v>
       </c>
-      <c r="Q114" s="28" t="n">
-        <v>5000</v>
-      </c>
-      <c r="R114" s="22">
+      <c r="Q114" s="22">
+        <f>K114+M114+O114</f>
+        <v/>
+      </c>
+      <c r="R114" s="23">
         <f>L114+N114+P114</f>
         <v/>
       </c>
-      <c r="S114" s="23">
-        <f>M114+O114+Q114</f>
-        <v/>
-      </c>
-      <c r="T114" s="29">
-        <f>S114-R114</f>
-        <v/>
-      </c>
-      <c r="U114" s="30" t="inlineStr"/>
+      <c r="S114" s="28">
+        <f>R114-Q114</f>
+        <v/>
+      </c>
+      <c r="T114" s="29" t="inlineStr"/>
     </row>
     <row r="115" ht="20" customHeight="1">
       <c r="B115" s="20" t="inlineStr">
@@ -8682,42 +8244,38 @@
         <f>IF(F115&gt;0, G115/F115, IF(G115&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J115" s="25">
-        <f>IF(F115&gt;0, 1.0 - (H115/F115), IF(G115=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K115" s="26" t="inlineStr"/>
+      <c r="J115" s="25" t="inlineStr"/>
+      <c r="K115" s="26" t="n">
+        <v>3000</v>
+      </c>
       <c r="L115" s="27" t="n">
         <v>3000</v>
       </c>
-      <c r="M115" s="28" t="n">
-        <v>3000</v>
+      <c r="M115" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="N115" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O115" s="28" t="n">
+      <c r="O115" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P115" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R115" s="22">
+      <c r="Q115" s="22">
+        <f>K115+M115+O115</f>
+        <v/>
+      </c>
+      <c r="R115" s="23">
         <f>L115+N115+P115</f>
         <v/>
       </c>
-      <c r="S115" s="23">
-        <f>M115+O115+Q115</f>
-        <v/>
-      </c>
-      <c r="T115" s="29">
-        <f>S115-R115</f>
-        <v/>
-      </c>
-      <c r="U115" s="30" t="inlineStr"/>
+      <c r="S115" s="28">
+        <f>R115-Q115</f>
+        <v/>
+      </c>
+      <c r="T115" s="29" t="inlineStr"/>
     </row>
     <row r="116" ht="20" customHeight="1">
       <c r="B116" s="20" t="inlineStr">
@@ -8754,42 +8312,38 @@
         <f>IF(F116&gt;0, G116/F116, IF(G116&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J116" s="25">
-        <f>IF(F116&gt;0, 1.0 - (H116/F116), IF(G116=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K116" s="26" t="inlineStr"/>
+      <c r="J116" s="25" t="inlineStr"/>
+      <c r="K116" s="26" t="n">
+        <v>5000</v>
+      </c>
       <c r="L116" s="27" t="n">
         <v>5000</v>
       </c>
-      <c r="M116" s="28" t="n">
+      <c r="M116" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N116" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" s="26" t="n">
         <v>5000</v>
-      </c>
-      <c r="N116" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O116" s="28" t="n">
-        <v>0</v>
       </c>
       <c r="P116" s="27" t="n">
         <v>5000</v>
       </c>
-      <c r="Q116" s="28" t="n">
-        <v>5000</v>
-      </c>
-      <c r="R116" s="22">
+      <c r="Q116" s="22">
+        <f>K116+M116+O116</f>
+        <v/>
+      </c>
+      <c r="R116" s="23">
         <f>L116+N116+P116</f>
         <v/>
       </c>
-      <c r="S116" s="23">
-        <f>M116+O116+Q116</f>
-        <v/>
-      </c>
-      <c r="T116" s="29">
-        <f>S116-R116</f>
-        <v/>
-      </c>
-      <c r="U116" s="30" t="inlineStr"/>
+      <c r="S116" s="28">
+        <f>R116-Q116</f>
+        <v/>
+      </c>
+      <c r="T116" s="29" t="inlineStr"/>
     </row>
     <row r="117" ht="20" customHeight="1">
       <c r="B117" s="20" t="inlineStr">
@@ -8826,42 +8380,38 @@
         <f>IF(F117&gt;0, G117/F117, IF(G117&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J117" s="25">
-        <f>IF(F117&gt;0, 1.0 - (H117/F117), IF(G117=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K117" s="26" t="inlineStr"/>
+      <c r="J117" s="25" t="inlineStr"/>
+      <c r="K117" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L117" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M117" s="28" t="n">
+      <c r="M117" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N117" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O117" s="28" t="n">
-        <v>0</v>
+      <c r="O117" s="26" t="n">
+        <v>1000</v>
       </c>
       <c r="P117" s="27" t="n">
         <v>1000</v>
       </c>
-      <c r="Q117" s="28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="R117" s="22">
+      <c r="Q117" s="22">
+        <f>K117+M117+O117</f>
+        <v/>
+      </c>
+      <c r="R117" s="23">
         <f>L117+N117+P117</f>
         <v/>
       </c>
-      <c r="S117" s="23">
-        <f>M117+O117+Q117</f>
-        <v/>
-      </c>
-      <c r="T117" s="29">
-        <f>S117-R117</f>
-        <v/>
-      </c>
-      <c r="U117" s="30" t="inlineStr"/>
+      <c r="S117" s="28">
+        <f>R117-Q117</f>
+        <v/>
+      </c>
+      <c r="T117" s="29" t="inlineStr"/>
     </row>
     <row r="118" ht="20" customHeight="1">
       <c r="B118" s="20" t="inlineStr">
@@ -8898,42 +8448,38 @@
         <f>IF(F118&gt;0, G118/F118, IF(G118&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J118" s="25">
-        <f>IF(F118&gt;0, 1.0 - (H118/F118), IF(G118=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K118" s="26" t="inlineStr"/>
+      <c r="J118" s="25" t="inlineStr"/>
+      <c r="K118" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L118" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M118" s="28" t="n">
-        <v>0</v>
+      <c r="M118" s="26" t="n">
+        <v>1000</v>
       </c>
       <c r="N118" s="27" t="n">
         <v>1000</v>
       </c>
-      <c r="O118" s="28" t="n">
-        <v>1000</v>
+      <c r="O118" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P118" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R118" s="22">
+      <c r="Q118" s="22">
+        <f>K118+M118+O118</f>
+        <v/>
+      </c>
+      <c r="R118" s="23">
         <f>L118+N118+P118</f>
         <v/>
       </c>
-      <c r="S118" s="23">
-        <f>M118+O118+Q118</f>
-        <v/>
-      </c>
-      <c r="T118" s="29">
-        <f>S118-R118</f>
-        <v/>
-      </c>
-      <c r="U118" s="30" t="inlineStr"/>
+      <c r="S118" s="28">
+        <f>R118-Q118</f>
+        <v/>
+      </c>
+      <c r="T118" s="29" t="inlineStr"/>
     </row>
     <row r="119" ht="20" customHeight="1">
       <c r="B119" s="20" t="inlineStr">
@@ -8970,42 +8516,38 @@
         <f>IF(F119&gt;0, G119/F119, IF(G119&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J119" s="25">
-        <f>IF(F119&gt;0, 1.0 - (H119/F119), IF(G119=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K119" s="26" t="inlineStr"/>
+      <c r="J119" s="25" t="inlineStr"/>
+      <c r="K119" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L119" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M119" s="28" t="n">
+      <c r="M119" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N119" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O119" s="28" t="n">
-        <v>0</v>
+      <c r="O119" s="26" t="n">
+        <v>2000</v>
       </c>
       <c r="P119" s="27" t="n">
         <v>2000</v>
       </c>
-      <c r="Q119" s="28" t="n">
-        <v>2000</v>
-      </c>
-      <c r="R119" s="22">
+      <c r="Q119" s="22">
+        <f>K119+M119+O119</f>
+        <v/>
+      </c>
+      <c r="R119" s="23">
         <f>L119+N119+P119</f>
         <v/>
       </c>
-      <c r="S119" s="23">
-        <f>M119+O119+Q119</f>
-        <v/>
-      </c>
-      <c r="T119" s="29">
-        <f>S119-R119</f>
-        <v/>
-      </c>
-      <c r="U119" s="30" t="inlineStr"/>
+      <c r="S119" s="28">
+        <f>R119-Q119</f>
+        <v/>
+      </c>
+      <c r="T119" s="29" t="inlineStr"/>
     </row>
     <row r="120" ht="20" customHeight="1">
       <c r="B120" s="20" t="inlineStr">
@@ -9042,42 +8584,38 @@
         <f>IF(F120&gt;0, G120/F120, IF(G120&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J120" s="25">
-        <f>IF(F120&gt;0, 1.0 - (H120/F120), IF(G120=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K120" s="26" t="inlineStr"/>
+      <c r="J120" s="25" t="inlineStr"/>
+      <c r="K120" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L120" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M120" s="28" t="n">
+      <c r="M120" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N120" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O120" s="28" t="n">
-        <v>0</v>
+      <c r="O120" s="26" t="n">
+        <v>1000</v>
       </c>
       <c r="P120" s="27" t="n">
         <v>1000</v>
       </c>
-      <c r="Q120" s="28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="R120" s="22">
+      <c r="Q120" s="22">
+        <f>K120+M120+O120</f>
+        <v/>
+      </c>
+      <c r="R120" s="23">
         <f>L120+N120+P120</f>
         <v/>
       </c>
-      <c r="S120" s="23">
-        <f>M120+O120+Q120</f>
-        <v/>
-      </c>
-      <c r="T120" s="29">
-        <f>S120-R120</f>
-        <v/>
-      </c>
-      <c r="U120" s="30" t="inlineStr"/>
+      <c r="S120" s="28">
+        <f>R120-Q120</f>
+        <v/>
+      </c>
+      <c r="T120" s="29" t="inlineStr"/>
     </row>
     <row r="121" ht="20" customHeight="1">
       <c r="B121" s="20" t="inlineStr">
@@ -9114,42 +8652,38 @@
         <f>IF(F121&gt;0, G121/F121, IF(G121&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J121" s="25">
-        <f>IF(F121&gt;0, 1.0 - (H121/F121), IF(G121=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K121" s="26" t="inlineStr"/>
+      <c r="J121" s="25" t="inlineStr"/>
+      <c r="K121" s="26" t="n">
+        <v>1600</v>
+      </c>
       <c r="L121" s="27" t="n">
         <v>1600</v>
       </c>
-      <c r="M121" s="28" t="n">
-        <v>1600</v>
+      <c r="M121" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="N121" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O121" s="28" t="n">
+      <c r="O121" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P121" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q121" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R121" s="22">
+      <c r="Q121" s="22">
+        <f>K121+M121+O121</f>
+        <v/>
+      </c>
+      <c r="R121" s="23">
         <f>L121+N121+P121</f>
         <v/>
       </c>
-      <c r="S121" s="23">
-        <f>M121+O121+Q121</f>
-        <v/>
-      </c>
-      <c r="T121" s="29">
-        <f>S121-R121</f>
-        <v/>
-      </c>
-      <c r="U121" s="30" t="inlineStr"/>
+      <c r="S121" s="28">
+        <f>R121-Q121</f>
+        <v/>
+      </c>
+      <c r="T121" s="29" t="inlineStr"/>
     </row>
     <row r="122" ht="20" customHeight="1">
       <c r="B122" s="20" t="inlineStr">
@@ -9186,42 +8720,38 @@
         <f>IF(F122&gt;0, G122/F122, IF(G122&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J122" s="25">
-        <f>IF(F122&gt;0, 1.0 - (H122/F122), IF(G122=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K122" s="26" t="inlineStr"/>
+      <c r="J122" s="25" t="inlineStr"/>
+      <c r="K122" s="26" t="n">
+        <v>600</v>
+      </c>
       <c r="L122" s="27" t="n">
         <v>600</v>
       </c>
-      <c r="M122" s="28" t="n">
-        <v>600</v>
+      <c r="M122" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="N122" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O122" s="28" t="n">
+      <c r="O122" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P122" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R122" s="22">
+      <c r="Q122" s="22">
+        <f>K122+M122+O122</f>
+        <v/>
+      </c>
+      <c r="R122" s="23">
         <f>L122+N122+P122</f>
         <v/>
       </c>
-      <c r="S122" s="23">
-        <f>M122+O122+Q122</f>
-        <v/>
-      </c>
-      <c r="T122" s="29">
-        <f>S122-R122</f>
-        <v/>
-      </c>
-      <c r="U122" s="30" t="inlineStr"/>
+      <c r="S122" s="28">
+        <f>R122-Q122</f>
+        <v/>
+      </c>
+      <c r="T122" s="29" t="inlineStr"/>
     </row>
     <row r="123" ht="20" customHeight="1">
       <c r="B123" s="20" t="inlineStr">
@@ -9258,42 +8788,38 @@
         <f>IF(F123&gt;0, G123/F123, IF(G123&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J123" s="25">
-        <f>IF(F123&gt;0, 1.0 - (H123/F123), IF(G123=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K123" s="26" t="inlineStr"/>
+      <c r="J123" s="25" t="inlineStr"/>
+      <c r="K123" s="26" t="n">
+        <v>5000</v>
+      </c>
       <c r="L123" s="27" t="n">
         <v>5000</v>
       </c>
-      <c r="M123" s="28" t="n">
-        <v>5000</v>
+      <c r="M123" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="N123" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O123" s="28" t="n">
+      <c r="O123" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P123" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q123" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R123" s="22">
+      <c r="Q123" s="22">
+        <f>K123+M123+O123</f>
+        <v/>
+      </c>
+      <c r="R123" s="23">
         <f>L123+N123+P123</f>
         <v/>
       </c>
-      <c r="S123" s="23">
-        <f>M123+O123+Q123</f>
-        <v/>
-      </c>
-      <c r="T123" s="29">
-        <f>S123-R123</f>
-        <v/>
-      </c>
-      <c r="U123" s="30" t="inlineStr"/>
+      <c r="S123" s="28">
+        <f>R123-Q123</f>
+        <v/>
+      </c>
+      <c r="T123" s="29" t="inlineStr"/>
     </row>
     <row r="124" ht="20" customHeight="1">
       <c r="B124" s="20" t="inlineStr">
@@ -9330,42 +8856,38 @@
         <f>IF(F124&gt;0, G124/F124, IF(G124&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J124" s="25">
-        <f>IF(F124&gt;0, 1.0 - (H124/F124), IF(G124=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K124" s="26" t="inlineStr"/>
+      <c r="J124" s="25" t="inlineStr"/>
+      <c r="K124" s="26" t="n">
+        <v>2000</v>
+      </c>
       <c r="L124" s="27" t="n">
         <v>2000</v>
       </c>
-      <c r="M124" s="28" t="n">
+      <c r="M124" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" s="26" t="n">
         <v>2000</v>
-      </c>
-      <c r="N124" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O124" s="28" t="n">
-        <v>0</v>
       </c>
       <c r="P124" s="27" t="n">
         <v>2000</v>
       </c>
-      <c r="Q124" s="28" t="n">
-        <v>2000</v>
-      </c>
-      <c r="R124" s="22">
+      <c r="Q124" s="22">
+        <f>K124+M124+O124</f>
+        <v/>
+      </c>
+      <c r="R124" s="23">
         <f>L124+N124+P124</f>
         <v/>
       </c>
-      <c r="S124" s="23">
-        <f>M124+O124+Q124</f>
-        <v/>
-      </c>
-      <c r="T124" s="29">
-        <f>S124-R124</f>
-        <v/>
-      </c>
-      <c r="U124" s="30" t="inlineStr"/>
+      <c r="S124" s="28">
+        <f>R124-Q124</f>
+        <v/>
+      </c>
+      <c r="T124" s="29" t="inlineStr"/>
     </row>
     <row r="125" ht="20" customHeight="1">
       <c r="B125" s="20" t="inlineStr">
@@ -9402,42 +8924,38 @@
         <f>IF(F125&gt;0, G125/F125, IF(G125&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J125" s="25">
-        <f>IF(F125&gt;0, 1.0 - (H125/F125), IF(G125=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K125" s="26" t="inlineStr"/>
+      <c r="J125" s="25" t="inlineStr"/>
+      <c r="K125" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L125" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M125" s="28" t="n">
+      <c r="M125" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N125" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O125" s="28" t="n">
-        <v>0</v>
+      <c r="O125" s="26" t="n">
+        <v>1000</v>
       </c>
       <c r="P125" s="27" t="n">
         <v>1000</v>
       </c>
-      <c r="Q125" s="28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="R125" s="22">
+      <c r="Q125" s="22">
+        <f>K125+M125+O125</f>
+        <v/>
+      </c>
+      <c r="R125" s="23">
         <f>L125+N125+P125</f>
         <v/>
       </c>
-      <c r="S125" s="23">
-        <f>M125+O125+Q125</f>
-        <v/>
-      </c>
-      <c r="T125" s="29">
-        <f>S125-R125</f>
-        <v/>
-      </c>
-      <c r="U125" s="30" t="inlineStr"/>
+      <c r="S125" s="28">
+        <f>R125-Q125</f>
+        <v/>
+      </c>
+      <c r="T125" s="29" t="inlineStr"/>
     </row>
     <row r="126" ht="20" customHeight="1">
       <c r="B126" s="20" t="inlineStr">
@@ -9474,42 +8992,38 @@
         <f>IF(F126&gt;0, G126/F126, IF(G126&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J126" s="25">
-        <f>IF(F126&gt;0, 1.0 - (H126/F126), IF(G126=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K126" s="26" t="inlineStr"/>
+      <c r="J126" s="25" t="inlineStr"/>
+      <c r="K126" s="26" t="n">
+        <v>1100</v>
+      </c>
       <c r="L126" s="27" t="n">
         <v>1100</v>
       </c>
-      <c r="M126" s="28" t="n">
-        <v>1100</v>
+      <c r="M126" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="N126" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O126" s="28" t="n">
+      <c r="O126" s="26" t="n">
         <v>0</v>
       </c>
       <c r="P126" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q126" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R126" s="22">
+      <c r="Q126" s="22">
+        <f>K126+M126+O126</f>
+        <v/>
+      </c>
+      <c r="R126" s="23">
         <f>L126+N126+P126</f>
         <v/>
       </c>
-      <c r="S126" s="23">
-        <f>M126+O126+Q126</f>
-        <v/>
-      </c>
-      <c r="T126" s="29">
-        <f>S126-R126</f>
-        <v/>
-      </c>
-      <c r="U126" s="30" t="inlineStr"/>
+      <c r="S126" s="28">
+        <f>R126-Q126</f>
+        <v/>
+      </c>
+      <c r="T126" s="29" t="inlineStr"/>
     </row>
     <row r="127" ht="20" customHeight="1">
       <c r="B127" s="20" t="inlineStr">
@@ -9546,138 +9060,128 @@
         <f>IF(F127&gt;0, G127/F127, IF(G127&gt;0, 1.0, 0.0))</f>
         <v/>
       </c>
-      <c r="J127" s="25">
-        <f>IF(F127&gt;0, 1.0 - (H127/F127), IF(G127=0, 1.0, 0.0))</f>
-        <v/>
-      </c>
-      <c r="K127" s="26" t="inlineStr"/>
+      <c r="J127" s="25" t="inlineStr"/>
+      <c r="K127" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="L127" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="M127" s="28" t="n">
-        <v>0</v>
+      <c r="M127" s="26" t="n">
+        <v>640</v>
       </c>
       <c r="N127" s="27" t="n">
         <v>640</v>
       </c>
-      <c r="O127" s="28" t="n">
-        <v>640</v>
+      <c r="O127" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="P127" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q127" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R127" s="22">
+      <c r="Q127" s="22">
+        <f>K127+M127+O127</f>
+        <v/>
+      </c>
+      <c r="R127" s="23">
         <f>L127+N127+P127</f>
         <v/>
       </c>
-      <c r="S127" s="23">
-        <f>M127+O127+Q127</f>
-        <v/>
-      </c>
-      <c r="T127" s="29">
-        <f>S127-R127</f>
-        <v/>
-      </c>
-      <c r="U127" s="30" t="inlineStr"/>
+      <c r="S127" s="28">
+        <f>R127-Q127</f>
+        <v/>
+      </c>
+      <c r="T127" s="29" t="inlineStr"/>
     </row>
     <row r="128" ht="25" customHeight="1">
-      <c r="B128" s="31" t="inlineStr">
+      <c r="B128" s="30" t="inlineStr">
         <is>
           <t>TOTAL CONSOLIDADO - GARCÍA (UNIDADES)</t>
         </is>
       </c>
-      <c r="C128" s="32" t="n"/>
-      <c r="D128" s="32" t="n"/>
-      <c r="E128" s="32" t="n"/>
-      <c r="F128" s="33">
+      <c r="C128" s="31" t="n"/>
+      <c r="D128" s="31" t="n"/>
+      <c r="E128" s="31" t="n"/>
+      <c r="F128" s="32">
         <f>SUM(F10:F127)</f>
         <v/>
       </c>
-      <c r="G128" s="33">
+      <c r="G128" s="32">
         <f>SUM(G10:G127)</f>
         <v/>
       </c>
-      <c r="H128" s="33">
+      <c r="H128" s="32">
         <f>SUM(H10:H127)</f>
         <v/>
       </c>
-      <c r="I128" s="34">
+      <c r="I128" s="33">
         <f>IF(F128&gt;0, G128/F128, 1.0)</f>
         <v/>
       </c>
-      <c r="J128" s="34">
-        <f>IF(F128&gt;0, 1.0 - (H128/F128), 1.0)</f>
-        <v/>
-      </c>
-      <c r="K128" s="35" t="n"/>
-      <c r="L128" s="33">
+      <c r="J128" s="34" t="n"/>
+      <c r="K128" s="32">
+        <f>SUM(K10:K127)</f>
+        <v/>
+      </c>
+      <c r="L128" s="32">
         <f>SUM(L10:L127)</f>
         <v/>
       </c>
-      <c r="M128" s="33">
+      <c r="M128" s="32">
         <f>SUM(M10:M127)</f>
         <v/>
       </c>
-      <c r="N128" s="33">
+      <c r="N128" s="32">
         <f>SUM(N10:N127)</f>
         <v/>
       </c>
-      <c r="O128" s="33">
+      <c r="O128" s="32">
         <f>SUM(O10:O127)</f>
         <v/>
       </c>
-      <c r="P128" s="33">
+      <c r="P128" s="32">
         <f>SUM(P10:P127)</f>
         <v/>
       </c>
-      <c r="Q128" s="33">
+      <c r="Q128" s="32">
         <f>SUM(Q10:Q127)</f>
         <v/>
       </c>
-      <c r="R128" s="33">
+      <c r="R128" s="32">
         <f>SUM(R10:R127)</f>
         <v/>
       </c>
-      <c r="S128" s="33">
+      <c r="S128" s="35">
         <f>SUM(S10:S127)</f>
         <v/>
       </c>
-      <c r="T128" s="36">
-        <f>SUM(T10:T127)</f>
-        <v/>
-      </c>
-      <c r="U128" s="35" t="n"/>
+      <c r="T128" s="34" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="O5:Q5"/>
-    <mergeCell ref="B4:U4"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="F8:K8"/>
-    <mergeCell ref="L8:Q8"/>
-    <mergeCell ref="B3:U3"/>
+  <mergeCells count="20">
+    <mergeCell ref="N5:P5"/>
     <mergeCell ref="E6:G6"/>
-    <mergeCell ref="R5:U5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="R8:U8"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="B2:U2"/>
-    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="K8:P8"/>
+    <mergeCell ref="B4:T4"/>
+    <mergeCell ref="Q6:T6"/>
     <mergeCell ref="B6:D6"/>
+    <mergeCell ref="F8:J8"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="B3:T3"/>
     <mergeCell ref="B5:D5"/>
-    <mergeCell ref="R6:U6"/>
+    <mergeCell ref="Q8:T8"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="Q5:T5"/>
+    <mergeCell ref="B2:T2"/>
     <mergeCell ref="B8:E8"/>
-    <mergeCell ref="O6:Q6"/>
     <mergeCell ref="E5:G5"/>
-    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="K5:M5"/>
     <mergeCell ref="B128:E128"/>
+    <mergeCell ref="H6:J6"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="K10:K43 K10:K127" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Motivo de Desviación" error="Por favor seleccione un motivo de la lista o escriba su comentario" type="list">
+    <dataValidation sqref="J10:J43 J10:J127" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Motivo de Desviación" error="Por favor seleccione un motivo de la lista o escriba su comentario" type="list">
       <formula1>"Adelanto de pedidos,Atraso de pedidos,Pedido extra no previsto,Campaña habitual,Cancelado / Sin siembra,Otro motivo"</formula1>
     </dataValidation>
   </dataValidations>
